--- a/html/Specialsystemer_excel.XLSX
+++ b/html/Specialsystemer_excel.XLSX
@@ -5,25 +5,25 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://medcomdk-my.sharepoint.com/personal/sof_medcom_dk/Documents/Dokumenter/GitHub/GodkendteSystemer/html/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{481C86E7-C42D-456B-988B-5872EBE3F480}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="1" documentId="11_BEA61AB95DAD33E7D50B2C219EB39BDA71D99364" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{18361D3D-0E6D-431B-820C-4506F9762960}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 09-09-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 14-09-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Specialsystemer">'Opdateret d. 09-09-2026'!$A$1:$BM$173</definedName>
+    <definedName name="Specialsystemer">'Opdateret d. 14-09-2026'!$A$1:$BM$173</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1194" uniqueCount="256">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1195" uniqueCount="256">
   <si>
     <t>Standard</t>
   </si>
@@ -1134,9 +1134,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:BM173"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1" spans="1:65" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:65" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1333,7 +1333,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="2" spans="1:65" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:65" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>65</v>
       </c>
@@ -1353,7 +1353,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="3" spans="1:65" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:65" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>70</v>
       </c>
@@ -1373,7 +1373,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="4" spans="1:65" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:65" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>72</v>
       </c>
@@ -1405,7 +1405,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="5" spans="1:65" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:65" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>74</v>
       </c>
@@ -1418,8 +1418,11 @@
       <c r="V5" t="s">
         <v>69</v>
       </c>
-    </row>
-    <row r="6" spans="1:65" x14ac:dyDescent="0.3">
+      <c r="AC5" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="6" spans="1:65" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>76</v>
       </c>
@@ -1439,7 +1442,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="7" spans="1:65" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:65" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>78</v>
       </c>
@@ -1456,7 +1459,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="8" spans="1:65" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:65" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>81</v>
       </c>
@@ -1521,7 +1524,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="9" spans="1:65" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:65" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>83</v>
       </c>
@@ -1571,7 +1574,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="10" spans="1:65" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:65" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>85</v>
       </c>
@@ -1585,7 +1588,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="11" spans="1:65" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:65" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>87</v>
       </c>
@@ -1599,7 +1602,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="12" spans="1:65" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:65" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>89</v>
       </c>
@@ -1613,7 +1616,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="13" spans="1:65" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:65" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>91</v>
       </c>
@@ -1627,7 +1630,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="14" spans="1:65" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:65" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>91</v>
       </c>
@@ -1641,7 +1644,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="15" spans="1:65" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:65" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>94</v>
       </c>
@@ -1655,7 +1658,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="16" spans="1:65" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:65" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
         <v>96</v>
       </c>
@@ -1669,7 +1672,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="17" spans="1:65" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:65" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
         <v>98</v>
       </c>
@@ -1683,7 +1686,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="18" spans="1:65" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:65" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
         <v>100</v>
       </c>
@@ -1739,7 +1742,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="19" spans="1:65" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:65" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
         <v>102</v>
       </c>
@@ -1753,7 +1756,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="20" spans="1:65" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:65" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
         <v>104</v>
       </c>
@@ -1776,7 +1779,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="21" spans="1:65" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:65" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
         <v>104</v>
       </c>
@@ -1790,7 +1793,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="22" spans="1:65" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:65" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
         <v>107</v>
       </c>
@@ -1804,7 +1807,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="23" spans="1:65" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:65" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
         <v>109</v>
       </c>
@@ -1818,7 +1821,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="24" spans="1:65" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:65" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
         <v>111</v>
       </c>
@@ -1835,7 +1838,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="25" spans="1:65" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:65" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
         <v>113</v>
       </c>
@@ -1849,7 +1852,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="26" spans="1:65" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:65" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
         <v>115</v>
       </c>
@@ -1866,7 +1869,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="27" spans="1:65" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:65" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
         <v>117</v>
       </c>
@@ -1895,7 +1898,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="28" spans="1:65" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:65" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
         <v>117</v>
       </c>
@@ -1921,7 +1924,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="29" spans="1:65" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:65" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
         <v>120</v>
       </c>
@@ -1938,7 +1941,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="30" spans="1:65" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:65" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
         <v>120</v>
       </c>
@@ -1964,7 +1967,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="31" spans="1:65" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:65" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
         <v>124</v>
       </c>
@@ -1978,7 +1981,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="32" spans="1:65" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:65" x14ac:dyDescent="0.35">
       <c r="A32" t="s">
         <v>124</v>
       </c>
@@ -2001,7 +2004,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="33" spans="1:65" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:65" x14ac:dyDescent="0.35">
       <c r="A33" t="s">
         <v>127</v>
       </c>
@@ -2021,7 +2024,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="34" spans="1:65" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:65" x14ac:dyDescent="0.35">
       <c r="A34" t="s">
         <v>127</v>
       </c>
@@ -2041,7 +2044,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="35" spans="1:65" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:65" x14ac:dyDescent="0.35">
       <c r="A35" t="s">
         <v>130</v>
       </c>
@@ -2061,7 +2064,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="36" spans="1:65" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:65" x14ac:dyDescent="0.35">
       <c r="A36" t="s">
         <v>132</v>
       </c>
@@ -2078,7 +2081,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="37" spans="1:65" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:65" x14ac:dyDescent="0.35">
       <c r="A37" t="s">
         <v>132</v>
       </c>
@@ -2092,7 +2095,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="38" spans="1:65" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:65" x14ac:dyDescent="0.35">
       <c r="A38" t="s">
         <v>132</v>
       </c>
@@ -2106,7 +2109,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="39" spans="1:65" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:65" x14ac:dyDescent="0.35">
       <c r="A39" t="s">
         <v>136</v>
       </c>
@@ -2126,7 +2129,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="40" spans="1:65" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:65" x14ac:dyDescent="0.35">
       <c r="A40" t="s">
         <v>138</v>
       </c>
@@ -2143,7 +2146,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="41" spans="1:65" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:65" x14ac:dyDescent="0.35">
       <c r="A41" t="s">
         <v>138</v>
       </c>
@@ -2160,7 +2163,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="42" spans="1:65" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:65" x14ac:dyDescent="0.35">
       <c r="A42" t="s">
         <v>141</v>
       </c>
@@ -2174,7 +2177,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="43" spans="1:65" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:65" x14ac:dyDescent="0.35">
       <c r="A43" t="s">
         <v>141</v>
       </c>
@@ -2188,7 +2191,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="44" spans="1:65" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:65" x14ac:dyDescent="0.35">
       <c r="A44" t="s">
         <v>144</v>
       </c>
@@ -2208,7 +2211,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="45" spans="1:65" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:65" x14ac:dyDescent="0.35">
       <c r="A45" t="s">
         <v>144</v>
       </c>
@@ -2231,7 +2234,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="46" spans="1:65" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:65" x14ac:dyDescent="0.35">
       <c r="A46" t="s">
         <v>147</v>
       </c>
@@ -2248,7 +2251,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="47" spans="1:65" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:65" x14ac:dyDescent="0.35">
       <c r="A47" t="s">
         <v>149</v>
       </c>
@@ -2262,7 +2265,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="48" spans="1:65" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:65" x14ac:dyDescent="0.35">
       <c r="A48" t="s">
         <v>149</v>
       </c>
@@ -2276,7 +2279,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="49" spans="1:64" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:64" x14ac:dyDescent="0.35">
       <c r="A49" t="s">
         <v>152</v>
       </c>
@@ -2293,7 +2296,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="50" spans="1:64" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:64" x14ac:dyDescent="0.35">
       <c r="A50" t="s">
         <v>154</v>
       </c>
@@ -2316,7 +2319,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="51" spans="1:64" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:64" x14ac:dyDescent="0.35">
       <c r="A51" t="s">
         <v>156</v>
       </c>
@@ -2348,7 +2351,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="52" spans="1:64" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:64" x14ac:dyDescent="0.35">
       <c r="A52" t="s">
         <v>156</v>
       </c>
@@ -2368,7 +2371,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="53" spans="1:64" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:64" x14ac:dyDescent="0.35">
       <c r="A53" t="s">
         <v>159</v>
       </c>
@@ -2403,7 +2406,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="54" spans="1:64" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:64" x14ac:dyDescent="0.35">
       <c r="A54" t="s">
         <v>161</v>
       </c>
@@ -2417,7 +2420,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="55" spans="1:64" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:64" x14ac:dyDescent="0.35">
       <c r="A55" t="s">
         <v>163</v>
       </c>
@@ -2467,7 +2470,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="56" spans="1:64" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:64" x14ac:dyDescent="0.35">
       <c r="A56" t="s">
         <v>165</v>
       </c>
@@ -2517,7 +2520,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="57" spans="1:64" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:64" x14ac:dyDescent="0.35">
       <c r="A57" t="s">
         <v>167</v>
       </c>
@@ -2531,7 +2534,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="58" spans="1:64" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:64" x14ac:dyDescent="0.35">
       <c r="A58" t="s">
         <v>169</v>
       </c>
@@ -2545,7 +2548,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="59" spans="1:64" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:64" x14ac:dyDescent="0.35">
       <c r="A59" t="s">
         <v>169</v>
       </c>
@@ -2559,7 +2562,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="60" spans="1:64" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:64" x14ac:dyDescent="0.35">
       <c r="A60" t="s">
         <v>172</v>
       </c>
@@ -2573,7 +2576,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="61" spans="1:64" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:64" x14ac:dyDescent="0.35">
       <c r="A61" t="s">
         <v>174</v>
       </c>
@@ -2596,7 +2599,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="62" spans="1:64" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:64" x14ac:dyDescent="0.35">
       <c r="A62" t="s">
         <v>176</v>
       </c>
@@ -2610,7 +2613,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="63" spans="1:64" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:64" x14ac:dyDescent="0.35">
       <c r="A63" t="s">
         <v>178</v>
       </c>
@@ -2624,7 +2627,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="64" spans="1:64" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:64" x14ac:dyDescent="0.35">
       <c r="A64" t="s">
         <v>180</v>
       </c>
@@ -2638,7 +2641,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="65" spans="1:65" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:65" x14ac:dyDescent="0.35">
       <c r="A65" t="s">
         <v>180</v>
       </c>
@@ -2652,7 +2655,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="66" spans="1:65" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:65" x14ac:dyDescent="0.35">
       <c r="A66" t="s">
         <v>183</v>
       </c>
@@ -2666,7 +2669,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="67" spans="1:65" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:65" x14ac:dyDescent="0.35">
       <c r="A67" t="s">
         <v>185</v>
       </c>
@@ -2725,7 +2728,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="68" spans="1:65" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:65" x14ac:dyDescent="0.35">
       <c r="A68" t="s">
         <v>187</v>
       </c>
@@ -2754,7 +2757,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="69" spans="1:65" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:65" x14ac:dyDescent="0.35">
       <c r="A69" t="s">
         <v>187</v>
       </c>
@@ -2777,7 +2780,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="70" spans="1:65" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:65" x14ac:dyDescent="0.35">
       <c r="A70" t="s">
         <v>190</v>
       </c>
@@ -2791,7 +2794,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="71" spans="1:65" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:65" x14ac:dyDescent="0.35">
       <c r="A71" t="s">
         <v>192</v>
       </c>
@@ -2811,7 +2814,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="72" spans="1:65" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:65" x14ac:dyDescent="0.35">
       <c r="A72" t="s">
         <v>194</v>
       </c>
@@ -2825,7 +2828,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="73" spans="1:65" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:65" x14ac:dyDescent="0.35">
       <c r="A73" t="s">
         <v>196</v>
       </c>
@@ -2839,7 +2842,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="74" spans="1:65" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:65" x14ac:dyDescent="0.35">
       <c r="A74" t="s">
         <v>196</v>
       </c>
@@ -2859,7 +2862,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="75" spans="1:65" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:65" x14ac:dyDescent="0.35">
       <c r="A75" t="s">
         <v>199</v>
       </c>
@@ -2873,7 +2876,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="76" spans="1:65" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:65" x14ac:dyDescent="0.35">
       <c r="A76" t="s">
         <v>201</v>
       </c>
@@ -2893,7 +2896,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="77" spans="1:65" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:65" x14ac:dyDescent="0.35">
       <c r="A77" t="s">
         <v>203</v>
       </c>
@@ -2910,7 +2913,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="78" spans="1:65" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:65" x14ac:dyDescent="0.35">
       <c r="A78" t="s">
         <v>205</v>
       </c>
@@ -2924,7 +2927,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="79" spans="1:65" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:65" x14ac:dyDescent="0.35">
       <c r="A79" t="s">
         <v>207</v>
       </c>
@@ -2938,7 +2941,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="80" spans="1:65" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:65" x14ac:dyDescent="0.35">
       <c r="A80" t="s">
         <v>209</v>
       </c>
@@ -2952,7 +2955,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="81" spans="1:64" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:64" x14ac:dyDescent="0.35">
       <c r="A81" t="s">
         <v>65</v>
       </c>
@@ -2972,7 +2975,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="82" spans="1:64" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:64" x14ac:dyDescent="0.35">
       <c r="A82" t="s">
         <v>70</v>
       </c>
@@ -3007,7 +3010,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="83" spans="1:64" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:64" x14ac:dyDescent="0.35">
       <c r="A83" t="s">
         <v>72</v>
       </c>
@@ -3030,7 +3033,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="84" spans="1:64" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:64" x14ac:dyDescent="0.35">
       <c r="A84" t="s">
         <v>74</v>
       </c>
@@ -3044,7 +3047,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="85" spans="1:64" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:64" x14ac:dyDescent="0.35">
       <c r="A85" t="s">
         <v>76</v>
       </c>
@@ -3064,7 +3067,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="86" spans="1:64" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:64" x14ac:dyDescent="0.35">
       <c r="A86" t="s">
         <v>78</v>
       </c>
@@ -3081,7 +3084,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="87" spans="1:64" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:64" x14ac:dyDescent="0.35">
       <c r="A87" t="s">
         <v>212</v>
       </c>
@@ -3098,7 +3101,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="88" spans="1:64" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:64" x14ac:dyDescent="0.35">
       <c r="A88" t="s">
         <v>214</v>
       </c>
@@ -3115,7 +3118,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="89" spans="1:64" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:64" x14ac:dyDescent="0.35">
       <c r="A89" t="s">
         <v>214</v>
       </c>
@@ -3138,7 +3141,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="90" spans="1:64" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:64" x14ac:dyDescent="0.35">
       <c r="A90" t="s">
         <v>217</v>
       </c>
@@ -3209,7 +3212,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="91" spans="1:64" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:64" x14ac:dyDescent="0.35">
       <c r="A91" t="s">
         <v>81</v>
       </c>
@@ -3283,7 +3286,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="92" spans="1:64" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:64" x14ac:dyDescent="0.35">
       <c r="A92" t="s">
         <v>83</v>
       </c>
@@ -3354,7 +3357,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="93" spans="1:64" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:64" x14ac:dyDescent="0.35">
       <c r="A93" t="s">
         <v>85</v>
       </c>
@@ -3368,7 +3371,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="94" spans="1:64" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:64" x14ac:dyDescent="0.35">
       <c r="A94" t="s">
         <v>87</v>
       </c>
@@ -3382,7 +3385,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="95" spans="1:64" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:64" x14ac:dyDescent="0.35">
       <c r="A95" t="s">
         <v>89</v>
       </c>
@@ -3399,7 +3402,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="96" spans="1:64" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:64" x14ac:dyDescent="0.35">
       <c r="A96" t="s">
         <v>89</v>
       </c>
@@ -3416,7 +3419,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="97" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:60" x14ac:dyDescent="0.35">
       <c r="A97" t="s">
         <v>91</v>
       </c>
@@ -3430,7 +3433,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="98" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:60" x14ac:dyDescent="0.35">
       <c r="A98" t="s">
         <v>91</v>
       </c>
@@ -3456,7 +3459,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="99" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:60" x14ac:dyDescent="0.35">
       <c r="A99" t="s">
         <v>220</v>
       </c>
@@ -3473,7 +3476,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="100" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:60" x14ac:dyDescent="0.35">
       <c r="A100" t="s">
         <v>222</v>
       </c>
@@ -3493,7 +3496,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="101" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:60" x14ac:dyDescent="0.35">
       <c r="A101" t="s">
         <v>94</v>
       </c>
@@ -3510,7 +3513,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="102" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:60" x14ac:dyDescent="0.35">
       <c r="A102" t="s">
         <v>96</v>
       </c>
@@ -3527,7 +3530,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="103" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:60" x14ac:dyDescent="0.35">
       <c r="A103" t="s">
         <v>98</v>
       </c>
@@ -3541,7 +3544,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="104" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:60" x14ac:dyDescent="0.35">
       <c r="A104" t="s">
         <v>100</v>
       </c>
@@ -3585,7 +3588,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="105" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:60" x14ac:dyDescent="0.35">
       <c r="A105" t="s">
         <v>102</v>
       </c>
@@ -3605,7 +3608,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="106" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:60" x14ac:dyDescent="0.35">
       <c r="A106" t="s">
         <v>102</v>
       </c>
@@ -3625,7 +3628,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="107" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:60" x14ac:dyDescent="0.35">
       <c r="A107" t="s">
         <v>225</v>
       </c>
@@ -3639,7 +3642,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="108" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:60" x14ac:dyDescent="0.35">
       <c r="A108" t="s">
         <v>104</v>
       </c>
@@ -3659,7 +3662,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="109" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:60" x14ac:dyDescent="0.35">
       <c r="A109" t="s">
         <v>104</v>
       </c>
@@ -3673,7 +3676,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="110" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:60" x14ac:dyDescent="0.35">
       <c r="A110" t="s">
         <v>107</v>
       </c>
@@ -3693,7 +3696,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="111" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:60" x14ac:dyDescent="0.35">
       <c r="A111" t="s">
         <v>109</v>
       </c>
@@ -3713,7 +3716,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="112" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:60" x14ac:dyDescent="0.35">
       <c r="A112" t="s">
         <v>111</v>
       </c>
@@ -3730,7 +3733,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="113" spans="1:59" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:59" x14ac:dyDescent="0.35">
       <c r="A113" t="s">
         <v>113</v>
       </c>
@@ -3750,7 +3753,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="114" spans="1:59" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:59" x14ac:dyDescent="0.35">
       <c r="A114" t="s">
         <v>115</v>
       </c>
@@ -3764,7 +3767,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="115" spans="1:59" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:59" x14ac:dyDescent="0.35">
       <c r="A115" t="s">
         <v>115</v>
       </c>
@@ -3778,7 +3781,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="116" spans="1:59" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:59" x14ac:dyDescent="0.35">
       <c r="A116" t="s">
         <v>117</v>
       </c>
@@ -3798,7 +3801,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="117" spans="1:59" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:59" x14ac:dyDescent="0.35">
       <c r="A117" t="s">
         <v>117</v>
       </c>
@@ -3818,7 +3821,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="118" spans="1:59" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:59" x14ac:dyDescent="0.35">
       <c r="A118" t="s">
         <v>120</v>
       </c>
@@ -3832,7 +3835,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="119" spans="1:59" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:59" x14ac:dyDescent="0.35">
       <c r="A119" t="s">
         <v>120</v>
       </c>
@@ -3858,7 +3861,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="120" spans="1:59" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:59" x14ac:dyDescent="0.35">
       <c r="A120" t="s">
         <v>124</v>
       </c>
@@ -3884,7 +3887,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="121" spans="1:59" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:59" x14ac:dyDescent="0.35">
       <c r="A121" t="s">
         <v>127</v>
       </c>
@@ -3907,7 +3910,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="122" spans="1:59" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:59" x14ac:dyDescent="0.35">
       <c r="A122" t="s">
         <v>127</v>
       </c>
@@ -3930,7 +3933,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="123" spans="1:59" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:59" x14ac:dyDescent="0.35">
       <c r="A123" t="s">
         <v>130</v>
       </c>
@@ -3953,7 +3956,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="124" spans="1:59" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:59" x14ac:dyDescent="0.35">
       <c r="A124" t="s">
         <v>132</v>
       </c>
@@ -3973,7 +3976,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="125" spans="1:59" x14ac:dyDescent="0.3">
+    <row r="125" spans="1:59" x14ac:dyDescent="0.35">
       <c r="A125" t="s">
         <v>132</v>
       </c>
@@ -3990,7 +3993,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="126" spans="1:59" x14ac:dyDescent="0.3">
+    <row r="126" spans="1:59" x14ac:dyDescent="0.35">
       <c r="A126" t="s">
         <v>132</v>
       </c>
@@ -4007,7 +4010,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="127" spans="1:59" x14ac:dyDescent="0.3">
+    <row r="127" spans="1:59" x14ac:dyDescent="0.35">
       <c r="A127" t="s">
         <v>136</v>
       </c>
@@ -4030,7 +4033,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="128" spans="1:59" x14ac:dyDescent="0.3">
+    <row r="128" spans="1:59" x14ac:dyDescent="0.35">
       <c r="A128" t="s">
         <v>138</v>
       </c>
@@ -4050,7 +4053,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="129" spans="1:59" x14ac:dyDescent="0.3">
+    <row r="129" spans="1:59" x14ac:dyDescent="0.35">
       <c r="A129" t="s">
         <v>138</v>
       </c>
@@ -4073,7 +4076,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="130" spans="1:59" x14ac:dyDescent="0.3">
+    <row r="130" spans="1:59" x14ac:dyDescent="0.35">
       <c r="A130" t="s">
         <v>141</v>
       </c>
@@ -4087,7 +4090,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="131" spans="1:59" x14ac:dyDescent="0.3">
+    <row r="131" spans="1:59" x14ac:dyDescent="0.35">
       <c r="A131" t="s">
         <v>144</v>
       </c>
@@ -4101,7 +4104,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="132" spans="1:59" x14ac:dyDescent="0.3">
+    <row r="132" spans="1:59" x14ac:dyDescent="0.35">
       <c r="A132" t="s">
         <v>144</v>
       </c>
@@ -4130,7 +4133,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="133" spans="1:59" x14ac:dyDescent="0.3">
+    <row r="133" spans="1:59" x14ac:dyDescent="0.35">
       <c r="A133" t="s">
         <v>228</v>
       </c>
@@ -4147,7 +4150,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="134" spans="1:59" x14ac:dyDescent="0.3">
+    <row r="134" spans="1:59" x14ac:dyDescent="0.35">
       <c r="A134" t="s">
         <v>230</v>
       </c>
@@ -4161,7 +4164,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="135" spans="1:59" x14ac:dyDescent="0.3">
+    <row r="135" spans="1:59" x14ac:dyDescent="0.35">
       <c r="A135" t="s">
         <v>232</v>
       </c>
@@ -4178,7 +4181,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="136" spans="1:59" x14ac:dyDescent="0.3">
+    <row r="136" spans="1:59" x14ac:dyDescent="0.35">
       <c r="A136" t="s">
         <v>234</v>
       </c>
@@ -4195,7 +4198,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="137" spans="1:59" x14ac:dyDescent="0.3">
+    <row r="137" spans="1:59" x14ac:dyDescent="0.35">
       <c r="A137" t="s">
         <v>234</v>
       </c>
@@ -4215,7 +4218,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="138" spans="1:59" x14ac:dyDescent="0.3">
+    <row r="138" spans="1:59" x14ac:dyDescent="0.35">
       <c r="A138" t="s">
         <v>237</v>
       </c>
@@ -4229,7 +4232,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="139" spans="1:59" x14ac:dyDescent="0.3">
+    <row r="139" spans="1:59" x14ac:dyDescent="0.35">
       <c r="A139" t="s">
         <v>154</v>
       </c>
@@ -4243,7 +4246,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="140" spans="1:59" x14ac:dyDescent="0.3">
+    <row r="140" spans="1:59" x14ac:dyDescent="0.35">
       <c r="A140" t="s">
         <v>240</v>
       </c>
@@ -4257,7 +4260,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="141" spans="1:59" x14ac:dyDescent="0.3">
+    <row r="141" spans="1:59" x14ac:dyDescent="0.35">
       <c r="A141" t="s">
         <v>242</v>
       </c>
@@ -4271,7 +4274,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="142" spans="1:59" x14ac:dyDescent="0.3">
+    <row r="142" spans="1:59" x14ac:dyDescent="0.35">
       <c r="A142" t="s">
         <v>156</v>
       </c>
@@ -4303,7 +4306,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="143" spans="1:59" x14ac:dyDescent="0.3">
+    <row r="143" spans="1:59" x14ac:dyDescent="0.35">
       <c r="A143" t="s">
         <v>156</v>
       </c>
@@ -4320,7 +4323,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="144" spans="1:59" x14ac:dyDescent="0.3">
+    <row r="144" spans="1:59" x14ac:dyDescent="0.35">
       <c r="A144" t="s">
         <v>159</v>
       </c>
@@ -4352,7 +4355,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="145" spans="1:56" x14ac:dyDescent="0.3">
+    <row r="145" spans="1:56" x14ac:dyDescent="0.35">
       <c r="A145" t="s">
         <v>244</v>
       </c>
@@ -4423,7 +4426,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="146" spans="1:56" x14ac:dyDescent="0.3">
+    <row r="146" spans="1:56" x14ac:dyDescent="0.35">
       <c r="A146" t="s">
         <v>163</v>
       </c>
@@ -4497,7 +4500,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="147" spans="1:56" x14ac:dyDescent="0.3">
+    <row r="147" spans="1:56" x14ac:dyDescent="0.35">
       <c r="A147" t="s">
         <v>165</v>
       </c>
@@ -4565,7 +4568,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="148" spans="1:56" x14ac:dyDescent="0.3">
+    <row r="148" spans="1:56" x14ac:dyDescent="0.35">
       <c r="A148" t="s">
         <v>167</v>
       </c>
@@ -4579,7 +4582,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="149" spans="1:56" x14ac:dyDescent="0.3">
+    <row r="149" spans="1:56" x14ac:dyDescent="0.35">
       <c r="A149" t="s">
         <v>167</v>
       </c>
@@ -4593,13 +4596,13 @@
         <v>69</v>
       </c>
       <c r="AC149" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="AD149" t="s">
         <v>123</v>
       </c>
     </row>
-    <row r="150" spans="1:56" x14ac:dyDescent="0.3">
+    <row r="150" spans="1:56" x14ac:dyDescent="0.35">
       <c r="A150" t="s">
         <v>169</v>
       </c>
@@ -4616,7 +4619,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="151" spans="1:56" x14ac:dyDescent="0.3">
+    <row r="151" spans="1:56" x14ac:dyDescent="0.35">
       <c r="A151" t="s">
         <v>169</v>
       </c>
@@ -4627,13 +4630,13 @@
         <v>211</v>
       </c>
       <c r="AC151" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="AD151" t="s">
         <v>123</v>
       </c>
     </row>
-    <row r="152" spans="1:56" x14ac:dyDescent="0.3">
+    <row r="152" spans="1:56" x14ac:dyDescent="0.35">
       <c r="A152" t="s">
         <v>172</v>
       </c>
@@ -4644,10 +4647,10 @@
         <v>211</v>
       </c>
       <c r="AC152" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="153" spans="1:56" x14ac:dyDescent="0.3">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="153" spans="1:56" x14ac:dyDescent="0.35">
       <c r="A153" t="s">
         <v>247</v>
       </c>
@@ -4661,10 +4664,10 @@
         <v>69</v>
       </c>
       <c r="AC153" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="154" spans="1:56" x14ac:dyDescent="0.3">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="154" spans="1:56" x14ac:dyDescent="0.35">
       <c r="A154" t="s">
         <v>176</v>
       </c>
@@ -4681,7 +4684,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="155" spans="1:56" x14ac:dyDescent="0.3">
+    <row r="155" spans="1:56" x14ac:dyDescent="0.35">
       <c r="A155" t="s">
         <v>176</v>
       </c>
@@ -4692,10 +4695,10 @@
         <v>211</v>
       </c>
       <c r="AC155" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="156" spans="1:56" x14ac:dyDescent="0.3">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="156" spans="1:56" x14ac:dyDescent="0.35">
       <c r="A156" t="s">
         <v>178</v>
       </c>
@@ -4715,7 +4718,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="157" spans="1:56" x14ac:dyDescent="0.3">
+    <row r="157" spans="1:56" x14ac:dyDescent="0.35">
       <c r="A157" t="s">
         <v>180</v>
       </c>
@@ -4729,7 +4732,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="158" spans="1:56" x14ac:dyDescent="0.3">
+    <row r="158" spans="1:56" x14ac:dyDescent="0.35">
       <c r="A158" t="s">
         <v>180</v>
       </c>
@@ -4743,7 +4746,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="159" spans="1:56" x14ac:dyDescent="0.3">
+    <row r="159" spans="1:56" x14ac:dyDescent="0.35">
       <c r="A159" t="s">
         <v>183</v>
       </c>
@@ -4757,7 +4760,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="160" spans="1:56" x14ac:dyDescent="0.3">
+    <row r="160" spans="1:56" x14ac:dyDescent="0.35">
       <c r="A160" t="s">
         <v>185</v>
       </c>
@@ -4798,7 +4801,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="161" spans="1:59" x14ac:dyDescent="0.3">
+    <row r="161" spans="1:59" x14ac:dyDescent="0.35">
       <c r="A161" t="s">
         <v>187</v>
       </c>
@@ -4833,7 +4836,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="162" spans="1:59" x14ac:dyDescent="0.3">
+    <row r="162" spans="1:59" x14ac:dyDescent="0.35">
       <c r="A162" t="s">
         <v>187</v>
       </c>
@@ -4850,7 +4853,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="163" spans="1:59" x14ac:dyDescent="0.3">
+    <row r="163" spans="1:59" x14ac:dyDescent="0.35">
       <c r="A163" t="s">
         <v>192</v>
       </c>
@@ -4864,7 +4867,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="164" spans="1:59" x14ac:dyDescent="0.3">
+    <row r="164" spans="1:59" x14ac:dyDescent="0.35">
       <c r="A164" t="s">
         <v>192</v>
       </c>
@@ -4884,7 +4887,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="165" spans="1:59" x14ac:dyDescent="0.3">
+    <row r="165" spans="1:59" x14ac:dyDescent="0.35">
       <c r="A165" t="s">
         <v>196</v>
       </c>
@@ -4898,7 +4901,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="166" spans="1:59" x14ac:dyDescent="0.3">
+    <row r="166" spans="1:59" x14ac:dyDescent="0.35">
       <c r="A166" t="s">
         <v>196</v>
       </c>
@@ -4915,7 +4918,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="167" spans="1:59" x14ac:dyDescent="0.3">
+    <row r="167" spans="1:59" x14ac:dyDescent="0.35">
       <c r="A167" t="s">
         <v>201</v>
       </c>
@@ -4941,7 +4944,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="168" spans="1:59" x14ac:dyDescent="0.3">
+    <row r="168" spans="1:59" x14ac:dyDescent="0.35">
       <c r="A168" t="s">
         <v>203</v>
       </c>
@@ -4961,7 +4964,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="169" spans="1:59" x14ac:dyDescent="0.3">
+    <row r="169" spans="1:59" x14ac:dyDescent="0.35">
       <c r="A169" t="s">
         <v>207</v>
       </c>
@@ -4981,7 +4984,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="170" spans="1:59" x14ac:dyDescent="0.3">
+    <row r="170" spans="1:59" x14ac:dyDescent="0.35">
       <c r="A170" t="s">
         <v>207</v>
       </c>
@@ -5007,7 +5010,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="171" spans="1:59" x14ac:dyDescent="0.3">
+    <row r="171" spans="1:59" x14ac:dyDescent="0.35">
       <c r="A171" t="s">
         <v>252</v>
       </c>
@@ -5024,7 +5027,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="172" spans="1:59" x14ac:dyDescent="0.3">
+    <row r="172" spans="1:59" x14ac:dyDescent="0.35">
       <c r="A172" t="s">
         <v>209</v>
       </c>
@@ -5050,7 +5053,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="173" spans="1:59" x14ac:dyDescent="0.3">
+    <row r="173" spans="1:59" x14ac:dyDescent="0.35">
       <c r="A173" t="s">
         <v>254</v>
       </c>

--- a/html/Specialsystemer_excel.XLSX
+++ b/html/Specialsystemer_excel.XLSX
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://medcomdk-my.sharepoint.com/personal/sof_medcom_dk/Documents/Dokumenter/GitHub/GodkendteSystemer/html/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1" documentId="11_BEA61AB95DAD33E7D50B2C219EB39BDA71D99364" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{18361D3D-0E6D-431B-820C-4506F9762960}"/>
+  <xr:revisionPtr revIDLastSave="1" documentId="11_BEA61AB9C41DB7D11B0B2C2166749E5270D96C92" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3DA85A02-E305-4417-9C9F-48E3B0FF36D4}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3416,7 +3416,7 @@
         <v>69</v>
       </c>
       <c r="AC96" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
     </row>
     <row r="97" spans="1:60" x14ac:dyDescent="0.35">
@@ -3453,7 +3453,7 @@
         <v>69</v>
       </c>
       <c r="AC98" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="AD98" t="s">
         <v>123</v>
@@ -3473,7 +3473,7 @@
         <v>69</v>
       </c>
       <c r="AC99" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
     </row>
     <row r="100" spans="1:60" x14ac:dyDescent="0.35">
@@ -3493,7 +3493,7 @@
         <v>69</v>
       </c>
       <c r="AC100" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
     </row>
     <row r="101" spans="1:60" x14ac:dyDescent="0.35">
@@ -3510,7 +3510,7 @@
         <v>69</v>
       </c>
       <c r="AC101" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
     </row>
     <row r="102" spans="1:60" x14ac:dyDescent="0.35">

--- a/html/Specialsystemer_excel.XLSX
+++ b/html/Specialsystemer_excel.XLSX
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://medcomdk-my.sharepoint.com/personal/sof_medcom_dk/Documents/Dokumenter/GitHub/GodkendteSystemer/html/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1" documentId="11_BEA61AB9C41DB7D11B0B2C2166749E5270D96C92" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3DA85A02-E305-4417-9C9F-48E3B0FF36D4}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{44D18BD5-4405-4503-9044-43BE6B3206D7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1440" yWindow="1632" windowWidth="21600" windowHeight="11232" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Opdateret d. 14-09-2026" sheetId="1" r:id="rId1"/>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1195" uniqueCount="256">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1204" uniqueCount="256">
   <si>
     <t>Standard</t>
   </si>
@@ -1134,9 +1134,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:BM173"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:65" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:65" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1333,7 +1333,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="2" spans="1:65" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:65" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>65</v>
       </c>
@@ -1353,7 +1353,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="3" spans="1:65" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:65" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>70</v>
       </c>
@@ -1373,7 +1373,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="4" spans="1:65" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:65" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>72</v>
       </c>
@@ -1404,8 +1404,11 @@
       <c r="AY4" t="s">
         <v>69</v>
       </c>
-    </row>
-    <row r="5" spans="1:65" x14ac:dyDescent="0.35">
+      <c r="BD4" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="5" spans="1:65" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>74</v>
       </c>
@@ -1422,7 +1425,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="6" spans="1:65" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:65" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>76</v>
       </c>
@@ -1442,7 +1445,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="7" spans="1:65" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:65" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>78</v>
       </c>
@@ -1459,7 +1462,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="8" spans="1:65" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:65" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>81</v>
       </c>
@@ -1514,6 +1517,9 @@
       <c r="AY8" t="s">
         <v>69</v>
       </c>
+      <c r="BD8" t="s">
+        <v>69</v>
+      </c>
       <c r="BE8" t="s">
         <v>69</v>
       </c>
@@ -1524,7 +1530,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="9" spans="1:65" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:65" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>83</v>
       </c>
@@ -1570,11 +1576,14 @@
       <c r="BA9" t="s">
         <v>69</v>
       </c>
+      <c r="BD9" t="s">
+        <v>69</v>
+      </c>
       <c r="BE9" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="10" spans="1:65" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:65" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>85</v>
       </c>
@@ -1588,7 +1597,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="11" spans="1:65" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:65" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>87</v>
       </c>
@@ -1602,7 +1611,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="12" spans="1:65" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:65" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>89</v>
       </c>
@@ -1616,7 +1625,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="13" spans="1:65" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:65" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>91</v>
       </c>
@@ -1630,7 +1639,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="14" spans="1:65" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:65" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>91</v>
       </c>
@@ -1644,7 +1653,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="15" spans="1:65" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:65" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>94</v>
       </c>
@@ -1658,7 +1667,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="16" spans="1:65" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:65" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>96</v>
       </c>
@@ -1672,7 +1681,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="17" spans="1:65" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:65" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>98</v>
       </c>
@@ -1686,7 +1695,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="18" spans="1:65" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:65" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>100</v>
       </c>
@@ -1735,6 +1744,9 @@
       <c r="BA18" t="s">
         <v>69</v>
       </c>
+      <c r="BD18" t="s">
+        <v>69</v>
+      </c>
       <c r="BF18" t="s">
         <v>69</v>
       </c>
@@ -1742,7 +1754,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="19" spans="1:65" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:65" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>102</v>
       </c>
@@ -1756,7 +1768,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="20" spans="1:65" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:65" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>104</v>
       </c>
@@ -1779,7 +1791,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="21" spans="1:65" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:65" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>104</v>
       </c>
@@ -1793,7 +1805,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="22" spans="1:65" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:65" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>107</v>
       </c>
@@ -1807,7 +1819,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="23" spans="1:65" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:65" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>109</v>
       </c>
@@ -1821,7 +1833,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="24" spans="1:65" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:65" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>111</v>
       </c>
@@ -1838,7 +1850,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="25" spans="1:65" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:65" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>113</v>
       </c>
@@ -1852,7 +1864,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="26" spans="1:65" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:65" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>115</v>
       </c>
@@ -1869,7 +1881,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="27" spans="1:65" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:65" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>117</v>
       </c>
@@ -1898,7 +1910,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="28" spans="1:65" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:65" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>117</v>
       </c>
@@ -1924,7 +1936,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="29" spans="1:65" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:65" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>120</v>
       </c>
@@ -1941,7 +1953,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="30" spans="1:65" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:65" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>120</v>
       </c>
@@ -1967,7 +1979,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="31" spans="1:65" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:65" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>124</v>
       </c>
@@ -1981,7 +1993,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="32" spans="1:65" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:65" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
         <v>124</v>
       </c>
@@ -2004,7 +2016,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="33" spans="1:65" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:65" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
         <v>127</v>
       </c>
@@ -2024,7 +2036,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="34" spans="1:65" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:65" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
         <v>127</v>
       </c>
@@ -2044,7 +2056,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="35" spans="1:65" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:65" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
         <v>130</v>
       </c>
@@ -2064,7 +2076,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="36" spans="1:65" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:65" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
         <v>132</v>
       </c>
@@ -2081,7 +2093,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="37" spans="1:65" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:65" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
         <v>132</v>
       </c>
@@ -2095,7 +2107,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="38" spans="1:65" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:65" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
         <v>132</v>
       </c>
@@ -2109,7 +2121,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="39" spans="1:65" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:65" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
         <v>136</v>
       </c>
@@ -2129,7 +2141,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="40" spans="1:65" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:65" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
         <v>138</v>
       </c>
@@ -2146,7 +2158,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="41" spans="1:65" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:65" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
         <v>138</v>
       </c>
@@ -2163,7 +2175,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="42" spans="1:65" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:65" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
         <v>141</v>
       </c>
@@ -2177,7 +2189,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="43" spans="1:65" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:65" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
         <v>141</v>
       </c>
@@ -2191,7 +2203,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="44" spans="1:65" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:65" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
         <v>144</v>
       </c>
@@ -2211,7 +2223,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="45" spans="1:65" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:65" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
         <v>144</v>
       </c>
@@ -2234,7 +2246,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="46" spans="1:65" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:65" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
         <v>147</v>
       </c>
@@ -2251,7 +2263,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="47" spans="1:65" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:65" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
         <v>149</v>
       </c>
@@ -2265,7 +2277,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="48" spans="1:65" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:65" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
         <v>149</v>
       </c>
@@ -2279,7 +2291,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="49" spans="1:64" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:64" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
         <v>152</v>
       </c>
@@ -2296,7 +2308,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="50" spans="1:64" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:64" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
         <v>154</v>
       </c>
@@ -2319,7 +2331,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="51" spans="1:64" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:64" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
         <v>156</v>
       </c>
@@ -2345,13 +2357,13 @@
         <v>69</v>
       </c>
       <c r="BD51" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="BK51" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="52" spans="1:64" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:64" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
         <v>156</v>
       </c>
@@ -2371,7 +2383,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="53" spans="1:64" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:64" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
         <v>159</v>
       </c>
@@ -2403,10 +2415,10 @@
         <v>69</v>
       </c>
       <c r="BD53" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="54" spans="1:64" x14ac:dyDescent="0.35">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="54" spans="1:64" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
         <v>161</v>
       </c>
@@ -2420,7 +2432,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="55" spans="1:64" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:64" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
         <v>163</v>
       </c>
@@ -2467,10 +2479,10 @@
         <v>69</v>
       </c>
       <c r="BD55" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="56" spans="1:64" x14ac:dyDescent="0.35">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="56" spans="1:64" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
         <v>165</v>
       </c>
@@ -2517,10 +2529,10 @@
         <v>69</v>
       </c>
       <c r="BD56" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="57" spans="1:64" x14ac:dyDescent="0.35">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="57" spans="1:64" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
         <v>167</v>
       </c>
@@ -2534,7 +2546,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="58" spans="1:64" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:64" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
         <v>169</v>
       </c>
@@ -2548,7 +2560,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="59" spans="1:64" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:64" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
         <v>169</v>
       </c>
@@ -2562,7 +2574,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="60" spans="1:64" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:64" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
         <v>172</v>
       </c>
@@ -2576,7 +2588,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="61" spans="1:64" x14ac:dyDescent="0.35">
+    <row r="61" spans="1:64" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
         <v>174</v>
       </c>
@@ -2599,7 +2611,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="62" spans="1:64" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:64" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
         <v>176</v>
       </c>
@@ -2613,7 +2625,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="63" spans="1:64" x14ac:dyDescent="0.35">
+    <row r="63" spans="1:64" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
         <v>178</v>
       </c>
@@ -2627,7 +2639,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="64" spans="1:64" x14ac:dyDescent="0.35">
+    <row r="64" spans="1:64" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
         <v>180</v>
       </c>
@@ -2641,7 +2653,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="65" spans="1:65" x14ac:dyDescent="0.35">
+    <row r="65" spans="1:65" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
         <v>180</v>
       </c>
@@ -2655,7 +2667,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="66" spans="1:65" x14ac:dyDescent="0.35">
+    <row r="66" spans="1:65" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
         <v>183</v>
       </c>
@@ -2669,7 +2681,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="67" spans="1:65" x14ac:dyDescent="0.35">
+    <row r="67" spans="1:65" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
         <v>185</v>
       </c>
@@ -2725,10 +2737,10 @@
         <v>69</v>
       </c>
       <c r="BD67" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="68" spans="1:65" x14ac:dyDescent="0.35">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="68" spans="1:65" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
         <v>187</v>
       </c>
@@ -2757,7 +2769,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="69" spans="1:65" x14ac:dyDescent="0.35">
+    <row r="69" spans="1:65" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
         <v>187</v>
       </c>
@@ -2780,7 +2792,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="70" spans="1:65" x14ac:dyDescent="0.35">
+    <row r="70" spans="1:65" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
         <v>190</v>
       </c>
@@ -2794,7 +2806,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="71" spans="1:65" x14ac:dyDescent="0.35">
+    <row r="71" spans="1:65" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
         <v>192</v>
       </c>
@@ -2814,7 +2826,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="72" spans="1:65" x14ac:dyDescent="0.35">
+    <row r="72" spans="1:65" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
         <v>194</v>
       </c>
@@ -2828,7 +2840,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="73" spans="1:65" x14ac:dyDescent="0.35">
+    <row r="73" spans="1:65" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
         <v>196</v>
       </c>
@@ -2842,7 +2854,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="74" spans="1:65" x14ac:dyDescent="0.35">
+    <row r="74" spans="1:65" x14ac:dyDescent="0.3">
       <c r="A74" t="s">
         <v>196</v>
       </c>
@@ -2862,7 +2874,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="75" spans="1:65" x14ac:dyDescent="0.35">
+    <row r="75" spans="1:65" x14ac:dyDescent="0.3">
       <c r="A75" t="s">
         <v>199</v>
       </c>
@@ -2876,7 +2888,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="76" spans="1:65" x14ac:dyDescent="0.35">
+    <row r="76" spans="1:65" x14ac:dyDescent="0.3">
       <c r="A76" t="s">
         <v>201</v>
       </c>
@@ -2896,7 +2908,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="77" spans="1:65" x14ac:dyDescent="0.35">
+    <row r="77" spans="1:65" x14ac:dyDescent="0.3">
       <c r="A77" t="s">
         <v>203</v>
       </c>
@@ -2913,7 +2925,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="78" spans="1:65" x14ac:dyDescent="0.35">
+    <row r="78" spans="1:65" x14ac:dyDescent="0.3">
       <c r="A78" t="s">
         <v>205</v>
       </c>
@@ -2927,7 +2939,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="79" spans="1:65" x14ac:dyDescent="0.35">
+    <row r="79" spans="1:65" x14ac:dyDescent="0.3">
       <c r="A79" t="s">
         <v>207</v>
       </c>
@@ -2941,7 +2953,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="80" spans="1:65" x14ac:dyDescent="0.35">
+    <row r="80" spans="1:65" x14ac:dyDescent="0.3">
       <c r="A80" t="s">
         <v>209</v>
       </c>
@@ -2955,7 +2967,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="81" spans="1:64" x14ac:dyDescent="0.35">
+    <row r="81" spans="1:64" x14ac:dyDescent="0.3">
       <c r="A81" t="s">
         <v>65</v>
       </c>
@@ -2975,7 +2987,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="82" spans="1:64" x14ac:dyDescent="0.35">
+    <row r="82" spans="1:64" x14ac:dyDescent="0.3">
       <c r="A82" t="s">
         <v>70</v>
       </c>
@@ -3010,7 +3022,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="83" spans="1:64" x14ac:dyDescent="0.35">
+    <row r="83" spans="1:64" x14ac:dyDescent="0.3">
       <c r="A83" t="s">
         <v>72</v>
       </c>
@@ -3032,8 +3044,11 @@
       <c r="AT83" t="s">
         <v>69</v>
       </c>
-    </row>
-    <row r="84" spans="1:64" x14ac:dyDescent="0.35">
+      <c r="BD83" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="84" spans="1:64" x14ac:dyDescent="0.3">
       <c r="A84" t="s">
         <v>74</v>
       </c>
@@ -3047,7 +3062,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="85" spans="1:64" x14ac:dyDescent="0.35">
+    <row r="85" spans="1:64" x14ac:dyDescent="0.3">
       <c r="A85" t="s">
         <v>76</v>
       </c>
@@ -3067,7 +3082,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="86" spans="1:64" x14ac:dyDescent="0.35">
+    <row r="86" spans="1:64" x14ac:dyDescent="0.3">
       <c r="A86" t="s">
         <v>78</v>
       </c>
@@ -3084,7 +3099,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="87" spans="1:64" x14ac:dyDescent="0.35">
+    <row r="87" spans="1:64" x14ac:dyDescent="0.3">
       <c r="A87" t="s">
         <v>212</v>
       </c>
@@ -3101,7 +3116,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="88" spans="1:64" x14ac:dyDescent="0.35">
+    <row r="88" spans="1:64" x14ac:dyDescent="0.3">
       <c r="A88" t="s">
         <v>214</v>
       </c>
@@ -3118,7 +3133,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="89" spans="1:64" x14ac:dyDescent="0.35">
+    <row r="89" spans="1:64" x14ac:dyDescent="0.3">
       <c r="A89" t="s">
         <v>214</v>
       </c>
@@ -3141,7 +3156,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="90" spans="1:64" x14ac:dyDescent="0.35">
+    <row r="90" spans="1:64" x14ac:dyDescent="0.3">
       <c r="A90" t="s">
         <v>217</v>
       </c>
@@ -3202,6 +3217,9 @@
       <c r="BA90" t="s">
         <v>69</v>
       </c>
+      <c r="BD90" t="s">
+        <v>69</v>
+      </c>
       <c r="BG90" t="s">
         <v>68</v>
       </c>
@@ -3212,7 +3230,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="91" spans="1:64" x14ac:dyDescent="0.35">
+    <row r="91" spans="1:64" x14ac:dyDescent="0.3">
       <c r="A91" t="s">
         <v>81</v>
       </c>
@@ -3273,6 +3291,9 @@
       <c r="BA91" t="s">
         <v>69</v>
       </c>
+      <c r="BD91" t="s">
+        <v>69</v>
+      </c>
       <c r="BF91" t="s">
         <v>69</v>
       </c>
@@ -3286,7 +3307,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="92" spans="1:64" x14ac:dyDescent="0.35">
+    <row r="92" spans="1:64" x14ac:dyDescent="0.3">
       <c r="A92" t="s">
         <v>83</v>
       </c>
@@ -3347,6 +3368,9 @@
       <c r="BA92" t="s">
         <v>69</v>
       </c>
+      <c r="BD92" t="s">
+        <v>69</v>
+      </c>
       <c r="BG92" t="s">
         <v>68</v>
       </c>
@@ -3357,7 +3381,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="93" spans="1:64" x14ac:dyDescent="0.35">
+    <row r="93" spans="1:64" x14ac:dyDescent="0.3">
       <c r="A93" t="s">
         <v>85</v>
       </c>
@@ -3371,7 +3395,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="94" spans="1:64" x14ac:dyDescent="0.35">
+    <row r="94" spans="1:64" x14ac:dyDescent="0.3">
       <c r="A94" t="s">
         <v>87</v>
       </c>
@@ -3385,7 +3409,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="95" spans="1:64" x14ac:dyDescent="0.35">
+    <row r="95" spans="1:64" x14ac:dyDescent="0.3">
       <c r="A95" t="s">
         <v>89</v>
       </c>
@@ -3402,7 +3426,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="96" spans="1:64" x14ac:dyDescent="0.35">
+    <row r="96" spans="1:64" x14ac:dyDescent="0.3">
       <c r="A96" t="s">
         <v>89</v>
       </c>
@@ -3419,7 +3443,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="97" spans="1:60" x14ac:dyDescent="0.35">
+    <row r="97" spans="1:60" x14ac:dyDescent="0.3">
       <c r="A97" t="s">
         <v>91</v>
       </c>
@@ -3433,7 +3457,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="98" spans="1:60" x14ac:dyDescent="0.35">
+    <row r="98" spans="1:60" x14ac:dyDescent="0.3">
       <c r="A98" t="s">
         <v>91</v>
       </c>
@@ -3459,7 +3483,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="99" spans="1:60" x14ac:dyDescent="0.35">
+    <row r="99" spans="1:60" x14ac:dyDescent="0.3">
       <c r="A99" t="s">
         <v>220</v>
       </c>
@@ -3476,7 +3500,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="100" spans="1:60" x14ac:dyDescent="0.35">
+    <row r="100" spans="1:60" x14ac:dyDescent="0.3">
       <c r="A100" t="s">
         <v>222</v>
       </c>
@@ -3496,7 +3520,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="101" spans="1:60" x14ac:dyDescent="0.35">
+    <row r="101" spans="1:60" x14ac:dyDescent="0.3">
       <c r="A101" t="s">
         <v>94</v>
       </c>
@@ -3513,7 +3537,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="102" spans="1:60" x14ac:dyDescent="0.35">
+    <row r="102" spans="1:60" x14ac:dyDescent="0.3">
       <c r="A102" t="s">
         <v>96</v>
       </c>
@@ -3530,7 +3554,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="103" spans="1:60" x14ac:dyDescent="0.35">
+    <row r="103" spans="1:60" x14ac:dyDescent="0.3">
       <c r="A103" t="s">
         <v>98</v>
       </c>
@@ -3544,7 +3568,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="104" spans="1:60" x14ac:dyDescent="0.35">
+    <row r="104" spans="1:60" x14ac:dyDescent="0.3">
       <c r="A104" t="s">
         <v>100</v>
       </c>
@@ -3587,8 +3611,11 @@
       <c r="BA104" t="s">
         <v>69</v>
       </c>
-    </row>
-    <row r="105" spans="1:60" x14ac:dyDescent="0.35">
+      <c r="BD104" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="105" spans="1:60" x14ac:dyDescent="0.3">
       <c r="A105" t="s">
         <v>102</v>
       </c>
@@ -3608,7 +3635,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="106" spans="1:60" x14ac:dyDescent="0.35">
+    <row r="106" spans="1:60" x14ac:dyDescent="0.3">
       <c r="A106" t="s">
         <v>102</v>
       </c>
@@ -3628,7 +3655,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="107" spans="1:60" x14ac:dyDescent="0.35">
+    <row r="107" spans="1:60" x14ac:dyDescent="0.3">
       <c r="A107" t="s">
         <v>225</v>
       </c>
@@ -3642,7 +3669,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="108" spans="1:60" x14ac:dyDescent="0.35">
+    <row r="108" spans="1:60" x14ac:dyDescent="0.3">
       <c r="A108" t="s">
         <v>104</v>
       </c>
@@ -3662,7 +3689,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="109" spans="1:60" x14ac:dyDescent="0.35">
+    <row r="109" spans="1:60" x14ac:dyDescent="0.3">
       <c r="A109" t="s">
         <v>104</v>
       </c>
@@ -3676,7 +3703,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="110" spans="1:60" x14ac:dyDescent="0.35">
+    <row r="110" spans="1:60" x14ac:dyDescent="0.3">
       <c r="A110" t="s">
         <v>107</v>
       </c>
@@ -3696,7 +3723,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="111" spans="1:60" x14ac:dyDescent="0.35">
+    <row r="111" spans="1:60" x14ac:dyDescent="0.3">
       <c r="A111" t="s">
         <v>109</v>
       </c>
@@ -3716,7 +3743,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="112" spans="1:60" x14ac:dyDescent="0.35">
+    <row r="112" spans="1:60" x14ac:dyDescent="0.3">
       <c r="A112" t="s">
         <v>111</v>
       </c>
@@ -3733,7 +3760,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="113" spans="1:59" x14ac:dyDescent="0.35">
+    <row r="113" spans="1:59" x14ac:dyDescent="0.3">
       <c r="A113" t="s">
         <v>113</v>
       </c>
@@ -3753,7 +3780,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="114" spans="1:59" x14ac:dyDescent="0.35">
+    <row r="114" spans="1:59" x14ac:dyDescent="0.3">
       <c r="A114" t="s">
         <v>115</v>
       </c>
@@ -3767,7 +3794,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="115" spans="1:59" x14ac:dyDescent="0.35">
+    <row r="115" spans="1:59" x14ac:dyDescent="0.3">
       <c r="A115" t="s">
         <v>115</v>
       </c>
@@ -3781,7 +3808,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="116" spans="1:59" x14ac:dyDescent="0.35">
+    <row r="116" spans="1:59" x14ac:dyDescent="0.3">
       <c r="A116" t="s">
         <v>117</v>
       </c>
@@ -3801,7 +3828,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="117" spans="1:59" x14ac:dyDescent="0.35">
+    <row r="117" spans="1:59" x14ac:dyDescent="0.3">
       <c r="A117" t="s">
         <v>117</v>
       </c>
@@ -3821,7 +3848,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="118" spans="1:59" x14ac:dyDescent="0.35">
+    <row r="118" spans="1:59" x14ac:dyDescent="0.3">
       <c r="A118" t="s">
         <v>120</v>
       </c>
@@ -3835,7 +3862,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="119" spans="1:59" x14ac:dyDescent="0.35">
+    <row r="119" spans="1:59" x14ac:dyDescent="0.3">
       <c r="A119" t="s">
         <v>120</v>
       </c>
@@ -3861,7 +3888,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="120" spans="1:59" x14ac:dyDescent="0.35">
+    <row r="120" spans="1:59" x14ac:dyDescent="0.3">
       <c r="A120" t="s">
         <v>124</v>
       </c>
@@ -3887,7 +3914,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="121" spans="1:59" x14ac:dyDescent="0.35">
+    <row r="121" spans="1:59" x14ac:dyDescent="0.3">
       <c r="A121" t="s">
         <v>127</v>
       </c>
@@ -3910,7 +3937,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="122" spans="1:59" x14ac:dyDescent="0.35">
+    <row r="122" spans="1:59" x14ac:dyDescent="0.3">
       <c r="A122" t="s">
         <v>127</v>
       </c>
@@ -3933,7 +3960,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="123" spans="1:59" x14ac:dyDescent="0.35">
+    <row r="123" spans="1:59" x14ac:dyDescent="0.3">
       <c r="A123" t="s">
         <v>130</v>
       </c>
@@ -3956,7 +3983,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="124" spans="1:59" x14ac:dyDescent="0.35">
+    <row r="124" spans="1:59" x14ac:dyDescent="0.3">
       <c r="A124" t="s">
         <v>132</v>
       </c>
@@ -3976,7 +4003,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="125" spans="1:59" x14ac:dyDescent="0.35">
+    <row r="125" spans="1:59" x14ac:dyDescent="0.3">
       <c r="A125" t="s">
         <v>132</v>
       </c>
@@ -3993,7 +4020,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="126" spans="1:59" x14ac:dyDescent="0.35">
+    <row r="126" spans="1:59" x14ac:dyDescent="0.3">
       <c r="A126" t="s">
         <v>132</v>
       </c>
@@ -4010,7 +4037,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="127" spans="1:59" x14ac:dyDescent="0.35">
+    <row r="127" spans="1:59" x14ac:dyDescent="0.3">
       <c r="A127" t="s">
         <v>136</v>
       </c>
@@ -4033,7 +4060,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="128" spans="1:59" x14ac:dyDescent="0.35">
+    <row r="128" spans="1:59" x14ac:dyDescent="0.3">
       <c r="A128" t="s">
         <v>138</v>
       </c>
@@ -4053,7 +4080,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="129" spans="1:59" x14ac:dyDescent="0.35">
+    <row r="129" spans="1:59" x14ac:dyDescent="0.3">
       <c r="A129" t="s">
         <v>138</v>
       </c>
@@ -4076,7 +4103,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="130" spans="1:59" x14ac:dyDescent="0.35">
+    <row r="130" spans="1:59" x14ac:dyDescent="0.3">
       <c r="A130" t="s">
         <v>141</v>
       </c>
@@ -4090,7 +4117,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="131" spans="1:59" x14ac:dyDescent="0.35">
+    <row r="131" spans="1:59" x14ac:dyDescent="0.3">
       <c r="A131" t="s">
         <v>144</v>
       </c>
@@ -4104,7 +4131,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="132" spans="1:59" x14ac:dyDescent="0.35">
+    <row r="132" spans="1:59" x14ac:dyDescent="0.3">
       <c r="A132" t="s">
         <v>144</v>
       </c>
@@ -4133,7 +4160,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="133" spans="1:59" x14ac:dyDescent="0.35">
+    <row r="133" spans="1:59" x14ac:dyDescent="0.3">
       <c r="A133" t="s">
         <v>228</v>
       </c>
@@ -4150,7 +4177,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="134" spans="1:59" x14ac:dyDescent="0.35">
+    <row r="134" spans="1:59" x14ac:dyDescent="0.3">
       <c r="A134" t="s">
         <v>230</v>
       </c>
@@ -4164,7 +4191,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="135" spans="1:59" x14ac:dyDescent="0.35">
+    <row r="135" spans="1:59" x14ac:dyDescent="0.3">
       <c r="A135" t="s">
         <v>232</v>
       </c>
@@ -4181,7 +4208,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="136" spans="1:59" x14ac:dyDescent="0.35">
+    <row r="136" spans="1:59" x14ac:dyDescent="0.3">
       <c r="A136" t="s">
         <v>234</v>
       </c>
@@ -4198,7 +4225,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="137" spans="1:59" x14ac:dyDescent="0.35">
+    <row r="137" spans="1:59" x14ac:dyDescent="0.3">
       <c r="A137" t="s">
         <v>234</v>
       </c>
@@ -4218,7 +4245,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="138" spans="1:59" x14ac:dyDescent="0.35">
+    <row r="138" spans="1:59" x14ac:dyDescent="0.3">
       <c r="A138" t="s">
         <v>237</v>
       </c>
@@ -4232,7 +4259,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="139" spans="1:59" x14ac:dyDescent="0.35">
+    <row r="139" spans="1:59" x14ac:dyDescent="0.3">
       <c r="A139" t="s">
         <v>154</v>
       </c>
@@ -4246,7 +4273,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="140" spans="1:59" x14ac:dyDescent="0.35">
+    <row r="140" spans="1:59" x14ac:dyDescent="0.3">
       <c r="A140" t="s">
         <v>240</v>
       </c>
@@ -4260,7 +4287,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="141" spans="1:59" x14ac:dyDescent="0.35">
+    <row r="141" spans="1:59" x14ac:dyDescent="0.3">
       <c r="A141" t="s">
         <v>242</v>
       </c>
@@ -4274,7 +4301,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="142" spans="1:59" x14ac:dyDescent="0.35">
+    <row r="142" spans="1:59" x14ac:dyDescent="0.3">
       <c r="A142" t="s">
         <v>156</v>
       </c>
@@ -4303,10 +4330,10 @@
         <v>69</v>
       </c>
       <c r="BD142" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="143" spans="1:59" x14ac:dyDescent="0.35">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="143" spans="1:59" x14ac:dyDescent="0.3">
       <c r="A143" t="s">
         <v>156</v>
       </c>
@@ -4323,7 +4350,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="144" spans="1:59" x14ac:dyDescent="0.35">
+    <row r="144" spans="1:59" x14ac:dyDescent="0.3">
       <c r="A144" t="s">
         <v>159</v>
       </c>
@@ -4352,10 +4379,10 @@
         <v>69</v>
       </c>
       <c r="BD144" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="145" spans="1:56" x14ac:dyDescent="0.35">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="145" spans="1:56" x14ac:dyDescent="0.3">
       <c r="A145" t="s">
         <v>244</v>
       </c>
@@ -4423,10 +4450,10 @@
         <v>69</v>
       </c>
       <c r="BD145" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="146" spans="1:56" x14ac:dyDescent="0.35">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="146" spans="1:56" x14ac:dyDescent="0.3">
       <c r="A146" t="s">
         <v>163</v>
       </c>
@@ -4497,10 +4524,10 @@
         <v>69</v>
       </c>
       <c r="BD146" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="147" spans="1:56" x14ac:dyDescent="0.35">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="147" spans="1:56" x14ac:dyDescent="0.3">
       <c r="A147" t="s">
         <v>165</v>
       </c>
@@ -4565,10 +4592,10 @@
         <v>69</v>
       </c>
       <c r="BD147" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="148" spans="1:56" x14ac:dyDescent="0.35">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="148" spans="1:56" x14ac:dyDescent="0.3">
       <c r="A148" t="s">
         <v>167</v>
       </c>
@@ -4582,7 +4609,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="149" spans="1:56" x14ac:dyDescent="0.35">
+    <row r="149" spans="1:56" x14ac:dyDescent="0.3">
       <c r="A149" t="s">
         <v>167</v>
       </c>
@@ -4602,7 +4629,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="150" spans="1:56" x14ac:dyDescent="0.35">
+    <row r="150" spans="1:56" x14ac:dyDescent="0.3">
       <c r="A150" t="s">
         <v>169</v>
       </c>
@@ -4619,7 +4646,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="151" spans="1:56" x14ac:dyDescent="0.35">
+    <row r="151" spans="1:56" x14ac:dyDescent="0.3">
       <c r="A151" t="s">
         <v>169</v>
       </c>
@@ -4636,7 +4663,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="152" spans="1:56" x14ac:dyDescent="0.35">
+    <row r="152" spans="1:56" x14ac:dyDescent="0.3">
       <c r="A152" t="s">
         <v>172</v>
       </c>
@@ -4650,7 +4677,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="153" spans="1:56" x14ac:dyDescent="0.35">
+    <row r="153" spans="1:56" x14ac:dyDescent="0.3">
       <c r="A153" t="s">
         <v>247</v>
       </c>
@@ -4667,7 +4694,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="154" spans="1:56" x14ac:dyDescent="0.35">
+    <row r="154" spans="1:56" x14ac:dyDescent="0.3">
       <c r="A154" t="s">
         <v>176</v>
       </c>
@@ -4684,7 +4711,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="155" spans="1:56" x14ac:dyDescent="0.35">
+    <row r="155" spans="1:56" x14ac:dyDescent="0.3">
       <c r="A155" t="s">
         <v>176</v>
       </c>
@@ -4698,7 +4725,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="156" spans="1:56" x14ac:dyDescent="0.35">
+    <row r="156" spans="1:56" x14ac:dyDescent="0.3">
       <c r="A156" t="s">
         <v>178</v>
       </c>
@@ -4718,7 +4745,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="157" spans="1:56" x14ac:dyDescent="0.35">
+    <row r="157" spans="1:56" x14ac:dyDescent="0.3">
       <c r="A157" t="s">
         <v>180</v>
       </c>
@@ -4732,7 +4759,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="158" spans="1:56" x14ac:dyDescent="0.35">
+    <row r="158" spans="1:56" x14ac:dyDescent="0.3">
       <c r="A158" t="s">
         <v>180</v>
       </c>
@@ -4746,7 +4773,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="159" spans="1:56" x14ac:dyDescent="0.35">
+    <row r="159" spans="1:56" x14ac:dyDescent="0.3">
       <c r="A159" t="s">
         <v>183</v>
       </c>
@@ -4760,7 +4787,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="160" spans="1:56" x14ac:dyDescent="0.35">
+    <row r="160" spans="1:56" x14ac:dyDescent="0.3">
       <c r="A160" t="s">
         <v>185</v>
       </c>
@@ -4798,10 +4825,10 @@
         <v>69</v>
       </c>
       <c r="BD160" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="161" spans="1:59" x14ac:dyDescent="0.35">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="161" spans="1:59" x14ac:dyDescent="0.3">
       <c r="A161" t="s">
         <v>187</v>
       </c>
@@ -4836,7 +4863,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="162" spans="1:59" x14ac:dyDescent="0.35">
+    <row r="162" spans="1:59" x14ac:dyDescent="0.3">
       <c r="A162" t="s">
         <v>187</v>
       </c>
@@ -4853,7 +4880,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="163" spans="1:59" x14ac:dyDescent="0.35">
+    <row r="163" spans="1:59" x14ac:dyDescent="0.3">
       <c r="A163" t="s">
         <v>192</v>
       </c>
@@ -4867,7 +4894,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="164" spans="1:59" x14ac:dyDescent="0.35">
+    <row r="164" spans="1:59" x14ac:dyDescent="0.3">
       <c r="A164" t="s">
         <v>192</v>
       </c>
@@ -4887,7 +4914,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="165" spans="1:59" x14ac:dyDescent="0.35">
+    <row r="165" spans="1:59" x14ac:dyDescent="0.3">
       <c r="A165" t="s">
         <v>196</v>
       </c>
@@ -4901,7 +4928,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="166" spans="1:59" x14ac:dyDescent="0.35">
+    <row r="166" spans="1:59" x14ac:dyDescent="0.3">
       <c r="A166" t="s">
         <v>196</v>
       </c>
@@ -4918,7 +4945,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="167" spans="1:59" x14ac:dyDescent="0.35">
+    <row r="167" spans="1:59" x14ac:dyDescent="0.3">
       <c r="A167" t="s">
         <v>201</v>
       </c>
@@ -4944,7 +4971,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="168" spans="1:59" x14ac:dyDescent="0.35">
+    <row r="168" spans="1:59" x14ac:dyDescent="0.3">
       <c r="A168" t="s">
         <v>203</v>
       </c>
@@ -4964,7 +4991,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="169" spans="1:59" x14ac:dyDescent="0.35">
+    <row r="169" spans="1:59" x14ac:dyDescent="0.3">
       <c r="A169" t="s">
         <v>207</v>
       </c>
@@ -4984,7 +5011,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="170" spans="1:59" x14ac:dyDescent="0.35">
+    <row r="170" spans="1:59" x14ac:dyDescent="0.3">
       <c r="A170" t="s">
         <v>207</v>
       </c>
@@ -5010,7 +5037,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="171" spans="1:59" x14ac:dyDescent="0.35">
+    <row r="171" spans="1:59" x14ac:dyDescent="0.3">
       <c r="A171" t="s">
         <v>252</v>
       </c>
@@ -5027,7 +5054,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="172" spans="1:59" x14ac:dyDescent="0.35">
+    <row r="172" spans="1:59" x14ac:dyDescent="0.3">
       <c r="A172" t="s">
         <v>209</v>
       </c>
@@ -5053,7 +5080,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="173" spans="1:59" x14ac:dyDescent="0.35">
+    <row r="173" spans="1:59" x14ac:dyDescent="0.3">
       <c r="A173" t="s">
         <v>254</v>
       </c>

--- a/html/Specialsystemer_excel.XLSX
+++ b/html/Specialsystemer_excel.XLSX
@@ -5,18 +5,18 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Documents\GitHub\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{44D18BD5-4405-4503-9044-43BE6B3206D7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{19289F87-737A-451D-8ACD-FAAAC9A3F79F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1440" yWindow="1632" windowWidth="21600" windowHeight="11232" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="780" yWindow="780" windowWidth="21600" windowHeight="11175" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 14-09-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 17-09-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Specialsystemer">'Opdateret d. 14-09-2026'!$A$1:$BM$173</definedName>
+    <definedName name="Specialsystemer">'Opdateret d. 17-09-2026'!$A$1:$BM$173</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>
@@ -1134,9 +1134,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:BM173"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:65" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1333,7 +1333,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="2" spans="1:65" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>65</v>
       </c>
@@ -1353,7 +1353,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="3" spans="1:65" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>70</v>
       </c>
@@ -1373,7 +1373,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="4" spans="1:65" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>72</v>
       </c>
@@ -1408,7 +1408,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="5" spans="1:65" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>74</v>
       </c>
@@ -1425,7 +1425,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="6" spans="1:65" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>76</v>
       </c>
@@ -1445,7 +1445,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="7" spans="1:65" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>78</v>
       </c>
@@ -1462,7 +1462,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="8" spans="1:65" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>81</v>
       </c>
@@ -1530,7 +1530,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="9" spans="1:65" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>83</v>
       </c>
@@ -1583,7 +1583,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="10" spans="1:65" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>85</v>
       </c>
@@ -1597,7 +1597,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="11" spans="1:65" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>87</v>
       </c>
@@ -1611,7 +1611,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="12" spans="1:65" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>89</v>
       </c>
@@ -1625,7 +1625,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="13" spans="1:65" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>91</v>
       </c>
@@ -1639,7 +1639,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="14" spans="1:65" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>91</v>
       </c>
@@ -1653,7 +1653,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="15" spans="1:65" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>94</v>
       </c>
@@ -1667,7 +1667,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="16" spans="1:65" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>96</v>
       </c>
@@ -1681,7 +1681,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="17" spans="1:65" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>98</v>
       </c>
@@ -1695,7 +1695,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="18" spans="1:65" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>100</v>
       </c>
@@ -1754,7 +1754,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="19" spans="1:65" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>102</v>
       </c>
@@ -1768,7 +1768,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="20" spans="1:65" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>104</v>
       </c>
@@ -1791,7 +1791,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="21" spans="1:65" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>104</v>
       </c>
@@ -1805,7 +1805,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="22" spans="1:65" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>107</v>
       </c>
@@ -1819,7 +1819,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="23" spans="1:65" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>109</v>
       </c>
@@ -1833,7 +1833,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="24" spans="1:65" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>111</v>
       </c>
@@ -1850,7 +1850,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="25" spans="1:65" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>113</v>
       </c>
@@ -1864,7 +1864,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="26" spans="1:65" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>115</v>
       </c>
@@ -1881,7 +1881,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="27" spans="1:65" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>117</v>
       </c>
@@ -1910,7 +1910,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="28" spans="1:65" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>117</v>
       </c>
@@ -1936,7 +1936,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="29" spans="1:65" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>120</v>
       </c>
@@ -1953,7 +1953,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="30" spans="1:65" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>120</v>
       </c>
@@ -1979,7 +1979,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="31" spans="1:65" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>124</v>
       </c>
@@ -1993,7 +1993,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="32" spans="1:65" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>124</v>
       </c>
@@ -2016,7 +2016,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="33" spans="1:65" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>127</v>
       </c>
@@ -2036,7 +2036,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="34" spans="1:65" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>127</v>
       </c>
@@ -2056,7 +2056,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="35" spans="1:65" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>130</v>
       </c>
@@ -2076,7 +2076,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="36" spans="1:65" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>132</v>
       </c>
@@ -2093,7 +2093,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="37" spans="1:65" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>132</v>
       </c>
@@ -2107,7 +2107,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="38" spans="1:65" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>132</v>
       </c>
@@ -2121,7 +2121,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="39" spans="1:65" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>136</v>
       </c>
@@ -2141,7 +2141,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="40" spans="1:65" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>138</v>
       </c>
@@ -2158,7 +2158,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="41" spans="1:65" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>138</v>
       </c>
@@ -2175,7 +2175,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="42" spans="1:65" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>141</v>
       </c>
@@ -2189,7 +2189,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="43" spans="1:65" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>141</v>
       </c>
@@ -2203,7 +2203,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="44" spans="1:65" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>144</v>
       </c>
@@ -2223,7 +2223,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="45" spans="1:65" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>144</v>
       </c>
@@ -2246,7 +2246,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="46" spans="1:65" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>147</v>
       </c>
@@ -2263,7 +2263,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="47" spans="1:65" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
         <v>149</v>
       </c>
@@ -2277,7 +2277,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="48" spans="1:65" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
         <v>149</v>
       </c>
@@ -2291,7 +2291,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="49" spans="1:64" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:64" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
         <v>152</v>
       </c>
@@ -2308,7 +2308,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="50" spans="1:64" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:64" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
         <v>154</v>
       </c>
@@ -2331,7 +2331,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="51" spans="1:64" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:64" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
         <v>156</v>
       </c>
@@ -2363,7 +2363,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="52" spans="1:64" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:64" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
         <v>156</v>
       </c>
@@ -2383,7 +2383,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="53" spans="1:64" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:64" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
         <v>159</v>
       </c>
@@ -2418,7 +2418,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="54" spans="1:64" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:64" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
         <v>161</v>
       </c>
@@ -2432,7 +2432,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="55" spans="1:64" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:64" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
         <v>163</v>
       </c>
@@ -2482,7 +2482,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="56" spans="1:64" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:64" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
         <v>165</v>
       </c>
@@ -2532,7 +2532,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="57" spans="1:64" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:64" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
         <v>167</v>
       </c>
@@ -2546,7 +2546,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="58" spans="1:64" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:64" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
         <v>169</v>
       </c>
@@ -2560,7 +2560,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="59" spans="1:64" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:64" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
         <v>169</v>
       </c>
@@ -2574,7 +2574,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="60" spans="1:64" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:64" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
         <v>172</v>
       </c>
@@ -2588,7 +2588,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="61" spans="1:64" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:64" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
         <v>174</v>
       </c>
@@ -2611,7 +2611,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="62" spans="1:64" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:64" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
         <v>176</v>
       </c>
@@ -2625,7 +2625,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="63" spans="1:64" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:64" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
         <v>178</v>
       </c>
@@ -2639,7 +2639,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="64" spans="1:64" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:64" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
         <v>180</v>
       </c>
@@ -2653,7 +2653,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="65" spans="1:65" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
         <v>180</v>
       </c>
@@ -2667,7 +2667,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="66" spans="1:65" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
         <v>183</v>
       </c>
@@ -2681,7 +2681,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="67" spans="1:65" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
         <v>185</v>
       </c>
@@ -2740,7 +2740,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="68" spans="1:65" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
         <v>187</v>
       </c>
@@ -2769,7 +2769,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="69" spans="1:65" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
         <v>187</v>
       </c>
@@ -2792,7 +2792,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="70" spans="1:65" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
         <v>190</v>
       </c>
@@ -2806,7 +2806,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="71" spans="1:65" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
         <v>192</v>
       </c>
@@ -2826,7 +2826,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="72" spans="1:65" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
         <v>194</v>
       </c>
@@ -2840,7 +2840,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="73" spans="1:65" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
         <v>196</v>
       </c>
@@ -2854,7 +2854,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="74" spans="1:65" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
         <v>196</v>
       </c>
@@ -2874,7 +2874,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="75" spans="1:65" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
         <v>199</v>
       </c>
@@ -2888,7 +2888,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="76" spans="1:65" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
         <v>201</v>
       </c>
@@ -2908,7 +2908,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="77" spans="1:65" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
         <v>203</v>
       </c>
@@ -2925,7 +2925,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="78" spans="1:65" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
         <v>205</v>
       </c>
@@ -2939,7 +2939,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="79" spans="1:65" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
         <v>207</v>
       </c>
@@ -2953,7 +2953,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="80" spans="1:65" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
         <v>209</v>
       </c>
@@ -2967,7 +2967,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="81" spans="1:64" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:64" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
         <v>65</v>
       </c>
@@ -2987,7 +2987,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="82" spans="1:64" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:64" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
         <v>70</v>
       </c>
@@ -3022,7 +3022,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="83" spans="1:64" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:64" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
         <v>72</v>
       </c>
@@ -3048,7 +3048,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="84" spans="1:64" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:64" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
         <v>74</v>
       </c>
@@ -3062,7 +3062,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="85" spans="1:64" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:64" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
         <v>76</v>
       </c>
@@ -3082,7 +3082,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="86" spans="1:64" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:64" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
         <v>78</v>
       </c>
@@ -3099,7 +3099,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="87" spans="1:64" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:64" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
         <v>212</v>
       </c>
@@ -3116,7 +3116,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="88" spans="1:64" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:64" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
         <v>214</v>
       </c>
@@ -3133,7 +3133,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="89" spans="1:64" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:64" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
         <v>214</v>
       </c>
@@ -3156,7 +3156,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="90" spans="1:64" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:64" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
         <v>217</v>
       </c>
@@ -3230,7 +3230,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="91" spans="1:64" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:64" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
         <v>81</v>
       </c>
@@ -3307,7 +3307,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="92" spans="1:64" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:64" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
         <v>83</v>
       </c>
@@ -3381,7 +3381,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="93" spans="1:64" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:64" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
         <v>85</v>
       </c>
@@ -3395,7 +3395,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="94" spans="1:64" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:64" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
         <v>87</v>
       </c>
@@ -3409,7 +3409,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="95" spans="1:64" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:64" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
         <v>89</v>
       </c>
@@ -3426,7 +3426,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="96" spans="1:64" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:64" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
         <v>89</v>
       </c>
@@ -3443,7 +3443,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="97" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:60" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
         <v>91</v>
       </c>
@@ -3457,7 +3457,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="98" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:60" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
         <v>91</v>
       </c>
@@ -3483,7 +3483,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="99" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:60" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
         <v>220</v>
       </c>
@@ -3500,7 +3500,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="100" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:60" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
         <v>222</v>
       </c>
@@ -3520,7 +3520,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="101" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:60" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
         <v>94</v>
       </c>
@@ -3537,7 +3537,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="102" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:60" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
         <v>96</v>
       </c>
@@ -3554,7 +3554,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="103" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:60" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
         <v>98</v>
       </c>
@@ -3568,7 +3568,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="104" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:60" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
         <v>100</v>
       </c>
@@ -3615,7 +3615,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="105" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:60" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
         <v>102</v>
       </c>
@@ -3635,7 +3635,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="106" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:60" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
         <v>102</v>
       </c>
@@ -3655,7 +3655,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="107" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:60" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
         <v>225</v>
       </c>
@@ -3669,7 +3669,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="108" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:60" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
         <v>104</v>
       </c>
@@ -3689,7 +3689,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="109" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:60" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
         <v>104</v>
       </c>
@@ -3703,7 +3703,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="110" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:60" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
         <v>107</v>
       </c>
@@ -3723,7 +3723,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="111" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:60" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
         <v>109</v>
       </c>
@@ -3743,7 +3743,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="112" spans="1:60" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:60" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
         <v>111</v>
       </c>
@@ -3760,7 +3760,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="113" spans="1:59" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:59" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
         <v>113</v>
       </c>
@@ -3780,7 +3780,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="114" spans="1:59" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:59" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
         <v>115</v>
       </c>
@@ -3794,7 +3794,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="115" spans="1:59" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:59" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
         <v>115</v>
       </c>
@@ -3808,7 +3808,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="116" spans="1:59" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:59" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
         <v>117</v>
       </c>
@@ -3828,7 +3828,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="117" spans="1:59" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:59" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
         <v>117</v>
       </c>
@@ -3848,7 +3848,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="118" spans="1:59" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:59" x14ac:dyDescent="0.25">
       <c r="A118" t="s">
         <v>120</v>
       </c>
@@ -3862,7 +3862,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="119" spans="1:59" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:59" x14ac:dyDescent="0.25">
       <c r="A119" t="s">
         <v>120</v>
       </c>
@@ -3888,7 +3888,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="120" spans="1:59" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:59" x14ac:dyDescent="0.25">
       <c r="A120" t="s">
         <v>124</v>
       </c>
@@ -3914,7 +3914,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="121" spans="1:59" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:59" x14ac:dyDescent="0.25">
       <c r="A121" t="s">
         <v>127</v>
       </c>
@@ -3937,7 +3937,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="122" spans="1:59" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:59" x14ac:dyDescent="0.25">
       <c r="A122" t="s">
         <v>127</v>
       </c>
@@ -3960,7 +3960,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="123" spans="1:59" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:59" x14ac:dyDescent="0.25">
       <c r="A123" t="s">
         <v>130</v>
       </c>
@@ -3983,7 +3983,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="124" spans="1:59" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:59" x14ac:dyDescent="0.25">
       <c r="A124" t="s">
         <v>132</v>
       </c>
@@ -4003,7 +4003,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="125" spans="1:59" x14ac:dyDescent="0.3">
+    <row r="125" spans="1:59" x14ac:dyDescent="0.25">
       <c r="A125" t="s">
         <v>132</v>
       </c>
@@ -4020,7 +4020,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="126" spans="1:59" x14ac:dyDescent="0.3">
+    <row r="126" spans="1:59" x14ac:dyDescent="0.25">
       <c r="A126" t="s">
         <v>132</v>
       </c>
@@ -4037,7 +4037,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="127" spans="1:59" x14ac:dyDescent="0.3">
+    <row r="127" spans="1:59" x14ac:dyDescent="0.25">
       <c r="A127" t="s">
         <v>136</v>
       </c>
@@ -4060,7 +4060,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="128" spans="1:59" x14ac:dyDescent="0.3">
+    <row r="128" spans="1:59" x14ac:dyDescent="0.25">
       <c r="A128" t="s">
         <v>138</v>
       </c>
@@ -4080,7 +4080,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="129" spans="1:59" x14ac:dyDescent="0.3">
+    <row r="129" spans="1:59" x14ac:dyDescent="0.25">
       <c r="A129" t="s">
         <v>138</v>
       </c>
@@ -4103,7 +4103,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="130" spans="1:59" x14ac:dyDescent="0.3">
+    <row r="130" spans="1:59" x14ac:dyDescent="0.25">
       <c r="A130" t="s">
         <v>141</v>
       </c>
@@ -4117,7 +4117,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="131" spans="1:59" x14ac:dyDescent="0.3">
+    <row r="131" spans="1:59" x14ac:dyDescent="0.25">
       <c r="A131" t="s">
         <v>144</v>
       </c>
@@ -4131,7 +4131,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="132" spans="1:59" x14ac:dyDescent="0.3">
+    <row r="132" spans="1:59" x14ac:dyDescent="0.25">
       <c r="A132" t="s">
         <v>144</v>
       </c>
@@ -4160,7 +4160,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="133" spans="1:59" x14ac:dyDescent="0.3">
+    <row r="133" spans="1:59" x14ac:dyDescent="0.25">
       <c r="A133" t="s">
         <v>228</v>
       </c>
@@ -4177,7 +4177,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="134" spans="1:59" x14ac:dyDescent="0.3">
+    <row r="134" spans="1:59" x14ac:dyDescent="0.25">
       <c r="A134" t="s">
         <v>230</v>
       </c>
@@ -4191,7 +4191,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="135" spans="1:59" x14ac:dyDescent="0.3">
+    <row r="135" spans="1:59" x14ac:dyDescent="0.25">
       <c r="A135" t="s">
         <v>232</v>
       </c>
@@ -4208,7 +4208,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="136" spans="1:59" x14ac:dyDescent="0.3">
+    <row r="136" spans="1:59" x14ac:dyDescent="0.25">
       <c r="A136" t="s">
         <v>234</v>
       </c>
@@ -4225,7 +4225,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="137" spans="1:59" x14ac:dyDescent="0.3">
+    <row r="137" spans="1:59" x14ac:dyDescent="0.25">
       <c r="A137" t="s">
         <v>234</v>
       </c>
@@ -4245,7 +4245,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="138" spans="1:59" x14ac:dyDescent="0.3">
+    <row r="138" spans="1:59" x14ac:dyDescent="0.25">
       <c r="A138" t="s">
         <v>237</v>
       </c>
@@ -4259,7 +4259,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="139" spans="1:59" x14ac:dyDescent="0.3">
+    <row r="139" spans="1:59" x14ac:dyDescent="0.25">
       <c r="A139" t="s">
         <v>154</v>
       </c>
@@ -4273,7 +4273,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="140" spans="1:59" x14ac:dyDescent="0.3">
+    <row r="140" spans="1:59" x14ac:dyDescent="0.25">
       <c r="A140" t="s">
         <v>240</v>
       </c>
@@ -4287,7 +4287,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="141" spans="1:59" x14ac:dyDescent="0.3">
+    <row r="141" spans="1:59" x14ac:dyDescent="0.25">
       <c r="A141" t="s">
         <v>242</v>
       </c>
@@ -4301,7 +4301,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="142" spans="1:59" x14ac:dyDescent="0.3">
+    <row r="142" spans="1:59" x14ac:dyDescent="0.25">
       <c r="A142" t="s">
         <v>156</v>
       </c>
@@ -4333,7 +4333,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="143" spans="1:59" x14ac:dyDescent="0.3">
+    <row r="143" spans="1:59" x14ac:dyDescent="0.25">
       <c r="A143" t="s">
         <v>156</v>
       </c>
@@ -4350,7 +4350,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="144" spans="1:59" x14ac:dyDescent="0.3">
+    <row r="144" spans="1:59" x14ac:dyDescent="0.25">
       <c r="A144" t="s">
         <v>159</v>
       </c>
@@ -4382,7 +4382,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="145" spans="1:56" x14ac:dyDescent="0.3">
+    <row r="145" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A145" t="s">
         <v>244</v>
       </c>
@@ -4453,7 +4453,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="146" spans="1:56" x14ac:dyDescent="0.3">
+    <row r="146" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A146" t="s">
         <v>163</v>
       </c>
@@ -4527,7 +4527,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="147" spans="1:56" x14ac:dyDescent="0.3">
+    <row r="147" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A147" t="s">
         <v>165</v>
       </c>
@@ -4595,7 +4595,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="148" spans="1:56" x14ac:dyDescent="0.3">
+    <row r="148" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A148" t="s">
         <v>167</v>
       </c>
@@ -4609,7 +4609,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="149" spans="1:56" x14ac:dyDescent="0.3">
+    <row r="149" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A149" t="s">
         <v>167</v>
       </c>
@@ -4629,7 +4629,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="150" spans="1:56" x14ac:dyDescent="0.3">
+    <row r="150" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A150" t="s">
         <v>169</v>
       </c>
@@ -4646,7 +4646,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="151" spans="1:56" x14ac:dyDescent="0.3">
+    <row r="151" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A151" t="s">
         <v>169</v>
       </c>
@@ -4663,7 +4663,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="152" spans="1:56" x14ac:dyDescent="0.3">
+    <row r="152" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A152" t="s">
         <v>172</v>
       </c>
@@ -4677,7 +4677,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="153" spans="1:56" x14ac:dyDescent="0.3">
+    <row r="153" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A153" t="s">
         <v>247</v>
       </c>
@@ -4694,7 +4694,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="154" spans="1:56" x14ac:dyDescent="0.3">
+    <row r="154" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A154" t="s">
         <v>176</v>
       </c>
@@ -4711,7 +4711,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="155" spans="1:56" x14ac:dyDescent="0.3">
+    <row r="155" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A155" t="s">
         <v>176</v>
       </c>
@@ -4725,7 +4725,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="156" spans="1:56" x14ac:dyDescent="0.3">
+    <row r="156" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A156" t="s">
         <v>178</v>
       </c>
@@ -4745,7 +4745,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="157" spans="1:56" x14ac:dyDescent="0.3">
+    <row r="157" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A157" t="s">
         <v>180</v>
       </c>
@@ -4759,7 +4759,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="158" spans="1:56" x14ac:dyDescent="0.3">
+    <row r="158" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A158" t="s">
         <v>180</v>
       </c>
@@ -4773,7 +4773,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="159" spans="1:56" x14ac:dyDescent="0.3">
+    <row r="159" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A159" t="s">
         <v>183</v>
       </c>
@@ -4787,7 +4787,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="160" spans="1:56" x14ac:dyDescent="0.3">
+    <row r="160" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A160" t="s">
         <v>185</v>
       </c>
@@ -4828,7 +4828,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="161" spans="1:59" x14ac:dyDescent="0.3">
+    <row r="161" spans="1:59" x14ac:dyDescent="0.25">
       <c r="A161" t="s">
         <v>187</v>
       </c>
@@ -4863,7 +4863,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="162" spans="1:59" x14ac:dyDescent="0.3">
+    <row r="162" spans="1:59" x14ac:dyDescent="0.25">
       <c r="A162" t="s">
         <v>187</v>
       </c>
@@ -4880,7 +4880,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="163" spans="1:59" x14ac:dyDescent="0.3">
+    <row r="163" spans="1:59" x14ac:dyDescent="0.25">
       <c r="A163" t="s">
         <v>192</v>
       </c>
@@ -4894,7 +4894,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="164" spans="1:59" x14ac:dyDescent="0.3">
+    <row r="164" spans="1:59" x14ac:dyDescent="0.25">
       <c r="A164" t="s">
         <v>192</v>
       </c>
@@ -4914,7 +4914,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="165" spans="1:59" x14ac:dyDescent="0.3">
+    <row r="165" spans="1:59" x14ac:dyDescent="0.25">
       <c r="A165" t="s">
         <v>196</v>
       </c>
@@ -4928,7 +4928,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="166" spans="1:59" x14ac:dyDescent="0.3">
+    <row r="166" spans="1:59" x14ac:dyDescent="0.25">
       <c r="A166" t="s">
         <v>196</v>
       </c>
@@ -4945,7 +4945,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="167" spans="1:59" x14ac:dyDescent="0.3">
+    <row r="167" spans="1:59" x14ac:dyDescent="0.25">
       <c r="A167" t="s">
         <v>201</v>
       </c>
@@ -4971,7 +4971,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="168" spans="1:59" x14ac:dyDescent="0.3">
+    <row r="168" spans="1:59" x14ac:dyDescent="0.25">
       <c r="A168" t="s">
         <v>203</v>
       </c>
@@ -4991,7 +4991,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="169" spans="1:59" x14ac:dyDescent="0.3">
+    <row r="169" spans="1:59" x14ac:dyDescent="0.25">
       <c r="A169" t="s">
         <v>207</v>
       </c>
@@ -5011,7 +5011,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="170" spans="1:59" x14ac:dyDescent="0.3">
+    <row r="170" spans="1:59" x14ac:dyDescent="0.25">
       <c r="A170" t="s">
         <v>207</v>
       </c>
@@ -5037,7 +5037,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="171" spans="1:59" x14ac:dyDescent="0.3">
+    <row r="171" spans="1:59" x14ac:dyDescent="0.25">
       <c r="A171" t="s">
         <v>252</v>
       </c>
@@ -5054,7 +5054,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="172" spans="1:59" x14ac:dyDescent="0.3">
+    <row r="172" spans="1:59" x14ac:dyDescent="0.25">
       <c r="A172" t="s">
         <v>209</v>
       </c>
@@ -5080,7 +5080,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="173" spans="1:59" x14ac:dyDescent="0.3">
+    <row r="173" spans="1:59" x14ac:dyDescent="0.25">
       <c r="A173" t="s">
         <v>254</v>
       </c>

--- a/html/Specialsystemer_excel.XLSX
+++ b/html/Specialsystemer_excel.XLSX
@@ -5,18 +5,18 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hua\GitHub\GodkendteSystemer\html\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://medcomdk-my.sharepoint.com/personal/sof_medcom_dk/Documents/Dokumenter/GitHub/GodkendteSystemer/html/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2378D91F-99A1-4190-B429-549A8220354E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="1" documentId="11_BEA61AB9937531F2A50A2AEB5674993C70D96F44" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B8F8EE83-44B1-49B3-8534-67E2C456FD97}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 17-09-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 18-09-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Specialsystemer">'Opdateret d. 17-09-2026'!$A$1:$BN$173</definedName>
+    <definedName name="Specialsystemer">'Opdateret d. 18-09-2026'!$A$1:$BN$173</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>
@@ -1137,9 +1137,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:BN173"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1" spans="1:66" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:66" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1339,7 +1339,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="2" spans="1:66" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:66" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>66</v>
       </c>
@@ -1359,7 +1359,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="3" spans="1:66" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:66" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>71</v>
       </c>
@@ -1379,7 +1379,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="4" spans="1:66" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:66" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>73</v>
       </c>
@@ -1414,7 +1414,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="5" spans="1:66" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:66" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>75</v>
       </c>
@@ -1431,7 +1431,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="6" spans="1:66" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:66" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>77</v>
       </c>
@@ -1451,7 +1451,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="7" spans="1:66" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:66" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>79</v>
       </c>
@@ -1468,7 +1468,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="8" spans="1:66" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:66" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>82</v>
       </c>
@@ -1539,7 +1539,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="9" spans="1:66" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:66" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>84</v>
       </c>
@@ -1595,7 +1595,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="10" spans="1:66" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:66" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>86</v>
       </c>
@@ -1609,7 +1609,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="11" spans="1:66" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:66" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>88</v>
       </c>
@@ -1623,7 +1623,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="12" spans="1:66" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:66" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>90</v>
       </c>
@@ -1637,7 +1637,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="13" spans="1:66" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:66" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>92</v>
       </c>
@@ -1651,7 +1651,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="14" spans="1:66" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:66" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>92</v>
       </c>
@@ -1665,7 +1665,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="15" spans="1:66" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:66" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>95</v>
       </c>
@@ -1679,7 +1679,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="16" spans="1:66" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:66" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
         <v>97</v>
       </c>
@@ -1693,7 +1693,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="17" spans="1:66" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:66" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
         <v>99</v>
       </c>
@@ -1707,7 +1707,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="18" spans="1:66" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:66" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
         <v>101</v>
       </c>
@@ -1766,7 +1766,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="19" spans="1:66" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:66" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
         <v>103</v>
       </c>
@@ -1780,7 +1780,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="20" spans="1:66" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:66" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
         <v>105</v>
       </c>
@@ -1803,7 +1803,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="21" spans="1:66" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:66" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
         <v>105</v>
       </c>
@@ -1817,7 +1817,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="22" spans="1:66" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:66" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
         <v>108</v>
       </c>
@@ -1831,7 +1831,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="23" spans="1:66" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:66" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
         <v>110</v>
       </c>
@@ -1845,7 +1845,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="24" spans="1:66" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:66" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
         <v>112</v>
       </c>
@@ -1862,7 +1862,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="25" spans="1:66" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:66" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
         <v>114</v>
       </c>
@@ -1876,7 +1876,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="26" spans="1:66" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:66" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
         <v>116</v>
       </c>
@@ -1893,7 +1893,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="27" spans="1:66" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:66" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
         <v>118</v>
       </c>
@@ -1922,7 +1922,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="28" spans="1:66" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:66" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
         <v>118</v>
       </c>
@@ -1948,7 +1948,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="29" spans="1:66" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:66" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
         <v>121</v>
       </c>
@@ -1965,7 +1965,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="30" spans="1:66" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:66" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
         <v>121</v>
       </c>
@@ -1991,7 +1991,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="31" spans="1:66" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:66" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
         <v>125</v>
       </c>
@@ -2005,7 +2005,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="32" spans="1:66" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:66" x14ac:dyDescent="0.35">
       <c r="A32" t="s">
         <v>125</v>
       </c>
@@ -2028,7 +2028,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="33" spans="1:66" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:66" x14ac:dyDescent="0.35">
       <c r="A33" t="s">
         <v>128</v>
       </c>
@@ -2048,7 +2048,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="34" spans="1:66" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:66" x14ac:dyDescent="0.35">
       <c r="A34" t="s">
         <v>128</v>
       </c>
@@ -2068,7 +2068,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="35" spans="1:66" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:66" x14ac:dyDescent="0.35">
       <c r="A35" t="s">
         <v>131</v>
       </c>
@@ -2088,7 +2088,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="36" spans="1:66" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:66" x14ac:dyDescent="0.35">
       <c r="A36" t="s">
         <v>133</v>
       </c>
@@ -2105,7 +2105,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="37" spans="1:66" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:66" x14ac:dyDescent="0.35">
       <c r="A37" t="s">
         <v>133</v>
       </c>
@@ -2119,7 +2119,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="38" spans="1:66" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:66" x14ac:dyDescent="0.35">
       <c r="A38" t="s">
         <v>133</v>
       </c>
@@ -2133,7 +2133,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="39" spans="1:66" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:66" x14ac:dyDescent="0.35">
       <c r="A39" t="s">
         <v>137</v>
       </c>
@@ -2153,7 +2153,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="40" spans="1:66" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:66" x14ac:dyDescent="0.35">
       <c r="A40" t="s">
         <v>139</v>
       </c>
@@ -2170,7 +2170,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="41" spans="1:66" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:66" x14ac:dyDescent="0.35">
       <c r="A41" t="s">
         <v>139</v>
       </c>
@@ -2187,7 +2187,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="42" spans="1:66" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:66" x14ac:dyDescent="0.35">
       <c r="A42" t="s">
         <v>142</v>
       </c>
@@ -2201,7 +2201,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="43" spans="1:66" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:66" x14ac:dyDescent="0.35">
       <c r="A43" t="s">
         <v>142</v>
       </c>
@@ -2215,7 +2215,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="44" spans="1:66" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:66" x14ac:dyDescent="0.35">
       <c r="A44" t="s">
         <v>145</v>
       </c>
@@ -2235,7 +2235,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="45" spans="1:66" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:66" x14ac:dyDescent="0.35">
       <c r="A45" t="s">
         <v>145</v>
       </c>
@@ -2258,7 +2258,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="46" spans="1:66" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:66" x14ac:dyDescent="0.35">
       <c r="A46" t="s">
         <v>148</v>
       </c>
@@ -2275,7 +2275,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="47" spans="1:66" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:66" x14ac:dyDescent="0.35">
       <c r="A47" t="s">
         <v>150</v>
       </c>
@@ -2289,7 +2289,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="48" spans="1:66" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:66" x14ac:dyDescent="0.35">
       <c r="A48" t="s">
         <v>150</v>
       </c>
@@ -2303,7 +2303,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="49" spans="1:65" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:65" x14ac:dyDescent="0.35">
       <c r="A49" t="s">
         <v>153</v>
       </c>
@@ -2320,7 +2320,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="50" spans="1:65" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:65" x14ac:dyDescent="0.35">
       <c r="A50" t="s">
         <v>155</v>
       </c>
@@ -2343,7 +2343,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="51" spans="1:65" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:65" x14ac:dyDescent="0.35">
       <c r="A51" t="s">
         <v>157</v>
       </c>
@@ -2375,7 +2375,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="52" spans="1:65" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:65" x14ac:dyDescent="0.35">
       <c r="A52" t="s">
         <v>157</v>
       </c>
@@ -2395,7 +2395,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="53" spans="1:65" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:65" x14ac:dyDescent="0.35">
       <c r="A53" t="s">
         <v>160</v>
       </c>
@@ -2430,7 +2430,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="54" spans="1:65" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:65" x14ac:dyDescent="0.35">
       <c r="A54" t="s">
         <v>162</v>
       </c>
@@ -2444,7 +2444,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="55" spans="1:65" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:65" x14ac:dyDescent="0.35">
       <c r="A55" t="s">
         <v>164</v>
       </c>
@@ -2494,7 +2494,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="56" spans="1:65" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:65" x14ac:dyDescent="0.35">
       <c r="A56" t="s">
         <v>166</v>
       </c>
@@ -2544,7 +2544,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="57" spans="1:65" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:65" x14ac:dyDescent="0.35">
       <c r="A57" t="s">
         <v>168</v>
       </c>
@@ -2558,7 +2558,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="58" spans="1:65" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:65" x14ac:dyDescent="0.35">
       <c r="A58" t="s">
         <v>170</v>
       </c>
@@ -2572,7 +2572,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="59" spans="1:65" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:65" x14ac:dyDescent="0.35">
       <c r="A59" t="s">
         <v>170</v>
       </c>
@@ -2586,7 +2586,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="60" spans="1:65" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:65" x14ac:dyDescent="0.35">
       <c r="A60" t="s">
         <v>173</v>
       </c>
@@ -2600,7 +2600,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="61" spans="1:65" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:65" x14ac:dyDescent="0.35">
       <c r="A61" t="s">
         <v>175</v>
       </c>
@@ -2623,7 +2623,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="62" spans="1:65" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:65" x14ac:dyDescent="0.35">
       <c r="A62" t="s">
         <v>177</v>
       </c>
@@ -2637,7 +2637,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="63" spans="1:65" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:65" x14ac:dyDescent="0.35">
       <c r="A63" t="s">
         <v>179</v>
       </c>
@@ -2651,7 +2651,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="64" spans="1:65" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:65" x14ac:dyDescent="0.35">
       <c r="A64" t="s">
         <v>181</v>
       </c>
@@ -2665,7 +2665,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="65" spans="1:66" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:66" x14ac:dyDescent="0.35">
       <c r="A65" t="s">
         <v>181</v>
       </c>
@@ -2679,7 +2679,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="66" spans="1:66" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:66" x14ac:dyDescent="0.35">
       <c r="A66" t="s">
         <v>184</v>
       </c>
@@ -2693,7 +2693,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="67" spans="1:66" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:66" x14ac:dyDescent="0.35">
       <c r="A67" t="s">
         <v>186</v>
       </c>
@@ -2752,7 +2752,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="68" spans="1:66" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:66" x14ac:dyDescent="0.35">
       <c r="A68" t="s">
         <v>188</v>
       </c>
@@ -2781,7 +2781,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="69" spans="1:66" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:66" x14ac:dyDescent="0.35">
       <c r="A69" t="s">
         <v>188</v>
       </c>
@@ -2804,7 +2804,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="70" spans="1:66" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:66" x14ac:dyDescent="0.35">
       <c r="A70" t="s">
         <v>191</v>
       </c>
@@ -2818,7 +2818,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="71" spans="1:66" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:66" x14ac:dyDescent="0.35">
       <c r="A71" t="s">
         <v>193</v>
       </c>
@@ -2838,7 +2838,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="72" spans="1:66" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:66" x14ac:dyDescent="0.35">
       <c r="A72" t="s">
         <v>195</v>
       </c>
@@ -2852,7 +2852,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="73" spans="1:66" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:66" x14ac:dyDescent="0.35">
       <c r="A73" t="s">
         <v>197</v>
       </c>
@@ -2866,7 +2866,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="74" spans="1:66" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:66" x14ac:dyDescent="0.35">
       <c r="A74" t="s">
         <v>197</v>
       </c>
@@ -2886,7 +2886,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="75" spans="1:66" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:66" x14ac:dyDescent="0.35">
       <c r="A75" t="s">
         <v>200</v>
       </c>
@@ -2900,7 +2900,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="76" spans="1:66" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:66" x14ac:dyDescent="0.35">
       <c r="A76" t="s">
         <v>202</v>
       </c>
@@ -2920,7 +2920,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="77" spans="1:66" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:66" x14ac:dyDescent="0.35">
       <c r="A77" t="s">
         <v>204</v>
       </c>
@@ -2937,7 +2937,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="78" spans="1:66" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:66" x14ac:dyDescent="0.35">
       <c r="A78" t="s">
         <v>206</v>
       </c>
@@ -2951,7 +2951,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="79" spans="1:66" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:66" x14ac:dyDescent="0.35">
       <c r="A79" t="s">
         <v>208</v>
       </c>
@@ -2965,7 +2965,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="80" spans="1:66" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:66" x14ac:dyDescent="0.35">
       <c r="A80" t="s">
         <v>210</v>
       </c>
@@ -2979,7 +2979,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="81" spans="1:65" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:65" x14ac:dyDescent="0.35">
       <c r="A81" t="s">
         <v>66</v>
       </c>
@@ -2999,7 +2999,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="82" spans="1:65" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:65" x14ac:dyDescent="0.35">
       <c r="A82" t="s">
         <v>71</v>
       </c>
@@ -3034,7 +3034,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="83" spans="1:65" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:65" x14ac:dyDescent="0.35">
       <c r="A83" t="s">
         <v>73</v>
       </c>
@@ -3060,7 +3060,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="84" spans="1:65" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:65" x14ac:dyDescent="0.35">
       <c r="A84" t="s">
         <v>75</v>
       </c>
@@ -3074,7 +3074,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="85" spans="1:65" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:65" x14ac:dyDescent="0.35">
       <c r="A85" t="s">
         <v>77</v>
       </c>
@@ -3094,7 +3094,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="86" spans="1:65" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:65" x14ac:dyDescent="0.35">
       <c r="A86" t="s">
         <v>79</v>
       </c>
@@ -3111,7 +3111,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="87" spans="1:65" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:65" x14ac:dyDescent="0.35">
       <c r="A87" t="s">
         <v>213</v>
       </c>
@@ -3128,7 +3128,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="88" spans="1:65" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:65" x14ac:dyDescent="0.35">
       <c r="A88" t="s">
         <v>215</v>
       </c>
@@ -3145,7 +3145,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="89" spans="1:65" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:65" x14ac:dyDescent="0.35">
       <c r="A89" t="s">
         <v>215</v>
       </c>
@@ -3168,7 +3168,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="90" spans="1:65" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:65" x14ac:dyDescent="0.35">
       <c r="A90" t="s">
         <v>218</v>
       </c>
@@ -3245,7 +3245,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="91" spans="1:65" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:65" x14ac:dyDescent="0.35">
       <c r="A91" t="s">
         <v>82</v>
       </c>
@@ -3325,7 +3325,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="92" spans="1:65" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:65" x14ac:dyDescent="0.35">
       <c r="A92" t="s">
         <v>84</v>
       </c>
@@ -3402,7 +3402,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="93" spans="1:65" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:65" x14ac:dyDescent="0.35">
       <c r="A93" t="s">
         <v>86</v>
       </c>
@@ -3416,7 +3416,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="94" spans="1:65" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:65" x14ac:dyDescent="0.35">
       <c r="A94" t="s">
         <v>88</v>
       </c>
@@ -3430,7 +3430,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="95" spans="1:65" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:65" x14ac:dyDescent="0.35">
       <c r="A95" t="s">
         <v>90</v>
       </c>
@@ -3447,7 +3447,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="96" spans="1:65" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:65" x14ac:dyDescent="0.35">
       <c r="A96" t="s">
         <v>90</v>
       </c>
@@ -3464,7 +3464,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="97" spans="1:61" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:61" x14ac:dyDescent="0.35">
       <c r="A97" t="s">
         <v>92</v>
       </c>
@@ -3478,7 +3478,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="98" spans="1:61" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:61" x14ac:dyDescent="0.35">
       <c r="A98" t="s">
         <v>92</v>
       </c>
@@ -3504,7 +3504,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="99" spans="1:61" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:61" x14ac:dyDescent="0.35">
       <c r="A99" t="s">
         <v>221</v>
       </c>
@@ -3521,7 +3521,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="100" spans="1:61" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:61" x14ac:dyDescent="0.35">
       <c r="A100" t="s">
         <v>223</v>
       </c>
@@ -3541,7 +3541,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="101" spans="1:61" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:61" x14ac:dyDescent="0.35">
       <c r="A101" t="s">
         <v>95</v>
       </c>
@@ -3558,7 +3558,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="102" spans="1:61" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:61" x14ac:dyDescent="0.35">
       <c r="A102" t="s">
         <v>97</v>
       </c>
@@ -3575,7 +3575,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="103" spans="1:61" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:61" x14ac:dyDescent="0.35">
       <c r="A103" t="s">
         <v>99</v>
       </c>
@@ -3589,7 +3589,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="104" spans="1:61" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:61" x14ac:dyDescent="0.35">
       <c r="A104" t="s">
         <v>101</v>
       </c>
@@ -3636,7 +3636,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="105" spans="1:61" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:61" x14ac:dyDescent="0.35">
       <c r="A105" t="s">
         <v>103</v>
       </c>
@@ -3656,7 +3656,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="106" spans="1:61" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:61" x14ac:dyDescent="0.35">
       <c r="A106" t="s">
         <v>103</v>
       </c>
@@ -3676,7 +3676,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="107" spans="1:61" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:61" x14ac:dyDescent="0.35">
       <c r="A107" t="s">
         <v>226</v>
       </c>
@@ -3690,7 +3690,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="108" spans="1:61" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:61" x14ac:dyDescent="0.35">
       <c r="A108" t="s">
         <v>105</v>
       </c>
@@ -3710,7 +3710,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="109" spans="1:61" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:61" x14ac:dyDescent="0.35">
       <c r="A109" t="s">
         <v>105</v>
       </c>
@@ -3724,7 +3724,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="110" spans="1:61" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:61" x14ac:dyDescent="0.35">
       <c r="A110" t="s">
         <v>108</v>
       </c>
@@ -3744,7 +3744,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="111" spans="1:61" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:61" x14ac:dyDescent="0.35">
       <c r="A111" t="s">
         <v>110</v>
       </c>
@@ -3764,7 +3764,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="112" spans="1:61" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:61" x14ac:dyDescent="0.35">
       <c r="A112" t="s">
         <v>112</v>
       </c>
@@ -3781,7 +3781,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="113" spans="1:60" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:60" x14ac:dyDescent="0.35">
       <c r="A113" t="s">
         <v>114</v>
       </c>
@@ -3801,7 +3801,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="114" spans="1:60" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:60" x14ac:dyDescent="0.35">
       <c r="A114" t="s">
         <v>116</v>
       </c>
@@ -3815,7 +3815,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="115" spans="1:60" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:60" x14ac:dyDescent="0.35">
       <c r="A115" t="s">
         <v>116</v>
       </c>
@@ -3829,7 +3829,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="116" spans="1:60" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:60" x14ac:dyDescent="0.35">
       <c r="A116" t="s">
         <v>118</v>
       </c>
@@ -3849,7 +3849,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="117" spans="1:60" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:60" x14ac:dyDescent="0.35">
       <c r="A117" t="s">
         <v>118</v>
       </c>
@@ -3869,7 +3869,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="118" spans="1:60" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:60" x14ac:dyDescent="0.35">
       <c r="A118" t="s">
         <v>121</v>
       </c>
@@ -3883,7 +3883,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="119" spans="1:60" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:60" x14ac:dyDescent="0.35">
       <c r="A119" t="s">
         <v>121</v>
       </c>
@@ -3909,7 +3909,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="120" spans="1:60" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:60" x14ac:dyDescent="0.35">
       <c r="A120" t="s">
         <v>125</v>
       </c>
@@ -3935,7 +3935,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="121" spans="1:60" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:60" x14ac:dyDescent="0.35">
       <c r="A121" t="s">
         <v>128</v>
       </c>
@@ -3958,7 +3958,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="122" spans="1:60" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:60" x14ac:dyDescent="0.35">
       <c r="A122" t="s">
         <v>128</v>
       </c>
@@ -3981,7 +3981,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="123" spans="1:60" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:60" x14ac:dyDescent="0.35">
       <c r="A123" t="s">
         <v>131</v>
       </c>
@@ -4004,7 +4004,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="124" spans="1:60" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:60" x14ac:dyDescent="0.35">
       <c r="A124" t="s">
         <v>133</v>
       </c>
@@ -4024,7 +4024,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="125" spans="1:60" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:60" x14ac:dyDescent="0.35">
       <c r="A125" t="s">
         <v>133</v>
       </c>
@@ -4041,7 +4041,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="126" spans="1:60" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:60" x14ac:dyDescent="0.35">
       <c r="A126" t="s">
         <v>133</v>
       </c>
@@ -4058,7 +4058,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="127" spans="1:60" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:60" x14ac:dyDescent="0.35">
       <c r="A127" t="s">
         <v>137</v>
       </c>
@@ -4081,7 +4081,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="128" spans="1:60" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:60" x14ac:dyDescent="0.35">
       <c r="A128" t="s">
         <v>139</v>
       </c>
@@ -4101,7 +4101,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="129" spans="1:60" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:60" x14ac:dyDescent="0.35">
       <c r="A129" t="s">
         <v>139</v>
       </c>
@@ -4124,7 +4124,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="130" spans="1:60" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:60" x14ac:dyDescent="0.35">
       <c r="A130" t="s">
         <v>142</v>
       </c>
@@ -4138,7 +4138,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="131" spans="1:60" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:60" x14ac:dyDescent="0.35">
       <c r="A131" t="s">
         <v>145</v>
       </c>
@@ -4152,7 +4152,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="132" spans="1:60" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:60" x14ac:dyDescent="0.35">
       <c r="A132" t="s">
         <v>145</v>
       </c>
@@ -4184,7 +4184,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="133" spans="1:60" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:60" x14ac:dyDescent="0.35">
       <c r="A133" t="s">
         <v>229</v>
       </c>
@@ -4201,7 +4201,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="134" spans="1:60" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:60" x14ac:dyDescent="0.35">
       <c r="A134" t="s">
         <v>231</v>
       </c>
@@ -4215,7 +4215,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="135" spans="1:60" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:60" x14ac:dyDescent="0.35">
       <c r="A135" t="s">
         <v>233</v>
       </c>
@@ -4232,7 +4232,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="136" spans="1:60" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:60" x14ac:dyDescent="0.35">
       <c r="A136" t="s">
         <v>235</v>
       </c>
@@ -4249,7 +4249,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="137" spans="1:60" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:60" x14ac:dyDescent="0.35">
       <c r="A137" t="s">
         <v>235</v>
       </c>
@@ -4269,7 +4269,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="138" spans="1:60" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:60" x14ac:dyDescent="0.35">
       <c r="A138" t="s">
         <v>238</v>
       </c>
@@ -4283,7 +4283,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="139" spans="1:60" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:60" x14ac:dyDescent="0.35">
       <c r="A139" t="s">
         <v>155</v>
       </c>
@@ -4297,7 +4297,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="140" spans="1:60" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:60" x14ac:dyDescent="0.35">
       <c r="A140" t="s">
         <v>241</v>
       </c>
@@ -4311,7 +4311,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="141" spans="1:60" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:60" x14ac:dyDescent="0.35">
       <c r="A141" t="s">
         <v>243</v>
       </c>
@@ -4325,7 +4325,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="142" spans="1:60" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:60" x14ac:dyDescent="0.35">
       <c r="A142" t="s">
         <v>157</v>
       </c>
@@ -4357,7 +4357,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="143" spans="1:60" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:60" x14ac:dyDescent="0.35">
       <c r="A143" t="s">
         <v>157</v>
       </c>
@@ -4374,7 +4374,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="144" spans="1:60" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:60" x14ac:dyDescent="0.35">
       <c r="A144" t="s">
         <v>160</v>
       </c>
@@ -4406,7 +4406,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="145" spans="1:57" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:57" x14ac:dyDescent="0.35">
       <c r="A145" t="s">
         <v>245</v>
       </c>
@@ -4477,7 +4477,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="146" spans="1:57" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:57" x14ac:dyDescent="0.35">
       <c r="A146" t="s">
         <v>164</v>
       </c>
@@ -4551,7 +4551,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="147" spans="1:57" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:57" x14ac:dyDescent="0.35">
       <c r="A147" t="s">
         <v>166</v>
       </c>
@@ -4619,7 +4619,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="148" spans="1:57" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:57" x14ac:dyDescent="0.35">
       <c r="A148" t="s">
         <v>168</v>
       </c>
@@ -4633,7 +4633,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="149" spans="1:57" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:57" x14ac:dyDescent="0.35">
       <c r="A149" t="s">
         <v>168</v>
       </c>
@@ -4653,7 +4653,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="150" spans="1:57" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:57" x14ac:dyDescent="0.35">
       <c r="A150" t="s">
         <v>170</v>
       </c>
@@ -4670,7 +4670,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="151" spans="1:57" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:57" x14ac:dyDescent="0.35">
       <c r="A151" t="s">
         <v>170</v>
       </c>
@@ -4687,7 +4687,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="152" spans="1:57" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:57" x14ac:dyDescent="0.35">
       <c r="A152" t="s">
         <v>173</v>
       </c>
@@ -4701,7 +4701,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="153" spans="1:57" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:57" x14ac:dyDescent="0.35">
       <c r="A153" t="s">
         <v>248</v>
       </c>
@@ -4718,7 +4718,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="154" spans="1:57" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:57" x14ac:dyDescent="0.35">
       <c r="A154" t="s">
         <v>177</v>
       </c>
@@ -4735,7 +4735,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="155" spans="1:57" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:57" x14ac:dyDescent="0.35">
       <c r="A155" t="s">
         <v>177</v>
       </c>
@@ -4749,7 +4749,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="156" spans="1:57" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:57" x14ac:dyDescent="0.35">
       <c r="A156" t="s">
         <v>179</v>
       </c>
@@ -4769,7 +4769,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="157" spans="1:57" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:57" x14ac:dyDescent="0.35">
       <c r="A157" t="s">
         <v>181</v>
       </c>
@@ -4783,7 +4783,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="158" spans="1:57" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:57" x14ac:dyDescent="0.35">
       <c r="A158" t="s">
         <v>181</v>
       </c>
@@ -4797,7 +4797,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="159" spans="1:57" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:57" x14ac:dyDescent="0.35">
       <c r="A159" t="s">
         <v>184</v>
       </c>
@@ -4811,7 +4811,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="160" spans="1:57" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:57" x14ac:dyDescent="0.35">
       <c r="A160" t="s">
         <v>186</v>
       </c>
@@ -4852,7 +4852,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="161" spans="1:60" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:60" x14ac:dyDescent="0.35">
       <c r="A161" t="s">
         <v>188</v>
       </c>
@@ -4887,7 +4887,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="162" spans="1:60" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:60" x14ac:dyDescent="0.35">
       <c r="A162" t="s">
         <v>188</v>
       </c>
@@ -4904,7 +4904,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="163" spans="1:60" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:60" x14ac:dyDescent="0.35">
       <c r="A163" t="s">
         <v>193</v>
       </c>
@@ -4918,7 +4918,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="164" spans="1:60" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:60" x14ac:dyDescent="0.35">
       <c r="A164" t="s">
         <v>193</v>
       </c>
@@ -4938,7 +4938,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="165" spans="1:60" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:60" x14ac:dyDescent="0.35">
       <c r="A165" t="s">
         <v>197</v>
       </c>
@@ -4952,7 +4952,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="166" spans="1:60" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:60" x14ac:dyDescent="0.35">
       <c r="A166" t="s">
         <v>197</v>
       </c>
@@ -4969,7 +4969,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="167" spans="1:60" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:60" x14ac:dyDescent="0.35">
       <c r="A167" t="s">
         <v>202</v>
       </c>
@@ -4995,7 +4995,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="168" spans="1:60" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:60" x14ac:dyDescent="0.35">
       <c r="A168" t="s">
         <v>204</v>
       </c>
@@ -5015,7 +5015,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="169" spans="1:60" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:60" x14ac:dyDescent="0.35">
       <c r="A169" t="s">
         <v>208</v>
       </c>
@@ -5035,7 +5035,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="170" spans="1:60" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:60" x14ac:dyDescent="0.35">
       <c r="A170" t="s">
         <v>208</v>
       </c>
@@ -5061,7 +5061,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="171" spans="1:60" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:60" x14ac:dyDescent="0.35">
       <c r="A171" t="s">
         <v>253</v>
       </c>
@@ -5078,7 +5078,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="172" spans="1:60" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:60" x14ac:dyDescent="0.35">
       <c r="A172" t="s">
         <v>210</v>
       </c>
@@ -5104,7 +5104,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="173" spans="1:60" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:60" x14ac:dyDescent="0.35">
       <c r="A173" t="s">
         <v>255</v>
       </c>

--- a/html/Specialsystemer_excel.XLSX
+++ b/html/Specialsystemer_excel.XLSX
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://medcomdk-my.sharepoint.com/personal/sof_medcom_dk/Documents/Dokumenter/GitHub/GodkendteSystemer/html/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1" documentId="11_BEA61AB9937531F2A50A2AEB5674993C70D96F44" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B8F8EE83-44B1-49B3-8534-67E2C456FD97}"/>
+  <xr:revisionPtr revIDLastSave="1" documentId="11_BEA61AB9937531F2A50A2A37B673A87471D96F44" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2635CB36-B302-4EC1-9743-59B19120E5DC}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 18-09-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 21-09-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Specialsystemer">'Opdateret d. 18-09-2026'!$A$1:$BN$173</definedName>
+    <definedName name="Specialsystemer">'Opdateret d. 21-09-2026'!$A$1:$BN$173</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/Specialsystemer_excel.XLSX
+++ b/html/Specialsystemer_excel.XLSX
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://medcomdk-my.sharepoint.com/personal/sof_medcom_dk/Documents/Dokumenter/GitHub/GodkendteSystemer/html/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Documents\GitHub\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1" documentId="11_BEA61AB9937531F2A50A2A37B673A87471D96F44" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2635CB36-B302-4EC1-9743-59B19120E5DC}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8BD95B1C-46C9-4924-A16C-75D44D0F90D6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Opdateret d. 21-09-2026" sheetId="1" r:id="rId1"/>
@@ -1137,9 +1137,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:BN173"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:66" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:66" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1339,7 +1339,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="2" spans="1:66" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:66" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>66</v>
       </c>
@@ -1359,7 +1359,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="3" spans="1:66" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:66" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>71</v>
       </c>
@@ -1379,7 +1379,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="4" spans="1:66" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:66" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>73</v>
       </c>
@@ -1414,7 +1414,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="5" spans="1:66" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:66" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>75</v>
       </c>
@@ -1431,7 +1431,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="6" spans="1:66" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:66" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>77</v>
       </c>
@@ -1451,7 +1451,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="7" spans="1:66" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:66" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>79</v>
       </c>
@@ -1468,7 +1468,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="8" spans="1:66" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:66" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>82</v>
       </c>
@@ -1539,7 +1539,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="9" spans="1:66" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:66" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>84</v>
       </c>
@@ -1595,7 +1595,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="10" spans="1:66" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:66" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>86</v>
       </c>
@@ -1609,7 +1609,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="11" spans="1:66" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:66" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>88</v>
       </c>
@@ -1623,7 +1623,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="12" spans="1:66" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:66" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>90</v>
       </c>
@@ -1637,7 +1637,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="13" spans="1:66" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:66" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>92</v>
       </c>
@@ -1651,7 +1651,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="14" spans="1:66" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:66" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>92</v>
       </c>
@@ -1665,7 +1665,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="15" spans="1:66" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:66" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>95</v>
       </c>
@@ -1679,7 +1679,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="16" spans="1:66" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:66" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>97</v>
       </c>
@@ -1693,7 +1693,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="17" spans="1:66" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:66" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>99</v>
       </c>
@@ -1707,7 +1707,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="18" spans="1:66" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:66" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>101</v>
       </c>
@@ -1766,7 +1766,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="19" spans="1:66" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:66" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>103</v>
       </c>
@@ -1780,7 +1780,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="20" spans="1:66" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:66" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>105</v>
       </c>
@@ -1803,7 +1803,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="21" spans="1:66" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:66" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>105</v>
       </c>
@@ -1817,7 +1817,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="22" spans="1:66" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:66" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>108</v>
       </c>
@@ -1831,7 +1831,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="23" spans="1:66" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:66" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>110</v>
       </c>
@@ -1845,7 +1845,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="24" spans="1:66" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:66" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>112</v>
       </c>
@@ -1862,7 +1862,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="25" spans="1:66" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:66" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>114</v>
       </c>
@@ -1876,7 +1876,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="26" spans="1:66" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:66" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>116</v>
       </c>
@@ -1893,7 +1893,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="27" spans="1:66" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:66" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>118</v>
       </c>
@@ -1922,7 +1922,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="28" spans="1:66" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:66" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>118</v>
       </c>
@@ -1948,7 +1948,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="29" spans="1:66" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:66" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>121</v>
       </c>
@@ -1965,7 +1965,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="30" spans="1:66" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:66" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>121</v>
       </c>
@@ -1991,7 +1991,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="31" spans="1:66" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:66" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>125</v>
       </c>
@@ -2005,7 +2005,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="32" spans="1:66" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:66" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>125</v>
       </c>
@@ -2028,7 +2028,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="33" spans="1:66" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:66" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>128</v>
       </c>
@@ -2048,7 +2048,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="34" spans="1:66" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:66" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>128</v>
       </c>
@@ -2068,7 +2068,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="35" spans="1:66" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:66" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>131</v>
       </c>
@@ -2088,7 +2088,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="36" spans="1:66" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:66" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>133</v>
       </c>
@@ -2105,7 +2105,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="37" spans="1:66" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:66" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>133</v>
       </c>
@@ -2119,7 +2119,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="38" spans="1:66" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:66" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>133</v>
       </c>
@@ -2133,7 +2133,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="39" spans="1:66" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:66" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>137</v>
       </c>
@@ -2153,7 +2153,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="40" spans="1:66" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:66" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>139</v>
       </c>
@@ -2170,7 +2170,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="41" spans="1:66" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:66" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>139</v>
       </c>
@@ -2187,7 +2187,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="42" spans="1:66" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:66" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>142</v>
       </c>
@@ -2201,7 +2201,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="43" spans="1:66" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:66" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>142</v>
       </c>
@@ -2215,7 +2215,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="44" spans="1:66" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:66" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>145</v>
       </c>
@@ -2235,7 +2235,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="45" spans="1:66" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:66" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>145</v>
       </c>
@@ -2258,7 +2258,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="46" spans="1:66" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:66" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>148</v>
       </c>
@@ -2275,7 +2275,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="47" spans="1:66" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:66" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
         <v>150</v>
       </c>
@@ -2289,7 +2289,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="48" spans="1:66" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:66" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
         <v>150</v>
       </c>
@@ -2303,7 +2303,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="49" spans="1:65" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
         <v>153</v>
       </c>
@@ -2320,7 +2320,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="50" spans="1:65" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
         <v>155</v>
       </c>
@@ -2343,7 +2343,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="51" spans="1:65" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
         <v>157</v>
       </c>
@@ -2375,7 +2375,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="52" spans="1:65" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
         <v>157</v>
       </c>
@@ -2395,7 +2395,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="53" spans="1:65" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
         <v>160</v>
       </c>
@@ -2430,7 +2430,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="54" spans="1:65" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
         <v>162</v>
       </c>
@@ -2444,7 +2444,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="55" spans="1:65" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
         <v>164</v>
       </c>
@@ -2494,7 +2494,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="56" spans="1:65" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
         <v>166</v>
       </c>
@@ -2544,7 +2544,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="57" spans="1:65" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
         <v>168</v>
       </c>
@@ -2558,7 +2558,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="58" spans="1:65" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
         <v>170</v>
       </c>
@@ -2572,7 +2572,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="59" spans="1:65" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
         <v>170</v>
       </c>
@@ -2586,7 +2586,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="60" spans="1:65" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
         <v>173</v>
       </c>
@@ -2600,7 +2600,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="61" spans="1:65" x14ac:dyDescent="0.35">
+    <row r="61" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
         <v>175</v>
       </c>
@@ -2623,7 +2623,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="62" spans="1:65" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
         <v>177</v>
       </c>
@@ -2637,7 +2637,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="63" spans="1:65" x14ac:dyDescent="0.35">
+    <row r="63" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
         <v>179</v>
       </c>
@@ -2651,7 +2651,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="64" spans="1:65" x14ac:dyDescent="0.35">
+    <row r="64" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
         <v>181</v>
       </c>
@@ -2665,7 +2665,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="65" spans="1:66" x14ac:dyDescent="0.35">
+    <row r="65" spans="1:66" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
         <v>181</v>
       </c>
@@ -2679,7 +2679,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="66" spans="1:66" x14ac:dyDescent="0.35">
+    <row r="66" spans="1:66" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
         <v>184</v>
       </c>
@@ -2693,7 +2693,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="67" spans="1:66" x14ac:dyDescent="0.35">
+    <row r="67" spans="1:66" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
         <v>186</v>
       </c>
@@ -2752,7 +2752,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="68" spans="1:66" x14ac:dyDescent="0.35">
+    <row r="68" spans="1:66" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
         <v>188</v>
       </c>
@@ -2781,7 +2781,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="69" spans="1:66" x14ac:dyDescent="0.35">
+    <row r="69" spans="1:66" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
         <v>188</v>
       </c>
@@ -2804,7 +2804,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="70" spans="1:66" x14ac:dyDescent="0.35">
+    <row r="70" spans="1:66" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
         <v>191</v>
       </c>
@@ -2818,7 +2818,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="71" spans="1:66" x14ac:dyDescent="0.35">
+    <row r="71" spans="1:66" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
         <v>193</v>
       </c>
@@ -2838,7 +2838,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="72" spans="1:66" x14ac:dyDescent="0.35">
+    <row r="72" spans="1:66" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
         <v>195</v>
       </c>
@@ -2852,7 +2852,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="73" spans="1:66" x14ac:dyDescent="0.35">
+    <row r="73" spans="1:66" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
         <v>197</v>
       </c>
@@ -2866,7 +2866,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="74" spans="1:66" x14ac:dyDescent="0.35">
+    <row r="74" spans="1:66" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
         <v>197</v>
       </c>
@@ -2886,7 +2886,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="75" spans="1:66" x14ac:dyDescent="0.35">
+    <row r="75" spans="1:66" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
         <v>200</v>
       </c>
@@ -2900,7 +2900,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="76" spans="1:66" x14ac:dyDescent="0.35">
+    <row r="76" spans="1:66" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
         <v>202</v>
       </c>
@@ -2920,7 +2920,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="77" spans="1:66" x14ac:dyDescent="0.35">
+    <row r="77" spans="1:66" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
         <v>204</v>
       </c>
@@ -2937,7 +2937,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="78" spans="1:66" x14ac:dyDescent="0.35">
+    <row r="78" spans="1:66" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
         <v>206</v>
       </c>
@@ -2951,7 +2951,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="79" spans="1:66" x14ac:dyDescent="0.35">
+    <row r="79" spans="1:66" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
         <v>208</v>
       </c>
@@ -2965,7 +2965,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="80" spans="1:66" x14ac:dyDescent="0.35">
+    <row r="80" spans="1:66" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
         <v>210</v>
       </c>
@@ -2979,7 +2979,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="81" spans="1:65" x14ac:dyDescent="0.35">
+    <row r="81" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
         <v>66</v>
       </c>
@@ -2999,7 +2999,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="82" spans="1:65" x14ac:dyDescent="0.35">
+    <row r="82" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
         <v>71</v>
       </c>
@@ -3034,7 +3034,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="83" spans="1:65" x14ac:dyDescent="0.35">
+    <row r="83" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
         <v>73</v>
       </c>
@@ -3060,7 +3060,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="84" spans="1:65" x14ac:dyDescent="0.35">
+    <row r="84" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
         <v>75</v>
       </c>
@@ -3074,7 +3074,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="85" spans="1:65" x14ac:dyDescent="0.35">
+    <row r="85" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
         <v>77</v>
       </c>
@@ -3094,7 +3094,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="86" spans="1:65" x14ac:dyDescent="0.35">
+    <row r="86" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
         <v>79</v>
       </c>
@@ -3111,7 +3111,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="87" spans="1:65" x14ac:dyDescent="0.35">
+    <row r="87" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
         <v>213</v>
       </c>
@@ -3128,7 +3128,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="88" spans="1:65" x14ac:dyDescent="0.35">
+    <row r="88" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
         <v>215</v>
       </c>
@@ -3145,7 +3145,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="89" spans="1:65" x14ac:dyDescent="0.35">
+    <row r="89" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
         <v>215</v>
       </c>
@@ -3168,7 +3168,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="90" spans="1:65" x14ac:dyDescent="0.35">
+    <row r="90" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
         <v>218</v>
       </c>
@@ -3245,7 +3245,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="91" spans="1:65" x14ac:dyDescent="0.35">
+    <row r="91" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
         <v>82</v>
       </c>
@@ -3325,7 +3325,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="92" spans="1:65" x14ac:dyDescent="0.35">
+    <row r="92" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
         <v>84</v>
       </c>
@@ -3402,7 +3402,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="93" spans="1:65" x14ac:dyDescent="0.35">
+    <row r="93" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
         <v>86</v>
       </c>
@@ -3416,7 +3416,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="94" spans="1:65" x14ac:dyDescent="0.35">
+    <row r="94" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
         <v>88</v>
       </c>
@@ -3430,7 +3430,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="95" spans="1:65" x14ac:dyDescent="0.35">
+    <row r="95" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
         <v>90</v>
       </c>
@@ -3447,7 +3447,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="96" spans="1:65" x14ac:dyDescent="0.35">
+    <row r="96" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
         <v>90</v>
       </c>
@@ -3464,7 +3464,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="97" spans="1:61" x14ac:dyDescent="0.35">
+    <row r="97" spans="1:61" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
         <v>92</v>
       </c>
@@ -3478,7 +3478,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="98" spans="1:61" x14ac:dyDescent="0.35">
+    <row r="98" spans="1:61" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
         <v>92</v>
       </c>
@@ -3504,7 +3504,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="99" spans="1:61" x14ac:dyDescent="0.35">
+    <row r="99" spans="1:61" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
         <v>221</v>
       </c>
@@ -3521,7 +3521,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="100" spans="1:61" x14ac:dyDescent="0.35">
+    <row r="100" spans="1:61" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
         <v>223</v>
       </c>
@@ -3541,7 +3541,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="101" spans="1:61" x14ac:dyDescent="0.35">
+    <row r="101" spans="1:61" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
         <v>95</v>
       </c>
@@ -3558,7 +3558,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="102" spans="1:61" x14ac:dyDescent="0.35">
+    <row r="102" spans="1:61" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
         <v>97</v>
       </c>
@@ -3575,7 +3575,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="103" spans="1:61" x14ac:dyDescent="0.35">
+    <row r="103" spans="1:61" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
         <v>99</v>
       </c>
@@ -3589,7 +3589,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="104" spans="1:61" x14ac:dyDescent="0.35">
+    <row r="104" spans="1:61" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
         <v>101</v>
       </c>
@@ -3636,7 +3636,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="105" spans="1:61" x14ac:dyDescent="0.35">
+    <row r="105" spans="1:61" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
         <v>103</v>
       </c>
@@ -3656,7 +3656,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="106" spans="1:61" x14ac:dyDescent="0.35">
+    <row r="106" spans="1:61" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
         <v>103</v>
       </c>
@@ -3676,7 +3676,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="107" spans="1:61" x14ac:dyDescent="0.35">
+    <row r="107" spans="1:61" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
         <v>226</v>
       </c>
@@ -3690,7 +3690,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="108" spans="1:61" x14ac:dyDescent="0.35">
+    <row r="108" spans="1:61" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
         <v>105</v>
       </c>
@@ -3710,7 +3710,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="109" spans="1:61" x14ac:dyDescent="0.35">
+    <row r="109" spans="1:61" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
         <v>105</v>
       </c>
@@ -3724,7 +3724,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="110" spans="1:61" x14ac:dyDescent="0.35">
+    <row r="110" spans="1:61" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
         <v>108</v>
       </c>
@@ -3744,7 +3744,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="111" spans="1:61" x14ac:dyDescent="0.35">
+    <row r="111" spans="1:61" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
         <v>110</v>
       </c>
@@ -3764,7 +3764,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="112" spans="1:61" x14ac:dyDescent="0.35">
+    <row r="112" spans="1:61" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
         <v>112</v>
       </c>
@@ -3781,7 +3781,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="113" spans="1:60" x14ac:dyDescent="0.35">
+    <row r="113" spans="1:60" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
         <v>114</v>
       </c>
@@ -3801,7 +3801,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="114" spans="1:60" x14ac:dyDescent="0.35">
+    <row r="114" spans="1:60" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
         <v>116</v>
       </c>
@@ -3815,7 +3815,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="115" spans="1:60" x14ac:dyDescent="0.35">
+    <row r="115" spans="1:60" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
         <v>116</v>
       </c>
@@ -3829,7 +3829,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="116" spans="1:60" x14ac:dyDescent="0.35">
+    <row r="116" spans="1:60" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
         <v>118</v>
       </c>
@@ -3849,7 +3849,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="117" spans="1:60" x14ac:dyDescent="0.35">
+    <row r="117" spans="1:60" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
         <v>118</v>
       </c>
@@ -3869,7 +3869,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="118" spans="1:60" x14ac:dyDescent="0.35">
+    <row r="118" spans="1:60" x14ac:dyDescent="0.25">
       <c r="A118" t="s">
         <v>121</v>
       </c>
@@ -3883,7 +3883,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="119" spans="1:60" x14ac:dyDescent="0.35">
+    <row r="119" spans="1:60" x14ac:dyDescent="0.25">
       <c r="A119" t="s">
         <v>121</v>
       </c>
@@ -3909,7 +3909,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="120" spans="1:60" x14ac:dyDescent="0.35">
+    <row r="120" spans="1:60" x14ac:dyDescent="0.25">
       <c r="A120" t="s">
         <v>125</v>
       </c>
@@ -3935,7 +3935,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="121" spans="1:60" x14ac:dyDescent="0.35">
+    <row r="121" spans="1:60" x14ac:dyDescent="0.25">
       <c r="A121" t="s">
         <v>128</v>
       </c>
@@ -3958,7 +3958,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="122" spans="1:60" x14ac:dyDescent="0.35">
+    <row r="122" spans="1:60" x14ac:dyDescent="0.25">
       <c r="A122" t="s">
         <v>128</v>
       </c>
@@ -3981,7 +3981,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="123" spans="1:60" x14ac:dyDescent="0.35">
+    <row r="123" spans="1:60" x14ac:dyDescent="0.25">
       <c r="A123" t="s">
         <v>131</v>
       </c>
@@ -4004,7 +4004,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="124" spans="1:60" x14ac:dyDescent="0.35">
+    <row r="124" spans="1:60" x14ac:dyDescent="0.25">
       <c r="A124" t="s">
         <v>133</v>
       </c>
@@ -4024,7 +4024,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="125" spans="1:60" x14ac:dyDescent="0.35">
+    <row r="125" spans="1:60" x14ac:dyDescent="0.25">
       <c r="A125" t="s">
         <v>133</v>
       </c>
@@ -4041,7 +4041,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="126" spans="1:60" x14ac:dyDescent="0.35">
+    <row r="126" spans="1:60" x14ac:dyDescent="0.25">
       <c r="A126" t="s">
         <v>133</v>
       </c>
@@ -4058,7 +4058,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="127" spans="1:60" x14ac:dyDescent="0.35">
+    <row r="127" spans="1:60" x14ac:dyDescent="0.25">
       <c r="A127" t="s">
         <v>137</v>
       </c>
@@ -4081,7 +4081,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="128" spans="1:60" x14ac:dyDescent="0.35">
+    <row r="128" spans="1:60" x14ac:dyDescent="0.25">
       <c r="A128" t="s">
         <v>139</v>
       </c>
@@ -4101,7 +4101,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="129" spans="1:60" x14ac:dyDescent="0.35">
+    <row r="129" spans="1:60" x14ac:dyDescent="0.25">
       <c r="A129" t="s">
         <v>139</v>
       </c>
@@ -4124,7 +4124,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="130" spans="1:60" x14ac:dyDescent="0.35">
+    <row r="130" spans="1:60" x14ac:dyDescent="0.25">
       <c r="A130" t="s">
         <v>142</v>
       </c>
@@ -4138,7 +4138,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="131" spans="1:60" x14ac:dyDescent="0.35">
+    <row r="131" spans="1:60" x14ac:dyDescent="0.25">
       <c r="A131" t="s">
         <v>145</v>
       </c>
@@ -4152,7 +4152,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="132" spans="1:60" x14ac:dyDescent="0.35">
+    <row r="132" spans="1:60" x14ac:dyDescent="0.25">
       <c r="A132" t="s">
         <v>145</v>
       </c>
@@ -4184,7 +4184,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="133" spans="1:60" x14ac:dyDescent="0.35">
+    <row r="133" spans="1:60" x14ac:dyDescent="0.25">
       <c r="A133" t="s">
         <v>229</v>
       </c>
@@ -4201,7 +4201,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="134" spans="1:60" x14ac:dyDescent="0.35">
+    <row r="134" spans="1:60" x14ac:dyDescent="0.25">
       <c r="A134" t="s">
         <v>231</v>
       </c>
@@ -4215,7 +4215,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="135" spans="1:60" x14ac:dyDescent="0.35">
+    <row r="135" spans="1:60" x14ac:dyDescent="0.25">
       <c r="A135" t="s">
         <v>233</v>
       </c>
@@ -4232,7 +4232,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="136" spans="1:60" x14ac:dyDescent="0.35">
+    <row r="136" spans="1:60" x14ac:dyDescent="0.25">
       <c r="A136" t="s">
         <v>235</v>
       </c>
@@ -4249,7 +4249,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="137" spans="1:60" x14ac:dyDescent="0.35">
+    <row r="137" spans="1:60" x14ac:dyDescent="0.25">
       <c r="A137" t="s">
         <v>235</v>
       </c>
@@ -4269,7 +4269,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="138" spans="1:60" x14ac:dyDescent="0.35">
+    <row r="138" spans="1:60" x14ac:dyDescent="0.25">
       <c r="A138" t="s">
         <v>238</v>
       </c>
@@ -4283,7 +4283,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="139" spans="1:60" x14ac:dyDescent="0.35">
+    <row r="139" spans="1:60" x14ac:dyDescent="0.25">
       <c r="A139" t="s">
         <v>155</v>
       </c>
@@ -4297,7 +4297,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="140" spans="1:60" x14ac:dyDescent="0.35">
+    <row r="140" spans="1:60" x14ac:dyDescent="0.25">
       <c r="A140" t="s">
         <v>241</v>
       </c>
@@ -4311,7 +4311,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="141" spans="1:60" x14ac:dyDescent="0.35">
+    <row r="141" spans="1:60" x14ac:dyDescent="0.25">
       <c r="A141" t="s">
         <v>243</v>
       </c>
@@ -4325,7 +4325,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="142" spans="1:60" x14ac:dyDescent="0.35">
+    <row r="142" spans="1:60" x14ac:dyDescent="0.25">
       <c r="A142" t="s">
         <v>157</v>
       </c>
@@ -4357,7 +4357,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="143" spans="1:60" x14ac:dyDescent="0.35">
+    <row r="143" spans="1:60" x14ac:dyDescent="0.25">
       <c r="A143" t="s">
         <v>157</v>
       </c>
@@ -4374,7 +4374,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="144" spans="1:60" x14ac:dyDescent="0.35">
+    <row r="144" spans="1:60" x14ac:dyDescent="0.25">
       <c r="A144" t="s">
         <v>160</v>
       </c>
@@ -4406,7 +4406,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="145" spans="1:57" x14ac:dyDescent="0.35">
+    <row r="145" spans="1:57" x14ac:dyDescent="0.25">
       <c r="A145" t="s">
         <v>245</v>
       </c>
@@ -4477,7 +4477,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="146" spans="1:57" x14ac:dyDescent="0.35">
+    <row r="146" spans="1:57" x14ac:dyDescent="0.25">
       <c r="A146" t="s">
         <v>164</v>
       </c>
@@ -4551,7 +4551,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="147" spans="1:57" x14ac:dyDescent="0.35">
+    <row r="147" spans="1:57" x14ac:dyDescent="0.25">
       <c r="A147" t="s">
         <v>166</v>
       </c>
@@ -4619,7 +4619,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="148" spans="1:57" x14ac:dyDescent="0.35">
+    <row r="148" spans="1:57" x14ac:dyDescent="0.25">
       <c r="A148" t="s">
         <v>168</v>
       </c>
@@ -4633,7 +4633,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="149" spans="1:57" x14ac:dyDescent="0.35">
+    <row r="149" spans="1:57" x14ac:dyDescent="0.25">
       <c r="A149" t="s">
         <v>168</v>
       </c>
@@ -4653,7 +4653,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="150" spans="1:57" x14ac:dyDescent="0.35">
+    <row r="150" spans="1:57" x14ac:dyDescent="0.25">
       <c r="A150" t="s">
         <v>170</v>
       </c>
@@ -4670,7 +4670,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="151" spans="1:57" x14ac:dyDescent="0.35">
+    <row r="151" spans="1:57" x14ac:dyDescent="0.25">
       <c r="A151" t="s">
         <v>170</v>
       </c>
@@ -4687,7 +4687,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="152" spans="1:57" x14ac:dyDescent="0.35">
+    <row r="152" spans="1:57" x14ac:dyDescent="0.25">
       <c r="A152" t="s">
         <v>173</v>
       </c>
@@ -4701,7 +4701,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="153" spans="1:57" x14ac:dyDescent="0.35">
+    <row r="153" spans="1:57" x14ac:dyDescent="0.25">
       <c r="A153" t="s">
         <v>248</v>
       </c>
@@ -4718,7 +4718,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="154" spans="1:57" x14ac:dyDescent="0.35">
+    <row r="154" spans="1:57" x14ac:dyDescent="0.25">
       <c r="A154" t="s">
         <v>177</v>
       </c>
@@ -4735,7 +4735,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="155" spans="1:57" x14ac:dyDescent="0.35">
+    <row r="155" spans="1:57" x14ac:dyDescent="0.25">
       <c r="A155" t="s">
         <v>177</v>
       </c>
@@ -4749,7 +4749,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="156" spans="1:57" x14ac:dyDescent="0.35">
+    <row r="156" spans="1:57" x14ac:dyDescent="0.25">
       <c r="A156" t="s">
         <v>179</v>
       </c>
@@ -4769,7 +4769,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="157" spans="1:57" x14ac:dyDescent="0.35">
+    <row r="157" spans="1:57" x14ac:dyDescent="0.25">
       <c r="A157" t="s">
         <v>181</v>
       </c>
@@ -4783,7 +4783,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="158" spans="1:57" x14ac:dyDescent="0.35">
+    <row r="158" spans="1:57" x14ac:dyDescent="0.25">
       <c r="A158" t="s">
         <v>181</v>
       </c>
@@ -4797,7 +4797,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="159" spans="1:57" x14ac:dyDescent="0.35">
+    <row r="159" spans="1:57" x14ac:dyDescent="0.25">
       <c r="A159" t="s">
         <v>184</v>
       </c>
@@ -4811,7 +4811,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="160" spans="1:57" x14ac:dyDescent="0.35">
+    <row r="160" spans="1:57" x14ac:dyDescent="0.25">
       <c r="A160" t="s">
         <v>186</v>
       </c>
@@ -4852,7 +4852,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="161" spans="1:60" x14ac:dyDescent="0.35">
+    <row r="161" spans="1:60" x14ac:dyDescent="0.25">
       <c r="A161" t="s">
         <v>188</v>
       </c>
@@ -4887,7 +4887,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="162" spans="1:60" x14ac:dyDescent="0.35">
+    <row r="162" spans="1:60" x14ac:dyDescent="0.25">
       <c r="A162" t="s">
         <v>188</v>
       </c>
@@ -4904,7 +4904,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="163" spans="1:60" x14ac:dyDescent="0.35">
+    <row r="163" spans="1:60" x14ac:dyDescent="0.25">
       <c r="A163" t="s">
         <v>193</v>
       </c>
@@ -4918,7 +4918,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="164" spans="1:60" x14ac:dyDescent="0.35">
+    <row r="164" spans="1:60" x14ac:dyDescent="0.25">
       <c r="A164" t="s">
         <v>193</v>
       </c>
@@ -4938,7 +4938,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="165" spans="1:60" x14ac:dyDescent="0.35">
+    <row r="165" spans="1:60" x14ac:dyDescent="0.25">
       <c r="A165" t="s">
         <v>197</v>
       </c>
@@ -4952,7 +4952,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="166" spans="1:60" x14ac:dyDescent="0.35">
+    <row r="166" spans="1:60" x14ac:dyDescent="0.25">
       <c r="A166" t="s">
         <v>197</v>
       </c>
@@ -4969,7 +4969,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="167" spans="1:60" x14ac:dyDescent="0.35">
+    <row r="167" spans="1:60" x14ac:dyDescent="0.25">
       <c r="A167" t="s">
         <v>202</v>
       </c>
@@ -4995,7 +4995,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="168" spans="1:60" x14ac:dyDescent="0.35">
+    <row r="168" spans="1:60" x14ac:dyDescent="0.25">
       <c r="A168" t="s">
         <v>204</v>
       </c>
@@ -5015,7 +5015,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="169" spans="1:60" x14ac:dyDescent="0.35">
+    <row r="169" spans="1:60" x14ac:dyDescent="0.25">
       <c r="A169" t="s">
         <v>208</v>
       </c>
@@ -5035,7 +5035,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="170" spans="1:60" x14ac:dyDescent="0.35">
+    <row r="170" spans="1:60" x14ac:dyDescent="0.25">
       <c r="A170" t="s">
         <v>208</v>
       </c>
@@ -5061,7 +5061,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="171" spans="1:60" x14ac:dyDescent="0.35">
+    <row r="171" spans="1:60" x14ac:dyDescent="0.25">
       <c r="A171" t="s">
         <v>253</v>
       </c>
@@ -5078,7 +5078,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="172" spans="1:60" x14ac:dyDescent="0.35">
+    <row r="172" spans="1:60" x14ac:dyDescent="0.25">
       <c r="A172" t="s">
         <v>210</v>
       </c>
@@ -5104,7 +5104,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="173" spans="1:60" x14ac:dyDescent="0.35">
+    <row r="173" spans="1:60" x14ac:dyDescent="0.25">
       <c r="A173" t="s">
         <v>255</v>
       </c>

--- a/html/Specialsystemer_excel.XLSX
+++ b/html/Specialsystemer_excel.XLSX
@@ -5,18 +5,18 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Documents\GitHub\GodkendteSystemer\html\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8BD95B1C-46C9-4924-A16C-75D44D0F90D6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C299A148-7564-44F7-8F4D-A1D2D331649C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="780" yWindow="780" windowWidth="21600" windowHeight="12645" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 21-09-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 22-09-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Specialsystemer">'Opdateret d. 21-09-2026'!$A$1:$BN$173</definedName>
+    <definedName name="Specialsystemer">'Opdateret d. 22-09-2026'!$A$1:$BN$173</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/Specialsystemer_excel.XLSX
+++ b/html/Specialsystemer_excel.XLSX
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C299A148-7564-44F7-8F4D-A1D2D331649C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9D0532E1-480B-4E69-91E4-487CE988FCA0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="780" yWindow="780" windowWidth="21600" windowHeight="12645" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3120" yWindow="3120" windowWidth="21600" windowHeight="12645" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Opdateret d. 22-09-2026" sheetId="1" r:id="rId1"/>

--- a/html/Specialsystemer_excel.XLSX
+++ b/html/Specialsystemer_excel.XLSX
@@ -5,18 +5,18 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\GodkendteSystemer\html\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Documents\GitHub\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9D0532E1-480B-4E69-91E4-487CE988FCA0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D6C5B367-C69C-41D3-9C96-97BA6BCCADE1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3120" yWindow="3120" windowWidth="21600" windowHeight="12645" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 22-09-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 23-09-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Specialsystemer">'Opdateret d. 22-09-2026'!$A$1:$BN$173</definedName>
+    <definedName name="Specialsystemer">'Opdateret d. 23-09-2026'!$A$1:$BN$173</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/Specialsystemer_excel.XLSX
+++ b/html/Specialsystemer_excel.XLSX
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Documents\GitHub\GodkendteSystemer\html\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://medcomdk-my.sharepoint.com/personal/sof_medcom_dk/Documents/Dokumenter/GitHub/GodkendteSystemer/html/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D6C5B367-C69C-41D3-9C96-97BA6BCCADE1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="1" documentId="11_BEA61AB9937531F2A50A2AEEFEB4992A70D96F44" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{20A71358-860E-4971-9E5B-C4EFEB1D108B}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Opdateret d. 23-09-2026" sheetId="1" r:id="rId1"/>
@@ -1137,9 +1137,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:BN173"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1" spans="1:66" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:66" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1339,7 +1339,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="2" spans="1:66" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:66" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>66</v>
       </c>
@@ -1359,7 +1359,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="3" spans="1:66" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:66" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>71</v>
       </c>
@@ -1379,7 +1379,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="4" spans="1:66" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:66" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>73</v>
       </c>
@@ -1414,7 +1414,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="5" spans="1:66" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:66" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>75</v>
       </c>
@@ -1431,7 +1431,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="6" spans="1:66" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:66" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>77</v>
       </c>
@@ -1451,7 +1451,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="7" spans="1:66" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:66" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>79</v>
       </c>
@@ -1468,7 +1468,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="8" spans="1:66" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:66" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>82</v>
       </c>
@@ -1539,7 +1539,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="9" spans="1:66" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:66" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>84</v>
       </c>
@@ -1595,7 +1595,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="10" spans="1:66" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:66" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>86</v>
       </c>
@@ -1609,7 +1609,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="11" spans="1:66" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:66" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>88</v>
       </c>
@@ -1623,7 +1623,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="12" spans="1:66" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:66" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>90</v>
       </c>
@@ -1637,7 +1637,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="13" spans="1:66" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:66" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>92</v>
       </c>
@@ -1651,7 +1651,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="14" spans="1:66" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:66" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>92</v>
       </c>
@@ -1665,7 +1665,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="15" spans="1:66" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:66" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>95</v>
       </c>
@@ -1679,7 +1679,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="16" spans="1:66" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:66" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
         <v>97</v>
       </c>
@@ -1693,7 +1693,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="17" spans="1:66" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:66" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
         <v>99</v>
       </c>
@@ -1707,7 +1707,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="18" spans="1:66" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:66" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
         <v>101</v>
       </c>
@@ -1766,7 +1766,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="19" spans="1:66" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:66" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
         <v>103</v>
       </c>
@@ -1780,7 +1780,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="20" spans="1:66" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:66" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
         <v>105</v>
       </c>
@@ -1803,7 +1803,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="21" spans="1:66" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:66" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
         <v>105</v>
       </c>
@@ -1817,7 +1817,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="22" spans="1:66" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:66" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
         <v>108</v>
       </c>
@@ -1831,7 +1831,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="23" spans="1:66" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:66" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
         <v>110</v>
       </c>
@@ -1845,7 +1845,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="24" spans="1:66" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:66" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
         <v>112</v>
       </c>
@@ -1862,7 +1862,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="25" spans="1:66" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:66" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
         <v>114</v>
       </c>
@@ -1876,7 +1876,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="26" spans="1:66" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:66" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
         <v>116</v>
       </c>
@@ -1893,7 +1893,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="27" spans="1:66" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:66" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
         <v>118</v>
       </c>
@@ -1922,7 +1922,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="28" spans="1:66" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:66" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
         <v>118</v>
       </c>
@@ -1948,7 +1948,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="29" spans="1:66" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:66" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
         <v>121</v>
       </c>
@@ -1965,7 +1965,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="30" spans="1:66" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:66" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
         <v>121</v>
       </c>
@@ -1991,7 +1991,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="31" spans="1:66" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:66" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
         <v>125</v>
       </c>
@@ -2005,7 +2005,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="32" spans="1:66" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:66" x14ac:dyDescent="0.35">
       <c r="A32" t="s">
         <v>125</v>
       </c>
@@ -2028,7 +2028,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="33" spans="1:66" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:66" x14ac:dyDescent="0.35">
       <c r="A33" t="s">
         <v>128</v>
       </c>
@@ -2048,7 +2048,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="34" spans="1:66" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:66" x14ac:dyDescent="0.35">
       <c r="A34" t="s">
         <v>128</v>
       </c>
@@ -2068,7 +2068,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="35" spans="1:66" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:66" x14ac:dyDescent="0.35">
       <c r="A35" t="s">
         <v>131</v>
       </c>
@@ -2088,7 +2088,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="36" spans="1:66" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:66" x14ac:dyDescent="0.35">
       <c r="A36" t="s">
         <v>133</v>
       </c>
@@ -2105,7 +2105,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="37" spans="1:66" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:66" x14ac:dyDescent="0.35">
       <c r="A37" t="s">
         <v>133</v>
       </c>
@@ -2119,7 +2119,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="38" spans="1:66" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:66" x14ac:dyDescent="0.35">
       <c r="A38" t="s">
         <v>133</v>
       </c>
@@ -2133,7 +2133,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="39" spans="1:66" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:66" x14ac:dyDescent="0.35">
       <c r="A39" t="s">
         <v>137</v>
       </c>
@@ -2153,7 +2153,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="40" spans="1:66" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:66" x14ac:dyDescent="0.35">
       <c r="A40" t="s">
         <v>139</v>
       </c>
@@ -2170,7 +2170,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="41" spans="1:66" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:66" x14ac:dyDescent="0.35">
       <c r="A41" t="s">
         <v>139</v>
       </c>
@@ -2187,7 +2187,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="42" spans="1:66" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:66" x14ac:dyDescent="0.35">
       <c r="A42" t="s">
         <v>142</v>
       </c>
@@ -2201,7 +2201,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="43" spans="1:66" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:66" x14ac:dyDescent="0.35">
       <c r="A43" t="s">
         <v>142</v>
       </c>
@@ -2215,7 +2215,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="44" spans="1:66" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:66" x14ac:dyDescent="0.35">
       <c r="A44" t="s">
         <v>145</v>
       </c>
@@ -2235,7 +2235,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="45" spans="1:66" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:66" x14ac:dyDescent="0.35">
       <c r="A45" t="s">
         <v>145</v>
       </c>
@@ -2258,7 +2258,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="46" spans="1:66" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:66" x14ac:dyDescent="0.35">
       <c r="A46" t="s">
         <v>148</v>
       </c>
@@ -2275,7 +2275,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="47" spans="1:66" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:66" x14ac:dyDescent="0.35">
       <c r="A47" t="s">
         <v>150</v>
       </c>
@@ -2289,7 +2289,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="48" spans="1:66" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:66" x14ac:dyDescent="0.35">
       <c r="A48" t="s">
         <v>150</v>
       </c>
@@ -2303,7 +2303,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="49" spans="1:65" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:65" x14ac:dyDescent="0.35">
       <c r="A49" t="s">
         <v>153</v>
       </c>
@@ -2320,7 +2320,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="50" spans="1:65" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:65" x14ac:dyDescent="0.35">
       <c r="A50" t="s">
         <v>155</v>
       </c>
@@ -2343,7 +2343,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="51" spans="1:65" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:65" x14ac:dyDescent="0.35">
       <c r="A51" t="s">
         <v>157</v>
       </c>
@@ -2375,7 +2375,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="52" spans="1:65" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:65" x14ac:dyDescent="0.35">
       <c r="A52" t="s">
         <v>157</v>
       </c>
@@ -2395,7 +2395,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="53" spans="1:65" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:65" x14ac:dyDescent="0.35">
       <c r="A53" t="s">
         <v>160</v>
       </c>
@@ -2430,7 +2430,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="54" spans="1:65" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:65" x14ac:dyDescent="0.35">
       <c r="A54" t="s">
         <v>162</v>
       </c>
@@ -2444,7 +2444,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="55" spans="1:65" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:65" x14ac:dyDescent="0.35">
       <c r="A55" t="s">
         <v>164</v>
       </c>
@@ -2494,7 +2494,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="56" spans="1:65" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:65" x14ac:dyDescent="0.35">
       <c r="A56" t="s">
         <v>166</v>
       </c>
@@ -2544,7 +2544,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="57" spans="1:65" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:65" x14ac:dyDescent="0.35">
       <c r="A57" t="s">
         <v>168</v>
       </c>
@@ -2558,7 +2558,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="58" spans="1:65" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:65" x14ac:dyDescent="0.35">
       <c r="A58" t="s">
         <v>170</v>
       </c>
@@ -2572,7 +2572,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="59" spans="1:65" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:65" x14ac:dyDescent="0.35">
       <c r="A59" t="s">
         <v>170</v>
       </c>
@@ -2586,7 +2586,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="60" spans="1:65" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:65" x14ac:dyDescent="0.35">
       <c r="A60" t="s">
         <v>173</v>
       </c>
@@ -2600,7 +2600,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="61" spans="1:65" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:65" x14ac:dyDescent="0.35">
       <c r="A61" t="s">
         <v>175</v>
       </c>
@@ -2623,7 +2623,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="62" spans="1:65" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:65" x14ac:dyDescent="0.35">
       <c r="A62" t="s">
         <v>177</v>
       </c>
@@ -2637,7 +2637,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="63" spans="1:65" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:65" x14ac:dyDescent="0.35">
       <c r="A63" t="s">
         <v>179</v>
       </c>
@@ -2651,7 +2651,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="64" spans="1:65" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:65" x14ac:dyDescent="0.35">
       <c r="A64" t="s">
         <v>181</v>
       </c>
@@ -2665,7 +2665,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="65" spans="1:66" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:66" x14ac:dyDescent="0.35">
       <c r="A65" t="s">
         <v>181</v>
       </c>
@@ -2679,7 +2679,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="66" spans="1:66" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:66" x14ac:dyDescent="0.35">
       <c r="A66" t="s">
         <v>184</v>
       </c>
@@ -2693,7 +2693,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="67" spans="1:66" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:66" x14ac:dyDescent="0.35">
       <c r="A67" t="s">
         <v>186</v>
       </c>
@@ -2752,7 +2752,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="68" spans="1:66" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:66" x14ac:dyDescent="0.35">
       <c r="A68" t="s">
         <v>188</v>
       </c>
@@ -2781,7 +2781,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="69" spans="1:66" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:66" x14ac:dyDescent="0.35">
       <c r="A69" t="s">
         <v>188</v>
       </c>
@@ -2804,7 +2804,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="70" spans="1:66" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:66" x14ac:dyDescent="0.35">
       <c r="A70" t="s">
         <v>191</v>
       </c>
@@ -2818,7 +2818,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="71" spans="1:66" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:66" x14ac:dyDescent="0.35">
       <c r="A71" t="s">
         <v>193</v>
       </c>
@@ -2838,7 +2838,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="72" spans="1:66" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:66" x14ac:dyDescent="0.35">
       <c r="A72" t="s">
         <v>195</v>
       </c>
@@ -2852,7 +2852,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="73" spans="1:66" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:66" x14ac:dyDescent="0.35">
       <c r="A73" t="s">
         <v>197</v>
       </c>
@@ -2866,7 +2866,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="74" spans="1:66" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:66" x14ac:dyDescent="0.35">
       <c r="A74" t="s">
         <v>197</v>
       </c>
@@ -2886,7 +2886,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="75" spans="1:66" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:66" x14ac:dyDescent="0.35">
       <c r="A75" t="s">
         <v>200</v>
       </c>
@@ -2900,7 +2900,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="76" spans="1:66" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:66" x14ac:dyDescent="0.35">
       <c r="A76" t="s">
         <v>202</v>
       </c>
@@ -2920,7 +2920,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="77" spans="1:66" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:66" x14ac:dyDescent="0.35">
       <c r="A77" t="s">
         <v>204</v>
       </c>
@@ -2937,7 +2937,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="78" spans="1:66" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:66" x14ac:dyDescent="0.35">
       <c r="A78" t="s">
         <v>206</v>
       </c>
@@ -2951,7 +2951,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="79" spans="1:66" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:66" x14ac:dyDescent="0.35">
       <c r="A79" t="s">
         <v>208</v>
       </c>
@@ -2965,7 +2965,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="80" spans="1:66" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:66" x14ac:dyDescent="0.35">
       <c r="A80" t="s">
         <v>210</v>
       </c>
@@ -2979,7 +2979,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="81" spans="1:65" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:65" x14ac:dyDescent="0.35">
       <c r="A81" t="s">
         <v>66</v>
       </c>
@@ -2999,7 +2999,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="82" spans="1:65" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:65" x14ac:dyDescent="0.35">
       <c r="A82" t="s">
         <v>71</v>
       </c>
@@ -3034,7 +3034,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="83" spans="1:65" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:65" x14ac:dyDescent="0.35">
       <c r="A83" t="s">
         <v>73</v>
       </c>
@@ -3060,7 +3060,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="84" spans="1:65" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:65" x14ac:dyDescent="0.35">
       <c r="A84" t="s">
         <v>75</v>
       </c>
@@ -3074,7 +3074,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="85" spans="1:65" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:65" x14ac:dyDescent="0.35">
       <c r="A85" t="s">
         <v>77</v>
       </c>
@@ -3094,7 +3094,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="86" spans="1:65" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:65" x14ac:dyDescent="0.35">
       <c r="A86" t="s">
         <v>79</v>
       </c>
@@ -3111,7 +3111,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="87" spans="1:65" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:65" x14ac:dyDescent="0.35">
       <c r="A87" t="s">
         <v>213</v>
       </c>
@@ -3128,7 +3128,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="88" spans="1:65" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:65" x14ac:dyDescent="0.35">
       <c r="A88" t="s">
         <v>215</v>
       </c>
@@ -3145,7 +3145,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="89" spans="1:65" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:65" x14ac:dyDescent="0.35">
       <c r="A89" t="s">
         <v>215</v>
       </c>
@@ -3168,7 +3168,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="90" spans="1:65" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:65" x14ac:dyDescent="0.35">
       <c r="A90" t="s">
         <v>218</v>
       </c>
@@ -3245,7 +3245,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="91" spans="1:65" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:65" x14ac:dyDescent="0.35">
       <c r="A91" t="s">
         <v>82</v>
       </c>
@@ -3325,7 +3325,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="92" spans="1:65" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:65" x14ac:dyDescent="0.35">
       <c r="A92" t="s">
         <v>84</v>
       </c>
@@ -3402,7 +3402,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="93" spans="1:65" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:65" x14ac:dyDescent="0.35">
       <c r="A93" t="s">
         <v>86</v>
       </c>
@@ -3416,7 +3416,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="94" spans="1:65" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:65" x14ac:dyDescent="0.35">
       <c r="A94" t="s">
         <v>88</v>
       </c>
@@ -3430,7 +3430,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="95" spans="1:65" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:65" x14ac:dyDescent="0.35">
       <c r="A95" t="s">
         <v>90</v>
       </c>
@@ -3447,7 +3447,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="96" spans="1:65" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:65" x14ac:dyDescent="0.35">
       <c r="A96" t="s">
         <v>90</v>
       </c>
@@ -3464,7 +3464,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="97" spans="1:61" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:61" x14ac:dyDescent="0.35">
       <c r="A97" t="s">
         <v>92</v>
       </c>
@@ -3478,7 +3478,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="98" spans="1:61" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:61" x14ac:dyDescent="0.35">
       <c r="A98" t="s">
         <v>92</v>
       </c>
@@ -3504,7 +3504,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="99" spans="1:61" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:61" x14ac:dyDescent="0.35">
       <c r="A99" t="s">
         <v>221</v>
       </c>
@@ -3521,7 +3521,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="100" spans="1:61" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:61" x14ac:dyDescent="0.35">
       <c r="A100" t="s">
         <v>223</v>
       </c>
@@ -3541,7 +3541,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="101" spans="1:61" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:61" x14ac:dyDescent="0.35">
       <c r="A101" t="s">
         <v>95</v>
       </c>
@@ -3558,7 +3558,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="102" spans="1:61" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:61" x14ac:dyDescent="0.35">
       <c r="A102" t="s">
         <v>97</v>
       </c>
@@ -3575,7 +3575,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="103" spans="1:61" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:61" x14ac:dyDescent="0.35">
       <c r="A103" t="s">
         <v>99</v>
       </c>
@@ -3589,7 +3589,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="104" spans="1:61" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:61" x14ac:dyDescent="0.35">
       <c r="A104" t="s">
         <v>101</v>
       </c>
@@ -3636,7 +3636,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="105" spans="1:61" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:61" x14ac:dyDescent="0.35">
       <c r="A105" t="s">
         <v>103</v>
       </c>
@@ -3656,7 +3656,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="106" spans="1:61" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:61" x14ac:dyDescent="0.35">
       <c r="A106" t="s">
         <v>103</v>
       </c>
@@ -3676,7 +3676,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="107" spans="1:61" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:61" x14ac:dyDescent="0.35">
       <c r="A107" t="s">
         <v>226</v>
       </c>
@@ -3690,7 +3690,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="108" spans="1:61" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:61" x14ac:dyDescent="0.35">
       <c r="A108" t="s">
         <v>105</v>
       </c>
@@ -3710,7 +3710,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="109" spans="1:61" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:61" x14ac:dyDescent="0.35">
       <c r="A109" t="s">
         <v>105</v>
       </c>
@@ -3724,7 +3724,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="110" spans="1:61" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:61" x14ac:dyDescent="0.35">
       <c r="A110" t="s">
         <v>108</v>
       </c>
@@ -3744,7 +3744,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="111" spans="1:61" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:61" x14ac:dyDescent="0.35">
       <c r="A111" t="s">
         <v>110</v>
       </c>
@@ -3764,7 +3764,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="112" spans="1:61" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:61" x14ac:dyDescent="0.35">
       <c r="A112" t="s">
         <v>112</v>
       </c>
@@ -3781,7 +3781,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="113" spans="1:60" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:60" x14ac:dyDescent="0.35">
       <c r="A113" t="s">
         <v>114</v>
       </c>
@@ -3801,7 +3801,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="114" spans="1:60" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:60" x14ac:dyDescent="0.35">
       <c r="A114" t="s">
         <v>116</v>
       </c>
@@ -3815,7 +3815,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="115" spans="1:60" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:60" x14ac:dyDescent="0.35">
       <c r="A115" t="s">
         <v>116</v>
       </c>
@@ -3829,7 +3829,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="116" spans="1:60" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:60" x14ac:dyDescent="0.35">
       <c r="A116" t="s">
         <v>118</v>
       </c>
@@ -3849,7 +3849,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="117" spans="1:60" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:60" x14ac:dyDescent="0.35">
       <c r="A117" t="s">
         <v>118</v>
       </c>
@@ -3869,7 +3869,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="118" spans="1:60" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:60" x14ac:dyDescent="0.35">
       <c r="A118" t="s">
         <v>121</v>
       </c>
@@ -3883,7 +3883,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="119" spans="1:60" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:60" x14ac:dyDescent="0.35">
       <c r="A119" t="s">
         <v>121</v>
       </c>
@@ -3909,7 +3909,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="120" spans="1:60" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:60" x14ac:dyDescent="0.35">
       <c r="A120" t="s">
         <v>125</v>
       </c>
@@ -3935,7 +3935,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="121" spans="1:60" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:60" x14ac:dyDescent="0.35">
       <c r="A121" t="s">
         <v>128</v>
       </c>
@@ -3958,7 +3958,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="122" spans="1:60" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:60" x14ac:dyDescent="0.35">
       <c r="A122" t="s">
         <v>128</v>
       </c>
@@ -3981,7 +3981,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="123" spans="1:60" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:60" x14ac:dyDescent="0.35">
       <c r="A123" t="s">
         <v>131</v>
       </c>
@@ -4004,7 +4004,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="124" spans="1:60" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:60" x14ac:dyDescent="0.35">
       <c r="A124" t="s">
         <v>133</v>
       </c>
@@ -4024,7 +4024,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="125" spans="1:60" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:60" x14ac:dyDescent="0.35">
       <c r="A125" t="s">
         <v>133</v>
       </c>
@@ -4041,7 +4041,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="126" spans="1:60" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:60" x14ac:dyDescent="0.35">
       <c r="A126" t="s">
         <v>133</v>
       </c>
@@ -4058,7 +4058,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="127" spans="1:60" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:60" x14ac:dyDescent="0.35">
       <c r="A127" t="s">
         <v>137</v>
       </c>
@@ -4081,7 +4081,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="128" spans="1:60" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:60" x14ac:dyDescent="0.35">
       <c r="A128" t="s">
         <v>139</v>
       </c>
@@ -4101,7 +4101,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="129" spans="1:60" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:60" x14ac:dyDescent="0.35">
       <c r="A129" t="s">
         <v>139</v>
       </c>
@@ -4124,7 +4124,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="130" spans="1:60" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:60" x14ac:dyDescent="0.35">
       <c r="A130" t="s">
         <v>142</v>
       </c>
@@ -4138,7 +4138,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="131" spans="1:60" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:60" x14ac:dyDescent="0.35">
       <c r="A131" t="s">
         <v>145</v>
       </c>
@@ -4152,7 +4152,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="132" spans="1:60" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:60" x14ac:dyDescent="0.35">
       <c r="A132" t="s">
         <v>145</v>
       </c>
@@ -4184,7 +4184,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="133" spans="1:60" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:60" x14ac:dyDescent="0.35">
       <c r="A133" t="s">
         <v>229</v>
       </c>
@@ -4201,7 +4201,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="134" spans="1:60" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:60" x14ac:dyDescent="0.35">
       <c r="A134" t="s">
         <v>231</v>
       </c>
@@ -4215,7 +4215,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="135" spans="1:60" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:60" x14ac:dyDescent="0.35">
       <c r="A135" t="s">
         <v>233</v>
       </c>
@@ -4232,7 +4232,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="136" spans="1:60" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:60" x14ac:dyDescent="0.35">
       <c r="A136" t="s">
         <v>235</v>
       </c>
@@ -4249,7 +4249,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="137" spans="1:60" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:60" x14ac:dyDescent="0.35">
       <c r="A137" t="s">
         <v>235</v>
       </c>
@@ -4269,7 +4269,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="138" spans="1:60" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:60" x14ac:dyDescent="0.35">
       <c r="A138" t="s">
         <v>238</v>
       </c>
@@ -4283,7 +4283,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="139" spans="1:60" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:60" x14ac:dyDescent="0.35">
       <c r="A139" t="s">
         <v>155</v>
       </c>
@@ -4297,7 +4297,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="140" spans="1:60" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:60" x14ac:dyDescent="0.35">
       <c r="A140" t="s">
         <v>241</v>
       </c>
@@ -4311,7 +4311,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="141" spans="1:60" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:60" x14ac:dyDescent="0.35">
       <c r="A141" t="s">
         <v>243</v>
       </c>
@@ -4325,7 +4325,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="142" spans="1:60" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:60" x14ac:dyDescent="0.35">
       <c r="A142" t="s">
         <v>157</v>
       </c>
@@ -4357,7 +4357,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="143" spans="1:60" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:60" x14ac:dyDescent="0.35">
       <c r="A143" t="s">
         <v>157</v>
       </c>
@@ -4374,7 +4374,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="144" spans="1:60" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:60" x14ac:dyDescent="0.35">
       <c r="A144" t="s">
         <v>160</v>
       </c>
@@ -4406,7 +4406,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="145" spans="1:57" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:57" x14ac:dyDescent="0.35">
       <c r="A145" t="s">
         <v>245</v>
       </c>
@@ -4477,7 +4477,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="146" spans="1:57" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:57" x14ac:dyDescent="0.35">
       <c r="A146" t="s">
         <v>164</v>
       </c>
@@ -4551,7 +4551,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="147" spans="1:57" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:57" x14ac:dyDescent="0.35">
       <c r="A147" t="s">
         <v>166</v>
       </c>
@@ -4619,7 +4619,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="148" spans="1:57" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:57" x14ac:dyDescent="0.35">
       <c r="A148" t="s">
         <v>168</v>
       </c>
@@ -4633,7 +4633,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="149" spans="1:57" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:57" x14ac:dyDescent="0.35">
       <c r="A149" t="s">
         <v>168</v>
       </c>
@@ -4653,7 +4653,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="150" spans="1:57" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:57" x14ac:dyDescent="0.35">
       <c r="A150" t="s">
         <v>170</v>
       </c>
@@ -4670,7 +4670,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="151" spans="1:57" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:57" x14ac:dyDescent="0.35">
       <c r="A151" t="s">
         <v>170</v>
       </c>
@@ -4687,7 +4687,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="152" spans="1:57" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:57" x14ac:dyDescent="0.35">
       <c r="A152" t="s">
         <v>173</v>
       </c>
@@ -4701,7 +4701,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="153" spans="1:57" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:57" x14ac:dyDescent="0.35">
       <c r="A153" t="s">
         <v>248</v>
       </c>
@@ -4718,7 +4718,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="154" spans="1:57" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:57" x14ac:dyDescent="0.35">
       <c r="A154" t="s">
         <v>177</v>
       </c>
@@ -4735,7 +4735,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="155" spans="1:57" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:57" x14ac:dyDescent="0.35">
       <c r="A155" t="s">
         <v>177</v>
       </c>
@@ -4749,7 +4749,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="156" spans="1:57" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:57" x14ac:dyDescent="0.35">
       <c r="A156" t="s">
         <v>179</v>
       </c>
@@ -4769,7 +4769,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="157" spans="1:57" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:57" x14ac:dyDescent="0.35">
       <c r="A157" t="s">
         <v>181</v>
       </c>
@@ -4783,7 +4783,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="158" spans="1:57" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:57" x14ac:dyDescent="0.35">
       <c r="A158" t="s">
         <v>181</v>
       </c>
@@ -4797,7 +4797,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="159" spans="1:57" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:57" x14ac:dyDescent="0.35">
       <c r="A159" t="s">
         <v>184</v>
       </c>
@@ -4811,7 +4811,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="160" spans="1:57" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:57" x14ac:dyDescent="0.35">
       <c r="A160" t="s">
         <v>186</v>
       </c>
@@ -4852,7 +4852,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="161" spans="1:60" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:60" x14ac:dyDescent="0.35">
       <c r="A161" t="s">
         <v>188</v>
       </c>
@@ -4887,7 +4887,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="162" spans="1:60" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:60" x14ac:dyDescent="0.35">
       <c r="A162" t="s">
         <v>188</v>
       </c>
@@ -4904,7 +4904,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="163" spans="1:60" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:60" x14ac:dyDescent="0.35">
       <c r="A163" t="s">
         <v>193</v>
       </c>
@@ -4918,7 +4918,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="164" spans="1:60" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:60" x14ac:dyDescent="0.35">
       <c r="A164" t="s">
         <v>193</v>
       </c>
@@ -4938,7 +4938,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="165" spans="1:60" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:60" x14ac:dyDescent="0.35">
       <c r="A165" t="s">
         <v>197</v>
       </c>
@@ -4952,7 +4952,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="166" spans="1:60" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:60" x14ac:dyDescent="0.35">
       <c r="A166" t="s">
         <v>197</v>
       </c>
@@ -4969,7 +4969,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="167" spans="1:60" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:60" x14ac:dyDescent="0.35">
       <c r="A167" t="s">
         <v>202</v>
       </c>
@@ -4995,7 +4995,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="168" spans="1:60" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:60" x14ac:dyDescent="0.35">
       <c r="A168" t="s">
         <v>204</v>
       </c>
@@ -5015,7 +5015,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="169" spans="1:60" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:60" x14ac:dyDescent="0.35">
       <c r="A169" t="s">
         <v>208</v>
       </c>
@@ -5035,7 +5035,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="170" spans="1:60" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:60" x14ac:dyDescent="0.35">
       <c r="A170" t="s">
         <v>208</v>
       </c>
@@ -5061,7 +5061,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="171" spans="1:60" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:60" x14ac:dyDescent="0.35">
       <c r="A171" t="s">
         <v>253</v>
       </c>
@@ -5078,7 +5078,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="172" spans="1:60" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:60" x14ac:dyDescent="0.35">
       <c r="A172" t="s">
         <v>210</v>
       </c>
@@ -5104,7 +5104,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="173" spans="1:60" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:60" x14ac:dyDescent="0.35">
       <c r="A173" t="s">
         <v>255</v>
       </c>

--- a/html/Specialsystemer_excel.XLSX
+++ b/html/Specialsystemer_excel.XLSX
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://medcomdk-my.sharepoint.com/personal/sof_medcom_dk/Documents/Dokumenter/GitHub/GodkendteSystemer/html/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1" documentId="11_BEA61AB9937531F2A50A2AEEFEB4992A70D96F44" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{20A71358-860E-4971-9E5B-C4EFEB1D108B}"/>
+  <xr:revisionPtr revIDLastSave="1" documentId="11_BEA61AB9E8E5F1D2D50A2AA70EF7A61A71D96F44" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1EC15886-EC8B-4D7A-A955-C2DC3E71DCF0}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 23-09-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 24-09-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Specialsystemer">'Opdateret d. 23-09-2026'!$A$1:$BN$173</definedName>
+    <definedName name="Specialsystemer">'Opdateret d. 24-09-2026'!$A$1:$BN$173</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>
@@ -244,7 +244,7 @@
     <t>APD-DK (2.0.1)</t>
   </si>
   <si>
-    <t>Binær dokumenttransport</t>
+    <t>Binær Dokumenttransport</t>
   </si>
   <si>
     <t>BIN01 (B0131X)</t>

--- a/html/Specialsystemer_excel.XLSX
+++ b/html/Specialsystemer_excel.XLSX
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://medcomdk-my.sharepoint.com/personal/sof_medcom_dk/Documents/Dokumenter/GitHub/GodkendteSystemer/html/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1" documentId="11_BEA61AB9E8E5F1D2D50A2AA70EF7A61A71D96F44" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1EC15886-EC8B-4D7A-A955-C2DC3E71DCF0}"/>
+  <xr:revisionPtr revIDLastSave="1" documentId="11_BEA61AB9E8E5F1D2D50A2A0046F1912471D96F44" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E21F91F9-201A-4F6E-80A0-9503B529CBB1}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/html/Specialsystemer_excel.XLSX
+++ b/html/Specialsystemer_excel.XLSX
@@ -5,18 +5,18 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://medcomdk-my.sharepoint.com/personal/sof_medcom_dk/Documents/Dokumenter/GitHub/GodkendteSystemer/html/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Documents\GitHub\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1" documentId="11_BEA61AB9E8E5F1D2D50A2A0046F1912471D96F44" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E21F91F9-201A-4F6E-80A0-9503B529CBB1}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2732B803-A62C-4E43-9D85-11755F533766}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="19090" yWindow="5410" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 24-09-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 28-09-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Specialsystemer">'Opdateret d. 24-09-2026'!$A$1:$BN$173</definedName>
+    <definedName name="Specialsystemer">'Opdateret d. 28-09-2026'!$A$1:$BN$173</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>
@@ -1137,9 +1137,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:BN173"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:66" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:66" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1339,7 +1339,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="2" spans="1:66" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:66" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>66</v>
       </c>
@@ -1359,7 +1359,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="3" spans="1:66" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:66" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>71</v>
       </c>
@@ -1379,7 +1379,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="4" spans="1:66" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:66" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>73</v>
       </c>
@@ -1414,7 +1414,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="5" spans="1:66" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:66" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>75</v>
       </c>
@@ -1431,7 +1431,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="6" spans="1:66" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:66" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>77</v>
       </c>
@@ -1451,7 +1451,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="7" spans="1:66" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:66" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>79</v>
       </c>
@@ -1468,7 +1468,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="8" spans="1:66" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:66" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>82</v>
       </c>
@@ -1539,7 +1539,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="9" spans="1:66" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:66" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>84</v>
       </c>
@@ -1595,7 +1595,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="10" spans="1:66" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:66" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>86</v>
       </c>
@@ -1609,7 +1609,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="11" spans="1:66" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:66" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>88</v>
       </c>
@@ -1623,7 +1623,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="12" spans="1:66" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:66" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>90</v>
       </c>
@@ -1637,7 +1637,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="13" spans="1:66" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:66" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>92</v>
       </c>
@@ -1651,7 +1651,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="14" spans="1:66" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:66" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>92</v>
       </c>
@@ -1665,7 +1665,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="15" spans="1:66" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:66" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>95</v>
       </c>
@@ -1679,7 +1679,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="16" spans="1:66" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:66" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>97</v>
       </c>
@@ -1693,7 +1693,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="17" spans="1:66" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:66" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>99</v>
       </c>
@@ -1707,7 +1707,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="18" spans="1:66" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:66" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>101</v>
       </c>
@@ -1766,7 +1766,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="19" spans="1:66" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:66" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>103</v>
       </c>
@@ -1780,7 +1780,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="20" spans="1:66" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:66" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>105</v>
       </c>
@@ -1803,7 +1803,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="21" spans="1:66" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:66" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>105</v>
       </c>
@@ -1817,7 +1817,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="22" spans="1:66" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:66" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>108</v>
       </c>
@@ -1831,7 +1831,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="23" spans="1:66" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:66" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>110</v>
       </c>
@@ -1845,7 +1845,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="24" spans="1:66" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:66" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>112</v>
       </c>
@@ -1862,7 +1862,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="25" spans="1:66" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:66" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>114</v>
       </c>
@@ -1876,7 +1876,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="26" spans="1:66" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:66" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>116</v>
       </c>
@@ -1893,7 +1893,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="27" spans="1:66" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:66" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>118</v>
       </c>
@@ -1922,7 +1922,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="28" spans="1:66" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:66" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>118</v>
       </c>
@@ -1948,7 +1948,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="29" spans="1:66" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:66" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>121</v>
       </c>
@@ -1965,7 +1965,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="30" spans="1:66" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:66" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>121</v>
       </c>
@@ -1991,7 +1991,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="31" spans="1:66" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:66" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>125</v>
       </c>
@@ -2005,7 +2005,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="32" spans="1:66" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:66" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>125</v>
       </c>
@@ -2028,7 +2028,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="33" spans="1:66" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:66" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>128</v>
       </c>
@@ -2048,7 +2048,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="34" spans="1:66" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:66" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>128</v>
       </c>
@@ -2068,7 +2068,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="35" spans="1:66" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:66" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>131</v>
       </c>
@@ -2088,7 +2088,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="36" spans="1:66" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:66" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>133</v>
       </c>
@@ -2105,7 +2105,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="37" spans="1:66" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:66" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>133</v>
       </c>
@@ -2119,7 +2119,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="38" spans="1:66" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:66" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>133</v>
       </c>
@@ -2133,7 +2133,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="39" spans="1:66" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:66" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>137</v>
       </c>
@@ -2153,7 +2153,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="40" spans="1:66" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:66" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>139</v>
       </c>
@@ -2170,7 +2170,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="41" spans="1:66" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:66" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>139</v>
       </c>
@@ -2187,7 +2187,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="42" spans="1:66" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:66" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>142</v>
       </c>
@@ -2201,7 +2201,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="43" spans="1:66" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:66" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>142</v>
       </c>
@@ -2215,7 +2215,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="44" spans="1:66" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:66" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>145</v>
       </c>
@@ -2235,7 +2235,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="45" spans="1:66" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:66" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>145</v>
       </c>
@@ -2258,7 +2258,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="46" spans="1:66" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:66" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>148</v>
       </c>
@@ -2275,7 +2275,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="47" spans="1:66" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:66" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
         <v>150</v>
       </c>
@@ -2289,7 +2289,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="48" spans="1:66" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:66" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
         <v>150</v>
       </c>
@@ -2303,7 +2303,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="49" spans="1:65" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
         <v>153</v>
       </c>
@@ -2320,7 +2320,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="50" spans="1:65" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
         <v>155</v>
       </c>
@@ -2343,7 +2343,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="51" spans="1:65" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
         <v>157</v>
       </c>
@@ -2375,7 +2375,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="52" spans="1:65" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
         <v>157</v>
       </c>
@@ -2395,7 +2395,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="53" spans="1:65" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
         <v>160</v>
       </c>
@@ -2430,7 +2430,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="54" spans="1:65" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
         <v>162</v>
       </c>
@@ -2444,7 +2444,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="55" spans="1:65" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
         <v>164</v>
       </c>
@@ -2494,7 +2494,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="56" spans="1:65" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
         <v>166</v>
       </c>
@@ -2544,7 +2544,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="57" spans="1:65" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
         <v>168</v>
       </c>
@@ -2558,7 +2558,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="58" spans="1:65" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
         <v>170</v>
       </c>
@@ -2572,7 +2572,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="59" spans="1:65" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
         <v>170</v>
       </c>
@@ -2586,7 +2586,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="60" spans="1:65" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
         <v>173</v>
       </c>
@@ -2600,7 +2600,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="61" spans="1:65" x14ac:dyDescent="0.35">
+    <row r="61" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
         <v>175</v>
       </c>
@@ -2623,7 +2623,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="62" spans="1:65" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
         <v>177</v>
       </c>
@@ -2637,7 +2637,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="63" spans="1:65" x14ac:dyDescent="0.35">
+    <row r="63" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
         <v>179</v>
       </c>
@@ -2651,7 +2651,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="64" spans="1:65" x14ac:dyDescent="0.35">
+    <row r="64" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
         <v>181</v>
       </c>
@@ -2665,7 +2665,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="65" spans="1:66" x14ac:dyDescent="0.35">
+    <row r="65" spans="1:66" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
         <v>181</v>
       </c>
@@ -2679,7 +2679,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="66" spans="1:66" x14ac:dyDescent="0.35">
+    <row r="66" spans="1:66" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
         <v>184</v>
       </c>
@@ -2693,7 +2693,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="67" spans="1:66" x14ac:dyDescent="0.35">
+    <row r="67" spans="1:66" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
         <v>186</v>
       </c>
@@ -2752,7 +2752,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="68" spans="1:66" x14ac:dyDescent="0.35">
+    <row r="68" spans="1:66" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
         <v>188</v>
       </c>
@@ -2781,7 +2781,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="69" spans="1:66" x14ac:dyDescent="0.35">
+    <row r="69" spans="1:66" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
         <v>188</v>
       </c>
@@ -2804,7 +2804,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="70" spans="1:66" x14ac:dyDescent="0.35">
+    <row r="70" spans="1:66" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
         <v>191</v>
       </c>
@@ -2818,7 +2818,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="71" spans="1:66" x14ac:dyDescent="0.35">
+    <row r="71" spans="1:66" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
         <v>193</v>
       </c>
@@ -2838,7 +2838,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="72" spans="1:66" x14ac:dyDescent="0.35">
+    <row r="72" spans="1:66" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
         <v>195</v>
       </c>
@@ -2852,7 +2852,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="73" spans="1:66" x14ac:dyDescent="0.35">
+    <row r="73" spans="1:66" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
         <v>197</v>
       </c>
@@ -2866,7 +2866,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="74" spans="1:66" x14ac:dyDescent="0.35">
+    <row r="74" spans="1:66" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
         <v>197</v>
       </c>
@@ -2886,7 +2886,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="75" spans="1:66" x14ac:dyDescent="0.35">
+    <row r="75" spans="1:66" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
         <v>200</v>
       </c>
@@ -2900,7 +2900,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="76" spans="1:66" x14ac:dyDescent="0.35">
+    <row r="76" spans="1:66" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
         <v>202</v>
       </c>
@@ -2920,7 +2920,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="77" spans="1:66" x14ac:dyDescent="0.35">
+    <row r="77" spans="1:66" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
         <v>204</v>
       </c>
@@ -2937,7 +2937,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="78" spans="1:66" x14ac:dyDescent="0.35">
+    <row r="78" spans="1:66" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
         <v>206</v>
       </c>
@@ -2951,7 +2951,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="79" spans="1:66" x14ac:dyDescent="0.35">
+    <row r="79" spans="1:66" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
         <v>208</v>
       </c>
@@ -2965,7 +2965,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="80" spans="1:66" x14ac:dyDescent="0.35">
+    <row r="80" spans="1:66" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
         <v>210</v>
       </c>
@@ -2979,7 +2979,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="81" spans="1:65" x14ac:dyDescent="0.35">
+    <row r="81" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
         <v>66</v>
       </c>
@@ -2999,7 +2999,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="82" spans="1:65" x14ac:dyDescent="0.35">
+    <row r="82" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
         <v>71</v>
       </c>
@@ -3034,7 +3034,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="83" spans="1:65" x14ac:dyDescent="0.35">
+    <row r="83" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
         <v>73</v>
       </c>
@@ -3060,7 +3060,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="84" spans="1:65" x14ac:dyDescent="0.35">
+    <row r="84" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
         <v>75</v>
       </c>
@@ -3074,7 +3074,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="85" spans="1:65" x14ac:dyDescent="0.35">
+    <row r="85" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
         <v>77</v>
       </c>
@@ -3094,7 +3094,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="86" spans="1:65" x14ac:dyDescent="0.35">
+    <row r="86" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
         <v>79</v>
       </c>
@@ -3111,7 +3111,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="87" spans="1:65" x14ac:dyDescent="0.35">
+    <row r="87" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
         <v>213</v>
       </c>
@@ -3128,7 +3128,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="88" spans="1:65" x14ac:dyDescent="0.35">
+    <row r="88" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
         <v>215</v>
       </c>
@@ -3145,7 +3145,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="89" spans="1:65" x14ac:dyDescent="0.35">
+    <row r="89" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
         <v>215</v>
       </c>
@@ -3168,7 +3168,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="90" spans="1:65" x14ac:dyDescent="0.35">
+    <row r="90" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
         <v>218</v>
       </c>
@@ -3245,7 +3245,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="91" spans="1:65" x14ac:dyDescent="0.35">
+    <row r="91" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
         <v>82</v>
       </c>
@@ -3325,7 +3325,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="92" spans="1:65" x14ac:dyDescent="0.35">
+    <row r="92" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
         <v>84</v>
       </c>
@@ -3402,7 +3402,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="93" spans="1:65" x14ac:dyDescent="0.35">
+    <row r="93" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
         <v>86</v>
       </c>
@@ -3416,7 +3416,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="94" spans="1:65" x14ac:dyDescent="0.35">
+    <row r="94" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
         <v>88</v>
       </c>
@@ -3430,7 +3430,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="95" spans="1:65" x14ac:dyDescent="0.35">
+    <row r="95" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
         <v>90</v>
       </c>
@@ -3447,7 +3447,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="96" spans="1:65" x14ac:dyDescent="0.35">
+    <row r="96" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
         <v>90</v>
       </c>
@@ -3464,7 +3464,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="97" spans="1:61" x14ac:dyDescent="0.35">
+    <row r="97" spans="1:61" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
         <v>92</v>
       </c>
@@ -3478,7 +3478,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="98" spans="1:61" x14ac:dyDescent="0.35">
+    <row r="98" spans="1:61" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
         <v>92</v>
       </c>
@@ -3504,7 +3504,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="99" spans="1:61" x14ac:dyDescent="0.35">
+    <row r="99" spans="1:61" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
         <v>221</v>
       </c>
@@ -3521,7 +3521,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="100" spans="1:61" x14ac:dyDescent="0.35">
+    <row r="100" spans="1:61" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
         <v>223</v>
       </c>
@@ -3541,7 +3541,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="101" spans="1:61" x14ac:dyDescent="0.35">
+    <row r="101" spans="1:61" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
         <v>95</v>
       </c>
@@ -3558,7 +3558,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="102" spans="1:61" x14ac:dyDescent="0.35">
+    <row r="102" spans="1:61" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
         <v>97</v>
       </c>
@@ -3575,7 +3575,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="103" spans="1:61" x14ac:dyDescent="0.35">
+    <row r="103" spans="1:61" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
         <v>99</v>
       </c>
@@ -3589,7 +3589,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="104" spans="1:61" x14ac:dyDescent="0.35">
+    <row r="104" spans="1:61" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
         <v>101</v>
       </c>
@@ -3636,7 +3636,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="105" spans="1:61" x14ac:dyDescent="0.35">
+    <row r="105" spans="1:61" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
         <v>103</v>
       </c>
@@ -3656,7 +3656,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="106" spans="1:61" x14ac:dyDescent="0.35">
+    <row r="106" spans="1:61" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
         <v>103</v>
       </c>
@@ -3676,7 +3676,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="107" spans="1:61" x14ac:dyDescent="0.35">
+    <row r="107" spans="1:61" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
         <v>226</v>
       </c>
@@ -3690,7 +3690,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="108" spans="1:61" x14ac:dyDescent="0.35">
+    <row r="108" spans="1:61" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
         <v>105</v>
       </c>
@@ -3710,7 +3710,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="109" spans="1:61" x14ac:dyDescent="0.35">
+    <row r="109" spans="1:61" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
         <v>105</v>
       </c>
@@ -3724,7 +3724,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="110" spans="1:61" x14ac:dyDescent="0.35">
+    <row r="110" spans="1:61" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
         <v>108</v>
       </c>
@@ -3744,7 +3744,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="111" spans="1:61" x14ac:dyDescent="0.35">
+    <row r="111" spans="1:61" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
         <v>110</v>
       </c>
@@ -3764,7 +3764,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="112" spans="1:61" x14ac:dyDescent="0.35">
+    <row r="112" spans="1:61" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
         <v>112</v>
       </c>
@@ -3781,7 +3781,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="113" spans="1:60" x14ac:dyDescent="0.35">
+    <row r="113" spans="1:60" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
         <v>114</v>
       </c>
@@ -3801,7 +3801,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="114" spans="1:60" x14ac:dyDescent="0.35">
+    <row r="114" spans="1:60" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
         <v>116</v>
       </c>
@@ -3815,7 +3815,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="115" spans="1:60" x14ac:dyDescent="0.35">
+    <row r="115" spans="1:60" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
         <v>116</v>
       </c>
@@ -3829,7 +3829,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="116" spans="1:60" x14ac:dyDescent="0.35">
+    <row r="116" spans="1:60" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
         <v>118</v>
       </c>
@@ -3849,7 +3849,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="117" spans="1:60" x14ac:dyDescent="0.35">
+    <row r="117" spans="1:60" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
         <v>118</v>
       </c>
@@ -3869,7 +3869,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="118" spans="1:60" x14ac:dyDescent="0.35">
+    <row r="118" spans="1:60" x14ac:dyDescent="0.25">
       <c r="A118" t="s">
         <v>121</v>
       </c>
@@ -3883,7 +3883,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="119" spans="1:60" x14ac:dyDescent="0.35">
+    <row r="119" spans="1:60" x14ac:dyDescent="0.25">
       <c r="A119" t="s">
         <v>121</v>
       </c>
@@ -3909,7 +3909,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="120" spans="1:60" x14ac:dyDescent="0.35">
+    <row r="120" spans="1:60" x14ac:dyDescent="0.25">
       <c r="A120" t="s">
         <v>125</v>
       </c>
@@ -3935,7 +3935,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="121" spans="1:60" x14ac:dyDescent="0.35">
+    <row r="121" spans="1:60" x14ac:dyDescent="0.25">
       <c r="A121" t="s">
         <v>128</v>
       </c>
@@ -3958,7 +3958,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="122" spans="1:60" x14ac:dyDescent="0.35">
+    <row r="122" spans="1:60" x14ac:dyDescent="0.25">
       <c r="A122" t="s">
         <v>128</v>
       </c>
@@ -3981,7 +3981,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="123" spans="1:60" x14ac:dyDescent="0.35">
+    <row r="123" spans="1:60" x14ac:dyDescent="0.25">
       <c r="A123" t="s">
         <v>131</v>
       </c>
@@ -4004,7 +4004,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="124" spans="1:60" x14ac:dyDescent="0.35">
+    <row r="124" spans="1:60" x14ac:dyDescent="0.25">
       <c r="A124" t="s">
         <v>133</v>
       </c>
@@ -4024,7 +4024,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="125" spans="1:60" x14ac:dyDescent="0.35">
+    <row r="125" spans="1:60" x14ac:dyDescent="0.25">
       <c r="A125" t="s">
         <v>133</v>
       </c>
@@ -4041,7 +4041,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="126" spans="1:60" x14ac:dyDescent="0.35">
+    <row r="126" spans="1:60" x14ac:dyDescent="0.25">
       <c r="A126" t="s">
         <v>133</v>
       </c>
@@ -4058,7 +4058,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="127" spans="1:60" x14ac:dyDescent="0.35">
+    <row r="127" spans="1:60" x14ac:dyDescent="0.25">
       <c r="A127" t="s">
         <v>137</v>
       </c>
@@ -4081,7 +4081,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="128" spans="1:60" x14ac:dyDescent="0.35">
+    <row r="128" spans="1:60" x14ac:dyDescent="0.25">
       <c r="A128" t="s">
         <v>139</v>
       </c>
@@ -4101,7 +4101,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="129" spans="1:60" x14ac:dyDescent="0.35">
+    <row r="129" spans="1:60" x14ac:dyDescent="0.25">
       <c r="A129" t="s">
         <v>139</v>
       </c>
@@ -4124,7 +4124,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="130" spans="1:60" x14ac:dyDescent="0.35">
+    <row r="130" spans="1:60" x14ac:dyDescent="0.25">
       <c r="A130" t="s">
         <v>142</v>
       </c>
@@ -4138,7 +4138,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="131" spans="1:60" x14ac:dyDescent="0.35">
+    <row r="131" spans="1:60" x14ac:dyDescent="0.25">
       <c r="A131" t="s">
         <v>145</v>
       </c>
@@ -4152,7 +4152,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="132" spans="1:60" x14ac:dyDescent="0.35">
+    <row r="132" spans="1:60" x14ac:dyDescent="0.25">
       <c r="A132" t="s">
         <v>145</v>
       </c>
@@ -4184,7 +4184,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="133" spans="1:60" x14ac:dyDescent="0.35">
+    <row r="133" spans="1:60" x14ac:dyDescent="0.25">
       <c r="A133" t="s">
         <v>229</v>
       </c>
@@ -4201,7 +4201,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="134" spans="1:60" x14ac:dyDescent="0.35">
+    <row r="134" spans="1:60" x14ac:dyDescent="0.25">
       <c r="A134" t="s">
         <v>231</v>
       </c>
@@ -4215,7 +4215,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="135" spans="1:60" x14ac:dyDescent="0.35">
+    <row r="135" spans="1:60" x14ac:dyDescent="0.25">
       <c r="A135" t="s">
         <v>233</v>
       </c>
@@ -4232,7 +4232,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="136" spans="1:60" x14ac:dyDescent="0.35">
+    <row r="136" spans="1:60" x14ac:dyDescent="0.25">
       <c r="A136" t="s">
         <v>235</v>
       </c>
@@ -4249,7 +4249,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="137" spans="1:60" x14ac:dyDescent="0.35">
+    <row r="137" spans="1:60" x14ac:dyDescent="0.25">
       <c r="A137" t="s">
         <v>235</v>
       </c>
@@ -4269,7 +4269,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="138" spans="1:60" x14ac:dyDescent="0.35">
+    <row r="138" spans="1:60" x14ac:dyDescent="0.25">
       <c r="A138" t="s">
         <v>238</v>
       </c>
@@ -4283,7 +4283,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="139" spans="1:60" x14ac:dyDescent="0.35">
+    <row r="139" spans="1:60" x14ac:dyDescent="0.25">
       <c r="A139" t="s">
         <v>155</v>
       </c>
@@ -4297,7 +4297,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="140" spans="1:60" x14ac:dyDescent="0.35">
+    <row r="140" spans="1:60" x14ac:dyDescent="0.25">
       <c r="A140" t="s">
         <v>241</v>
       </c>
@@ -4311,7 +4311,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="141" spans="1:60" x14ac:dyDescent="0.35">
+    <row r="141" spans="1:60" x14ac:dyDescent="0.25">
       <c r="A141" t="s">
         <v>243</v>
       </c>
@@ -4325,7 +4325,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="142" spans="1:60" x14ac:dyDescent="0.35">
+    <row r="142" spans="1:60" x14ac:dyDescent="0.25">
       <c r="A142" t="s">
         <v>157</v>
       </c>
@@ -4357,7 +4357,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="143" spans="1:60" x14ac:dyDescent="0.35">
+    <row r="143" spans="1:60" x14ac:dyDescent="0.25">
       <c r="A143" t="s">
         <v>157</v>
       </c>
@@ -4374,7 +4374,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="144" spans="1:60" x14ac:dyDescent="0.35">
+    <row r="144" spans="1:60" x14ac:dyDescent="0.25">
       <c r="A144" t="s">
         <v>160</v>
       </c>
@@ -4406,7 +4406,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="145" spans="1:57" x14ac:dyDescent="0.35">
+    <row r="145" spans="1:57" x14ac:dyDescent="0.25">
       <c r="A145" t="s">
         <v>245</v>
       </c>
@@ -4477,7 +4477,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="146" spans="1:57" x14ac:dyDescent="0.35">
+    <row r="146" spans="1:57" x14ac:dyDescent="0.25">
       <c r="A146" t="s">
         <v>164</v>
       </c>
@@ -4551,7 +4551,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="147" spans="1:57" x14ac:dyDescent="0.35">
+    <row r="147" spans="1:57" x14ac:dyDescent="0.25">
       <c r="A147" t="s">
         <v>166</v>
       </c>
@@ -4619,7 +4619,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="148" spans="1:57" x14ac:dyDescent="0.35">
+    <row r="148" spans="1:57" x14ac:dyDescent="0.25">
       <c r="A148" t="s">
         <v>168</v>
       </c>
@@ -4633,7 +4633,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="149" spans="1:57" x14ac:dyDescent="0.35">
+    <row r="149" spans="1:57" x14ac:dyDescent="0.25">
       <c r="A149" t="s">
         <v>168</v>
       </c>
@@ -4653,7 +4653,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="150" spans="1:57" x14ac:dyDescent="0.35">
+    <row r="150" spans="1:57" x14ac:dyDescent="0.25">
       <c r="A150" t="s">
         <v>170</v>
       </c>
@@ -4670,7 +4670,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="151" spans="1:57" x14ac:dyDescent="0.35">
+    <row r="151" spans="1:57" x14ac:dyDescent="0.25">
       <c r="A151" t="s">
         <v>170</v>
       </c>
@@ -4687,7 +4687,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="152" spans="1:57" x14ac:dyDescent="0.35">
+    <row r="152" spans="1:57" x14ac:dyDescent="0.25">
       <c r="A152" t="s">
         <v>173</v>
       </c>
@@ -4701,7 +4701,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="153" spans="1:57" x14ac:dyDescent="0.35">
+    <row r="153" spans="1:57" x14ac:dyDescent="0.25">
       <c r="A153" t="s">
         <v>248</v>
       </c>
@@ -4718,7 +4718,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="154" spans="1:57" x14ac:dyDescent="0.35">
+    <row r="154" spans="1:57" x14ac:dyDescent="0.25">
       <c r="A154" t="s">
         <v>177</v>
       </c>
@@ -4735,7 +4735,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="155" spans="1:57" x14ac:dyDescent="0.35">
+    <row r="155" spans="1:57" x14ac:dyDescent="0.25">
       <c r="A155" t="s">
         <v>177</v>
       </c>
@@ -4749,7 +4749,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="156" spans="1:57" x14ac:dyDescent="0.35">
+    <row r="156" spans="1:57" x14ac:dyDescent="0.25">
       <c r="A156" t="s">
         <v>179</v>
       </c>
@@ -4769,7 +4769,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="157" spans="1:57" x14ac:dyDescent="0.35">
+    <row r="157" spans="1:57" x14ac:dyDescent="0.25">
       <c r="A157" t="s">
         <v>181</v>
       </c>
@@ -4783,7 +4783,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="158" spans="1:57" x14ac:dyDescent="0.35">
+    <row r="158" spans="1:57" x14ac:dyDescent="0.25">
       <c r="A158" t="s">
         <v>181</v>
       </c>
@@ -4797,7 +4797,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="159" spans="1:57" x14ac:dyDescent="0.35">
+    <row r="159" spans="1:57" x14ac:dyDescent="0.25">
       <c r="A159" t="s">
         <v>184</v>
       </c>
@@ -4811,7 +4811,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="160" spans="1:57" x14ac:dyDescent="0.35">
+    <row r="160" spans="1:57" x14ac:dyDescent="0.25">
       <c r="A160" t="s">
         <v>186</v>
       </c>
@@ -4852,7 +4852,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="161" spans="1:60" x14ac:dyDescent="0.35">
+    <row r="161" spans="1:60" x14ac:dyDescent="0.25">
       <c r="A161" t="s">
         <v>188</v>
       </c>
@@ -4887,7 +4887,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="162" spans="1:60" x14ac:dyDescent="0.35">
+    <row r="162" spans="1:60" x14ac:dyDescent="0.25">
       <c r="A162" t="s">
         <v>188</v>
       </c>
@@ -4904,7 +4904,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="163" spans="1:60" x14ac:dyDescent="0.35">
+    <row r="163" spans="1:60" x14ac:dyDescent="0.25">
       <c r="A163" t="s">
         <v>193</v>
       </c>
@@ -4918,7 +4918,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="164" spans="1:60" x14ac:dyDescent="0.35">
+    <row r="164" spans="1:60" x14ac:dyDescent="0.25">
       <c r="A164" t="s">
         <v>193</v>
       </c>
@@ -4938,7 +4938,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="165" spans="1:60" x14ac:dyDescent="0.35">
+    <row r="165" spans="1:60" x14ac:dyDescent="0.25">
       <c r="A165" t="s">
         <v>197</v>
       </c>
@@ -4952,7 +4952,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="166" spans="1:60" x14ac:dyDescent="0.35">
+    <row r="166" spans="1:60" x14ac:dyDescent="0.25">
       <c r="A166" t="s">
         <v>197</v>
       </c>
@@ -4969,7 +4969,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="167" spans="1:60" x14ac:dyDescent="0.35">
+    <row r="167" spans="1:60" x14ac:dyDescent="0.25">
       <c r="A167" t="s">
         <v>202</v>
       </c>
@@ -4995,7 +4995,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="168" spans="1:60" x14ac:dyDescent="0.35">
+    <row r="168" spans="1:60" x14ac:dyDescent="0.25">
       <c r="A168" t="s">
         <v>204</v>
       </c>
@@ -5015,7 +5015,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="169" spans="1:60" x14ac:dyDescent="0.35">
+    <row r="169" spans="1:60" x14ac:dyDescent="0.25">
       <c r="A169" t="s">
         <v>208</v>
       </c>
@@ -5035,7 +5035,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="170" spans="1:60" x14ac:dyDescent="0.35">
+    <row r="170" spans="1:60" x14ac:dyDescent="0.25">
       <c r="A170" t="s">
         <v>208</v>
       </c>
@@ -5061,7 +5061,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="171" spans="1:60" x14ac:dyDescent="0.35">
+    <row r="171" spans="1:60" x14ac:dyDescent="0.25">
       <c r="A171" t="s">
         <v>253</v>
       </c>
@@ -5078,7 +5078,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="172" spans="1:60" x14ac:dyDescent="0.35">
+    <row r="172" spans="1:60" x14ac:dyDescent="0.25">
       <c r="A172" t="s">
         <v>210</v>
       </c>
@@ -5104,7 +5104,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="173" spans="1:60" x14ac:dyDescent="0.35">
+    <row r="173" spans="1:60" x14ac:dyDescent="0.25">
       <c r="A173" t="s">
         <v>255</v>
       </c>

--- a/html/Specialsystemer_excel.XLSX
+++ b/html/Specialsystemer_excel.XLSX
@@ -1,22 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30430"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Documents\GitHub\GodkendteSystemer\html\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://medcomdk-my.sharepoint.com/personal/sof_medcom_dk/Documents/Dokumenter/GitHub/GodkendteSystemer/html/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2732B803-A62C-4E43-9D85-11755F533766}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="1" documentId="11_BEA61AB9E8E5F1D2D50A2AC236F496C670D96F44" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9FF510F7-3FE5-42D0-8B76-754DF9CCAE7B}"/>
   <bookViews>
-    <workbookView xWindow="19090" yWindow="5410" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="760" yWindow="760" windowWidth="14400" windowHeight="8170" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 28-09-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 02-10-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Specialsystemer">'Opdateret d. 28-09-2026'!$A$1:$BN$173</definedName>
+    <definedName name="Specialsystemer">'Opdateret d. 02-10-2026'!$A$1:$BN$173</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>
@@ -1137,9 +1137,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:BN173"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1" spans="1:66" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:66" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1339,7 +1339,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="2" spans="1:66" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:66" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>66</v>
       </c>
@@ -1359,7 +1359,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="3" spans="1:66" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:66" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>71</v>
       </c>
@@ -1379,7 +1379,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="4" spans="1:66" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:66" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>73</v>
       </c>
@@ -1414,7 +1414,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="5" spans="1:66" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:66" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>75</v>
       </c>
@@ -1431,7 +1431,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="6" spans="1:66" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:66" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>77</v>
       </c>
@@ -1451,7 +1451,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="7" spans="1:66" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:66" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>79</v>
       </c>
@@ -1468,7 +1468,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="8" spans="1:66" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:66" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>82</v>
       </c>
@@ -1539,7 +1539,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="9" spans="1:66" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:66" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>84</v>
       </c>
@@ -1595,7 +1595,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="10" spans="1:66" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:66" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>86</v>
       </c>
@@ -1609,7 +1609,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="11" spans="1:66" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:66" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>88</v>
       </c>
@@ -1623,7 +1623,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="12" spans="1:66" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:66" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>90</v>
       </c>
@@ -1637,7 +1637,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="13" spans="1:66" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:66" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>92</v>
       </c>
@@ -1651,7 +1651,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="14" spans="1:66" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:66" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>92</v>
       </c>
@@ -1665,7 +1665,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="15" spans="1:66" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:66" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>95</v>
       </c>
@@ -1679,7 +1679,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="16" spans="1:66" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:66" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
         <v>97</v>
       </c>
@@ -1693,7 +1693,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="17" spans="1:66" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:66" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
         <v>99</v>
       </c>
@@ -1707,7 +1707,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="18" spans="1:66" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:66" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
         <v>101</v>
       </c>
@@ -1766,7 +1766,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="19" spans="1:66" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:66" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
         <v>103</v>
       </c>
@@ -1780,7 +1780,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="20" spans="1:66" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:66" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
         <v>105</v>
       </c>
@@ -1803,7 +1803,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="21" spans="1:66" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:66" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
         <v>105</v>
       </c>
@@ -1817,7 +1817,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="22" spans="1:66" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:66" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
         <v>108</v>
       </c>
@@ -1831,7 +1831,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="23" spans="1:66" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:66" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
         <v>110</v>
       </c>
@@ -1845,7 +1845,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="24" spans="1:66" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:66" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
         <v>112</v>
       </c>
@@ -1862,7 +1862,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="25" spans="1:66" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:66" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
         <v>114</v>
       </c>
@@ -1876,7 +1876,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="26" spans="1:66" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:66" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
         <v>116</v>
       </c>
@@ -1893,7 +1893,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="27" spans="1:66" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:66" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
         <v>118</v>
       </c>
@@ -1922,7 +1922,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="28" spans="1:66" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:66" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
         <v>118</v>
       </c>
@@ -1948,7 +1948,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="29" spans="1:66" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:66" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
         <v>121</v>
       </c>
@@ -1965,7 +1965,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="30" spans="1:66" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:66" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
         <v>121</v>
       </c>
@@ -1991,7 +1991,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="31" spans="1:66" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:66" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
         <v>125</v>
       </c>
@@ -2005,7 +2005,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="32" spans="1:66" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:66" x14ac:dyDescent="0.35">
       <c r="A32" t="s">
         <v>125</v>
       </c>
@@ -2028,7 +2028,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="33" spans="1:66" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:66" x14ac:dyDescent="0.35">
       <c r="A33" t="s">
         <v>128</v>
       </c>
@@ -2048,7 +2048,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="34" spans="1:66" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:66" x14ac:dyDescent="0.35">
       <c r="A34" t="s">
         <v>128</v>
       </c>
@@ -2068,7 +2068,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="35" spans="1:66" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:66" x14ac:dyDescent="0.35">
       <c r="A35" t="s">
         <v>131</v>
       </c>
@@ -2088,7 +2088,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="36" spans="1:66" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:66" x14ac:dyDescent="0.35">
       <c r="A36" t="s">
         <v>133</v>
       </c>
@@ -2105,7 +2105,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="37" spans="1:66" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:66" x14ac:dyDescent="0.35">
       <c r="A37" t="s">
         <v>133</v>
       </c>
@@ -2119,7 +2119,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="38" spans="1:66" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:66" x14ac:dyDescent="0.35">
       <c r="A38" t="s">
         <v>133</v>
       </c>
@@ -2133,7 +2133,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="39" spans="1:66" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:66" x14ac:dyDescent="0.35">
       <c r="A39" t="s">
         <v>137</v>
       </c>
@@ -2153,7 +2153,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="40" spans="1:66" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:66" x14ac:dyDescent="0.35">
       <c r="A40" t="s">
         <v>139</v>
       </c>
@@ -2170,7 +2170,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="41" spans="1:66" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:66" x14ac:dyDescent="0.35">
       <c r="A41" t="s">
         <v>139</v>
       </c>
@@ -2187,7 +2187,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="42" spans="1:66" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:66" x14ac:dyDescent="0.35">
       <c r="A42" t="s">
         <v>142</v>
       </c>
@@ -2201,7 +2201,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="43" spans="1:66" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:66" x14ac:dyDescent="0.35">
       <c r="A43" t="s">
         <v>142</v>
       </c>
@@ -2215,7 +2215,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="44" spans="1:66" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:66" x14ac:dyDescent="0.35">
       <c r="A44" t="s">
         <v>145</v>
       </c>
@@ -2235,7 +2235,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="45" spans="1:66" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:66" x14ac:dyDescent="0.35">
       <c r="A45" t="s">
         <v>145</v>
       </c>
@@ -2258,7 +2258,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="46" spans="1:66" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:66" x14ac:dyDescent="0.35">
       <c r="A46" t="s">
         <v>148</v>
       </c>
@@ -2275,7 +2275,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="47" spans="1:66" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:66" x14ac:dyDescent="0.35">
       <c r="A47" t="s">
         <v>150</v>
       </c>
@@ -2289,7 +2289,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="48" spans="1:66" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:66" x14ac:dyDescent="0.35">
       <c r="A48" t="s">
         <v>150</v>
       </c>
@@ -2303,7 +2303,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="49" spans="1:65" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:65" x14ac:dyDescent="0.35">
       <c r="A49" t="s">
         <v>153</v>
       </c>
@@ -2320,7 +2320,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="50" spans="1:65" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:65" x14ac:dyDescent="0.35">
       <c r="A50" t="s">
         <v>155</v>
       </c>
@@ -2343,7 +2343,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="51" spans="1:65" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:65" x14ac:dyDescent="0.35">
       <c r="A51" t="s">
         <v>157</v>
       </c>
@@ -2375,7 +2375,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="52" spans="1:65" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:65" x14ac:dyDescent="0.35">
       <c r="A52" t="s">
         <v>157</v>
       </c>
@@ -2395,7 +2395,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="53" spans="1:65" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:65" x14ac:dyDescent="0.35">
       <c r="A53" t="s">
         <v>160</v>
       </c>
@@ -2430,7 +2430,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="54" spans="1:65" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:65" x14ac:dyDescent="0.35">
       <c r="A54" t="s">
         <v>162</v>
       </c>
@@ -2444,7 +2444,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="55" spans="1:65" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:65" x14ac:dyDescent="0.35">
       <c r="A55" t="s">
         <v>164</v>
       </c>
@@ -2494,7 +2494,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="56" spans="1:65" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:65" x14ac:dyDescent="0.35">
       <c r="A56" t="s">
         <v>166</v>
       </c>
@@ -2544,7 +2544,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="57" spans="1:65" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:65" x14ac:dyDescent="0.35">
       <c r="A57" t="s">
         <v>168</v>
       </c>
@@ -2558,7 +2558,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="58" spans="1:65" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:65" x14ac:dyDescent="0.35">
       <c r="A58" t="s">
         <v>170</v>
       </c>
@@ -2572,7 +2572,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="59" spans="1:65" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:65" x14ac:dyDescent="0.35">
       <c r="A59" t="s">
         <v>170</v>
       </c>
@@ -2586,7 +2586,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="60" spans="1:65" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:65" x14ac:dyDescent="0.35">
       <c r="A60" t="s">
         <v>173</v>
       </c>
@@ -2600,7 +2600,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="61" spans="1:65" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:65" x14ac:dyDescent="0.35">
       <c r="A61" t="s">
         <v>175</v>
       </c>
@@ -2623,7 +2623,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="62" spans="1:65" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:65" x14ac:dyDescent="0.35">
       <c r="A62" t="s">
         <v>177</v>
       </c>
@@ -2637,7 +2637,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="63" spans="1:65" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:65" x14ac:dyDescent="0.35">
       <c r="A63" t="s">
         <v>179</v>
       </c>
@@ -2651,7 +2651,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="64" spans="1:65" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:65" x14ac:dyDescent="0.35">
       <c r="A64" t="s">
         <v>181</v>
       </c>
@@ -2665,7 +2665,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="65" spans="1:66" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:66" x14ac:dyDescent="0.35">
       <c r="A65" t="s">
         <v>181</v>
       </c>
@@ -2679,7 +2679,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="66" spans="1:66" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:66" x14ac:dyDescent="0.35">
       <c r="A66" t="s">
         <v>184</v>
       </c>
@@ -2693,7 +2693,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="67" spans="1:66" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:66" x14ac:dyDescent="0.35">
       <c r="A67" t="s">
         <v>186</v>
       </c>
@@ -2752,7 +2752,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="68" spans="1:66" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:66" x14ac:dyDescent="0.35">
       <c r="A68" t="s">
         <v>188</v>
       </c>
@@ -2781,7 +2781,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="69" spans="1:66" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:66" x14ac:dyDescent="0.35">
       <c r="A69" t="s">
         <v>188</v>
       </c>
@@ -2804,7 +2804,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="70" spans="1:66" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:66" x14ac:dyDescent="0.35">
       <c r="A70" t="s">
         <v>191</v>
       </c>
@@ -2818,7 +2818,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="71" spans="1:66" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:66" x14ac:dyDescent="0.35">
       <c r="A71" t="s">
         <v>193</v>
       </c>
@@ -2838,7 +2838,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="72" spans="1:66" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:66" x14ac:dyDescent="0.35">
       <c r="A72" t="s">
         <v>195</v>
       </c>
@@ -2852,7 +2852,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="73" spans="1:66" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:66" x14ac:dyDescent="0.35">
       <c r="A73" t="s">
         <v>197</v>
       </c>
@@ -2866,7 +2866,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="74" spans="1:66" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:66" x14ac:dyDescent="0.35">
       <c r="A74" t="s">
         <v>197</v>
       </c>
@@ -2886,7 +2886,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="75" spans="1:66" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:66" x14ac:dyDescent="0.35">
       <c r="A75" t="s">
         <v>200</v>
       </c>
@@ -2900,7 +2900,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="76" spans="1:66" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:66" x14ac:dyDescent="0.35">
       <c r="A76" t="s">
         <v>202</v>
       </c>
@@ -2920,7 +2920,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="77" spans="1:66" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:66" x14ac:dyDescent="0.35">
       <c r="A77" t="s">
         <v>204</v>
       </c>
@@ -2937,7 +2937,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="78" spans="1:66" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:66" x14ac:dyDescent="0.35">
       <c r="A78" t="s">
         <v>206</v>
       </c>
@@ -2951,7 +2951,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="79" spans="1:66" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:66" x14ac:dyDescent="0.35">
       <c r="A79" t="s">
         <v>208</v>
       </c>
@@ -2965,7 +2965,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="80" spans="1:66" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:66" x14ac:dyDescent="0.35">
       <c r="A80" t="s">
         <v>210</v>
       </c>
@@ -2979,7 +2979,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="81" spans="1:65" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:65" x14ac:dyDescent="0.35">
       <c r="A81" t="s">
         <v>66</v>
       </c>
@@ -2999,7 +2999,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="82" spans="1:65" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:65" x14ac:dyDescent="0.35">
       <c r="A82" t="s">
         <v>71</v>
       </c>
@@ -3034,7 +3034,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="83" spans="1:65" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:65" x14ac:dyDescent="0.35">
       <c r="A83" t="s">
         <v>73</v>
       </c>
@@ -3060,7 +3060,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="84" spans="1:65" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:65" x14ac:dyDescent="0.35">
       <c r="A84" t="s">
         <v>75</v>
       </c>
@@ -3074,7 +3074,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="85" spans="1:65" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:65" x14ac:dyDescent="0.35">
       <c r="A85" t="s">
         <v>77</v>
       </c>
@@ -3094,7 +3094,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="86" spans="1:65" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:65" x14ac:dyDescent="0.35">
       <c r="A86" t="s">
         <v>79</v>
       </c>
@@ -3111,7 +3111,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="87" spans="1:65" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:65" x14ac:dyDescent="0.35">
       <c r="A87" t="s">
         <v>213</v>
       </c>
@@ -3128,7 +3128,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="88" spans="1:65" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:65" x14ac:dyDescent="0.35">
       <c r="A88" t="s">
         <v>215</v>
       </c>
@@ -3145,7 +3145,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="89" spans="1:65" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:65" x14ac:dyDescent="0.35">
       <c r="A89" t="s">
         <v>215</v>
       </c>
@@ -3168,7 +3168,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="90" spans="1:65" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:65" x14ac:dyDescent="0.35">
       <c r="A90" t="s">
         <v>218</v>
       </c>
@@ -3245,7 +3245,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="91" spans="1:65" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:65" x14ac:dyDescent="0.35">
       <c r="A91" t="s">
         <v>82</v>
       </c>
@@ -3325,7 +3325,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="92" spans="1:65" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:65" x14ac:dyDescent="0.35">
       <c r="A92" t="s">
         <v>84</v>
       </c>
@@ -3402,7 +3402,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="93" spans="1:65" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:65" x14ac:dyDescent="0.35">
       <c r="A93" t="s">
         <v>86</v>
       </c>
@@ -3416,7 +3416,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="94" spans="1:65" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:65" x14ac:dyDescent="0.35">
       <c r="A94" t="s">
         <v>88</v>
       </c>
@@ -3430,7 +3430,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="95" spans="1:65" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:65" x14ac:dyDescent="0.35">
       <c r="A95" t="s">
         <v>90</v>
       </c>
@@ -3447,7 +3447,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="96" spans="1:65" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:65" x14ac:dyDescent="0.35">
       <c r="A96" t="s">
         <v>90</v>
       </c>
@@ -3464,7 +3464,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="97" spans="1:61" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:61" x14ac:dyDescent="0.35">
       <c r="A97" t="s">
         <v>92</v>
       </c>
@@ -3478,7 +3478,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="98" spans="1:61" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:61" x14ac:dyDescent="0.35">
       <c r="A98" t="s">
         <v>92</v>
       </c>
@@ -3504,7 +3504,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="99" spans="1:61" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:61" x14ac:dyDescent="0.35">
       <c r="A99" t="s">
         <v>221</v>
       </c>
@@ -3521,7 +3521,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="100" spans="1:61" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:61" x14ac:dyDescent="0.35">
       <c r="A100" t="s">
         <v>223</v>
       </c>
@@ -3541,7 +3541,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="101" spans="1:61" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:61" x14ac:dyDescent="0.35">
       <c r="A101" t="s">
         <v>95</v>
       </c>
@@ -3558,7 +3558,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="102" spans="1:61" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:61" x14ac:dyDescent="0.35">
       <c r="A102" t="s">
         <v>97</v>
       </c>
@@ -3575,7 +3575,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="103" spans="1:61" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:61" x14ac:dyDescent="0.35">
       <c r="A103" t="s">
         <v>99</v>
       </c>
@@ -3589,7 +3589,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="104" spans="1:61" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:61" x14ac:dyDescent="0.35">
       <c r="A104" t="s">
         <v>101</v>
       </c>
@@ -3636,7 +3636,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="105" spans="1:61" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:61" x14ac:dyDescent="0.35">
       <c r="A105" t="s">
         <v>103</v>
       </c>
@@ -3656,7 +3656,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="106" spans="1:61" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:61" x14ac:dyDescent="0.35">
       <c r="A106" t="s">
         <v>103</v>
       </c>
@@ -3676,7 +3676,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="107" spans="1:61" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:61" x14ac:dyDescent="0.35">
       <c r="A107" t="s">
         <v>226</v>
       </c>
@@ -3690,7 +3690,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="108" spans="1:61" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:61" x14ac:dyDescent="0.35">
       <c r="A108" t="s">
         <v>105</v>
       </c>
@@ -3710,7 +3710,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="109" spans="1:61" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:61" x14ac:dyDescent="0.35">
       <c r="A109" t="s">
         <v>105</v>
       </c>
@@ -3724,7 +3724,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="110" spans="1:61" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:61" x14ac:dyDescent="0.35">
       <c r="A110" t="s">
         <v>108</v>
       </c>
@@ -3744,7 +3744,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="111" spans="1:61" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:61" x14ac:dyDescent="0.35">
       <c r="A111" t="s">
         <v>110</v>
       </c>
@@ -3764,7 +3764,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="112" spans="1:61" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:61" x14ac:dyDescent="0.35">
       <c r="A112" t="s">
         <v>112</v>
       </c>
@@ -3781,7 +3781,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="113" spans="1:60" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:60" x14ac:dyDescent="0.35">
       <c r="A113" t="s">
         <v>114</v>
       </c>
@@ -3801,7 +3801,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="114" spans="1:60" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:60" x14ac:dyDescent="0.35">
       <c r="A114" t="s">
         <v>116</v>
       </c>
@@ -3815,7 +3815,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="115" spans="1:60" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:60" x14ac:dyDescent="0.35">
       <c r="A115" t="s">
         <v>116</v>
       </c>
@@ -3829,7 +3829,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="116" spans="1:60" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:60" x14ac:dyDescent="0.35">
       <c r="A116" t="s">
         <v>118</v>
       </c>
@@ -3849,7 +3849,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="117" spans="1:60" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:60" x14ac:dyDescent="0.35">
       <c r="A117" t="s">
         <v>118</v>
       </c>
@@ -3869,7 +3869,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="118" spans="1:60" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:60" x14ac:dyDescent="0.35">
       <c r="A118" t="s">
         <v>121</v>
       </c>
@@ -3883,7 +3883,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="119" spans="1:60" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:60" x14ac:dyDescent="0.35">
       <c r="A119" t="s">
         <v>121</v>
       </c>
@@ -3909,7 +3909,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="120" spans="1:60" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:60" x14ac:dyDescent="0.35">
       <c r="A120" t="s">
         <v>125</v>
       </c>
@@ -3935,7 +3935,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="121" spans="1:60" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:60" x14ac:dyDescent="0.35">
       <c r="A121" t="s">
         <v>128</v>
       </c>
@@ -3958,7 +3958,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="122" spans="1:60" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:60" x14ac:dyDescent="0.35">
       <c r="A122" t="s">
         <v>128</v>
       </c>
@@ -3981,7 +3981,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="123" spans="1:60" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:60" x14ac:dyDescent="0.35">
       <c r="A123" t="s">
         <v>131</v>
       </c>
@@ -4004,7 +4004,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="124" spans="1:60" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:60" x14ac:dyDescent="0.35">
       <c r="A124" t="s">
         <v>133</v>
       </c>
@@ -4024,7 +4024,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="125" spans="1:60" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:60" x14ac:dyDescent="0.35">
       <c r="A125" t="s">
         <v>133</v>
       </c>
@@ -4041,7 +4041,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="126" spans="1:60" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:60" x14ac:dyDescent="0.35">
       <c r="A126" t="s">
         <v>133</v>
       </c>
@@ -4058,7 +4058,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="127" spans="1:60" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:60" x14ac:dyDescent="0.35">
       <c r="A127" t="s">
         <v>137</v>
       </c>
@@ -4081,7 +4081,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="128" spans="1:60" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:60" x14ac:dyDescent="0.35">
       <c r="A128" t="s">
         <v>139</v>
       </c>
@@ -4101,7 +4101,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="129" spans="1:60" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:60" x14ac:dyDescent="0.35">
       <c r="A129" t="s">
         <v>139</v>
       </c>
@@ -4124,7 +4124,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="130" spans="1:60" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:60" x14ac:dyDescent="0.35">
       <c r="A130" t="s">
         <v>142</v>
       </c>
@@ -4138,7 +4138,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="131" spans="1:60" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:60" x14ac:dyDescent="0.35">
       <c r="A131" t="s">
         <v>145</v>
       </c>
@@ -4152,7 +4152,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="132" spans="1:60" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:60" x14ac:dyDescent="0.35">
       <c r="A132" t="s">
         <v>145</v>
       </c>
@@ -4184,7 +4184,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="133" spans="1:60" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:60" x14ac:dyDescent="0.35">
       <c r="A133" t="s">
         <v>229</v>
       </c>
@@ -4201,7 +4201,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="134" spans="1:60" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:60" x14ac:dyDescent="0.35">
       <c r="A134" t="s">
         <v>231</v>
       </c>
@@ -4215,7 +4215,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="135" spans="1:60" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:60" x14ac:dyDescent="0.35">
       <c r="A135" t="s">
         <v>233</v>
       </c>
@@ -4232,7 +4232,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="136" spans="1:60" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:60" x14ac:dyDescent="0.35">
       <c r="A136" t="s">
         <v>235</v>
       </c>
@@ -4249,7 +4249,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="137" spans="1:60" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:60" x14ac:dyDescent="0.35">
       <c r="A137" t="s">
         <v>235</v>
       </c>
@@ -4269,7 +4269,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="138" spans="1:60" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:60" x14ac:dyDescent="0.35">
       <c r="A138" t="s">
         <v>238</v>
       </c>
@@ -4283,7 +4283,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="139" spans="1:60" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:60" x14ac:dyDescent="0.35">
       <c r="A139" t="s">
         <v>155</v>
       </c>
@@ -4297,7 +4297,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="140" spans="1:60" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:60" x14ac:dyDescent="0.35">
       <c r="A140" t="s">
         <v>241</v>
       </c>
@@ -4311,7 +4311,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="141" spans="1:60" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:60" x14ac:dyDescent="0.35">
       <c r="A141" t="s">
         <v>243</v>
       </c>
@@ -4325,7 +4325,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="142" spans="1:60" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:60" x14ac:dyDescent="0.35">
       <c r="A142" t="s">
         <v>157</v>
       </c>
@@ -4357,7 +4357,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="143" spans="1:60" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:60" x14ac:dyDescent="0.35">
       <c r="A143" t="s">
         <v>157</v>
       </c>
@@ -4374,7 +4374,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="144" spans="1:60" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:60" x14ac:dyDescent="0.35">
       <c r="A144" t="s">
         <v>160</v>
       </c>
@@ -4406,7 +4406,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="145" spans="1:57" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:57" x14ac:dyDescent="0.35">
       <c r="A145" t="s">
         <v>245</v>
       </c>
@@ -4477,7 +4477,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="146" spans="1:57" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:57" x14ac:dyDescent="0.35">
       <c r="A146" t="s">
         <v>164</v>
       </c>
@@ -4551,7 +4551,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="147" spans="1:57" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:57" x14ac:dyDescent="0.35">
       <c r="A147" t="s">
         <v>166</v>
       </c>
@@ -4619,7 +4619,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="148" spans="1:57" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:57" x14ac:dyDescent="0.35">
       <c r="A148" t="s">
         <v>168</v>
       </c>
@@ -4633,7 +4633,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="149" spans="1:57" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:57" x14ac:dyDescent="0.35">
       <c r="A149" t="s">
         <v>168</v>
       </c>
@@ -4653,7 +4653,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="150" spans="1:57" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:57" x14ac:dyDescent="0.35">
       <c r="A150" t="s">
         <v>170</v>
       </c>
@@ -4670,7 +4670,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="151" spans="1:57" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:57" x14ac:dyDescent="0.35">
       <c r="A151" t="s">
         <v>170</v>
       </c>
@@ -4687,7 +4687,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="152" spans="1:57" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:57" x14ac:dyDescent="0.35">
       <c r="A152" t="s">
         <v>173</v>
       </c>
@@ -4701,7 +4701,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="153" spans="1:57" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:57" x14ac:dyDescent="0.35">
       <c r="A153" t="s">
         <v>248</v>
       </c>
@@ -4718,7 +4718,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="154" spans="1:57" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:57" x14ac:dyDescent="0.35">
       <c r="A154" t="s">
         <v>177</v>
       </c>
@@ -4735,7 +4735,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="155" spans="1:57" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:57" x14ac:dyDescent="0.35">
       <c r="A155" t="s">
         <v>177</v>
       </c>
@@ -4749,7 +4749,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="156" spans="1:57" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:57" x14ac:dyDescent="0.35">
       <c r="A156" t="s">
         <v>179</v>
       </c>
@@ -4769,7 +4769,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="157" spans="1:57" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:57" x14ac:dyDescent="0.35">
       <c r="A157" t="s">
         <v>181</v>
       </c>
@@ -4783,7 +4783,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="158" spans="1:57" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:57" x14ac:dyDescent="0.35">
       <c r="A158" t="s">
         <v>181</v>
       </c>
@@ -4797,7 +4797,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="159" spans="1:57" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:57" x14ac:dyDescent="0.35">
       <c r="A159" t="s">
         <v>184</v>
       </c>
@@ -4811,7 +4811,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="160" spans="1:57" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:57" x14ac:dyDescent="0.35">
       <c r="A160" t="s">
         <v>186</v>
       </c>
@@ -4852,7 +4852,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="161" spans="1:60" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:60" x14ac:dyDescent="0.35">
       <c r="A161" t="s">
         <v>188</v>
       </c>
@@ -4887,7 +4887,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="162" spans="1:60" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:60" x14ac:dyDescent="0.35">
       <c r="A162" t="s">
         <v>188</v>
       </c>
@@ -4904,7 +4904,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="163" spans="1:60" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:60" x14ac:dyDescent="0.35">
       <c r="A163" t="s">
         <v>193</v>
       </c>
@@ -4918,7 +4918,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="164" spans="1:60" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:60" x14ac:dyDescent="0.35">
       <c r="A164" t="s">
         <v>193</v>
       </c>
@@ -4938,7 +4938,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="165" spans="1:60" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:60" x14ac:dyDescent="0.35">
       <c r="A165" t="s">
         <v>197</v>
       </c>
@@ -4952,7 +4952,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="166" spans="1:60" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:60" x14ac:dyDescent="0.35">
       <c r="A166" t="s">
         <v>197</v>
       </c>
@@ -4969,7 +4969,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="167" spans="1:60" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:60" x14ac:dyDescent="0.35">
       <c r="A167" t="s">
         <v>202</v>
       </c>
@@ -4995,7 +4995,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="168" spans="1:60" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:60" x14ac:dyDescent="0.35">
       <c r="A168" t="s">
         <v>204</v>
       </c>
@@ -5015,7 +5015,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="169" spans="1:60" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:60" x14ac:dyDescent="0.35">
       <c r="A169" t="s">
         <v>208</v>
       </c>
@@ -5035,7 +5035,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="170" spans="1:60" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:60" x14ac:dyDescent="0.35">
       <c r="A170" t="s">
         <v>208</v>
       </c>
@@ -5061,7 +5061,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="171" spans="1:60" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:60" x14ac:dyDescent="0.35">
       <c r="A171" t="s">
         <v>253</v>
       </c>
@@ -5078,7 +5078,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="172" spans="1:60" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:60" x14ac:dyDescent="0.35">
       <c r="A172" t="s">
         <v>210</v>
       </c>
@@ -5104,7 +5104,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="173" spans="1:60" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:60" x14ac:dyDescent="0.35">
       <c r="A173" t="s">
         <v>255</v>
       </c>

--- a/html/Specialsystemer_excel.XLSX
+++ b/html/Specialsystemer_excel.XLSX
@@ -1,22 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30430"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9D0532E1-480B-4E69-91E4-487CE988FCA0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2551575B-B787-440B-ADC6-B848CFC8804C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3120" yWindow="3120" windowWidth="21600" windowHeight="12645" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4680" yWindow="4680" windowWidth="28800" windowHeight="15345" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 22-09-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 07-10-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Specialsystemer">'Opdateret d. 22-09-2026'!$A$1:$BN$173</definedName>
+    <definedName name="Specialsystemer">'Opdateret d. 07-10-2026'!$A$1:$BN$173</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>
@@ -244,7 +244,7 @@
     <t>APD-DK (2.0.1)</t>
   </si>
   <si>
-    <t>Binær dokumenttransport</t>
+    <t>Binær Dokumenttransport</t>
   </si>
   <si>
     <t>BIN01 (B0131X)</t>

--- a/html/Specialsystemer_excel.XLSX
+++ b/html/Specialsystemer_excel.XLSX
@@ -5,18 +5,18 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://medcomdk-my.sharepoint.com/personal/sof_medcom_dk/Documents/Dokumenter/GitHub/GodkendteSystemer/html/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1" documentId="11_BEA61AB9E8E5F1D2D50A2AC236F496C670D96F44" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9FF510F7-3FE5-42D0-8B76-754DF9CCAE7B}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{634F4C10-0E12-4520-8144-8BD6E1E150F4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="760" yWindow="760" windowWidth="14400" windowHeight="8170" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4680" yWindow="4680" windowWidth="28800" windowHeight="15345" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 02-10-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 07-10-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Specialsystemer">'Opdateret d. 02-10-2026'!$A$1:$BN$173</definedName>
+    <definedName name="Specialsystemer">'Opdateret d. 07-10-2026'!$A$1:$BN$173</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>
@@ -1137,9 +1137,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:BN173"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:66" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:66" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1339,7 +1339,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="2" spans="1:66" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:66" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>66</v>
       </c>
@@ -1359,7 +1359,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="3" spans="1:66" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:66" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>71</v>
       </c>
@@ -1379,7 +1379,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="4" spans="1:66" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:66" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>73</v>
       </c>
@@ -1414,7 +1414,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="5" spans="1:66" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:66" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>75</v>
       </c>
@@ -1431,7 +1431,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="6" spans="1:66" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:66" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>77</v>
       </c>
@@ -1451,7 +1451,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="7" spans="1:66" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:66" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>79</v>
       </c>
@@ -1468,7 +1468,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="8" spans="1:66" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:66" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>82</v>
       </c>
@@ -1539,7 +1539,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="9" spans="1:66" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:66" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>84</v>
       </c>
@@ -1595,7 +1595,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="10" spans="1:66" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:66" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>86</v>
       </c>
@@ -1609,7 +1609,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="11" spans="1:66" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:66" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>88</v>
       </c>
@@ -1623,7 +1623,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="12" spans="1:66" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:66" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>90</v>
       </c>
@@ -1637,7 +1637,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="13" spans="1:66" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:66" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>92</v>
       </c>
@@ -1651,7 +1651,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="14" spans="1:66" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:66" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>92</v>
       </c>
@@ -1665,7 +1665,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="15" spans="1:66" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:66" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>95</v>
       </c>
@@ -1679,7 +1679,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="16" spans="1:66" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:66" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>97</v>
       </c>
@@ -1693,7 +1693,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="17" spans="1:66" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:66" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>99</v>
       </c>
@@ -1707,7 +1707,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="18" spans="1:66" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:66" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>101</v>
       </c>
@@ -1766,7 +1766,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="19" spans="1:66" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:66" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>103</v>
       </c>
@@ -1780,7 +1780,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="20" spans="1:66" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:66" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>105</v>
       </c>
@@ -1803,7 +1803,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="21" spans="1:66" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:66" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>105</v>
       </c>
@@ -1817,7 +1817,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="22" spans="1:66" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:66" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>108</v>
       </c>
@@ -1831,7 +1831,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="23" spans="1:66" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:66" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>110</v>
       </c>
@@ -1845,7 +1845,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="24" spans="1:66" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:66" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>112</v>
       </c>
@@ -1862,7 +1862,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="25" spans="1:66" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:66" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>114</v>
       </c>
@@ -1876,7 +1876,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="26" spans="1:66" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:66" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>116</v>
       </c>
@@ -1893,7 +1893,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="27" spans="1:66" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:66" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>118</v>
       </c>
@@ -1922,7 +1922,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="28" spans="1:66" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:66" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>118</v>
       </c>
@@ -1948,7 +1948,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="29" spans="1:66" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:66" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>121</v>
       </c>
@@ -1965,7 +1965,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="30" spans="1:66" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:66" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>121</v>
       </c>
@@ -1991,7 +1991,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="31" spans="1:66" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:66" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>125</v>
       </c>
@@ -2005,7 +2005,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="32" spans="1:66" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:66" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>125</v>
       </c>
@@ -2028,7 +2028,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="33" spans="1:66" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:66" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>128</v>
       </c>
@@ -2048,7 +2048,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="34" spans="1:66" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:66" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>128</v>
       </c>
@@ -2068,7 +2068,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="35" spans="1:66" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:66" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>131</v>
       </c>
@@ -2088,7 +2088,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="36" spans="1:66" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:66" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>133</v>
       </c>
@@ -2105,7 +2105,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="37" spans="1:66" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:66" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>133</v>
       </c>
@@ -2119,7 +2119,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="38" spans="1:66" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:66" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>133</v>
       </c>
@@ -2133,7 +2133,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="39" spans="1:66" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:66" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>137</v>
       </c>
@@ -2153,7 +2153,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="40" spans="1:66" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:66" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>139</v>
       </c>
@@ -2170,7 +2170,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="41" spans="1:66" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:66" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>139</v>
       </c>
@@ -2187,7 +2187,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="42" spans="1:66" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:66" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>142</v>
       </c>
@@ -2201,7 +2201,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="43" spans="1:66" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:66" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>142</v>
       </c>
@@ -2215,7 +2215,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="44" spans="1:66" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:66" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>145</v>
       </c>
@@ -2235,7 +2235,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="45" spans="1:66" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:66" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>145</v>
       </c>
@@ -2258,7 +2258,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="46" spans="1:66" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:66" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>148</v>
       </c>
@@ -2275,7 +2275,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="47" spans="1:66" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:66" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
         <v>150</v>
       </c>
@@ -2289,7 +2289,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="48" spans="1:66" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:66" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
         <v>150</v>
       </c>
@@ -2303,7 +2303,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="49" spans="1:65" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
         <v>153</v>
       </c>
@@ -2320,7 +2320,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="50" spans="1:65" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
         <v>155</v>
       </c>
@@ -2343,7 +2343,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="51" spans="1:65" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
         <v>157</v>
       </c>
@@ -2375,7 +2375,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="52" spans="1:65" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
         <v>157</v>
       </c>
@@ -2395,7 +2395,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="53" spans="1:65" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
         <v>160</v>
       </c>
@@ -2430,7 +2430,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="54" spans="1:65" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
         <v>162</v>
       </c>
@@ -2444,7 +2444,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="55" spans="1:65" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
         <v>164</v>
       </c>
@@ -2494,7 +2494,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="56" spans="1:65" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
         <v>166</v>
       </c>
@@ -2544,7 +2544,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="57" spans="1:65" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
         <v>168</v>
       </c>
@@ -2558,7 +2558,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="58" spans="1:65" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
         <v>170</v>
       </c>
@@ -2572,7 +2572,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="59" spans="1:65" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
         <v>170</v>
       </c>
@@ -2586,7 +2586,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="60" spans="1:65" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
         <v>173</v>
       </c>
@@ -2600,7 +2600,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="61" spans="1:65" x14ac:dyDescent="0.35">
+    <row r="61" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
         <v>175</v>
       </c>
@@ -2623,7 +2623,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="62" spans="1:65" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
         <v>177</v>
       </c>
@@ -2637,7 +2637,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="63" spans="1:65" x14ac:dyDescent="0.35">
+    <row r="63" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
         <v>179</v>
       </c>
@@ -2651,7 +2651,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="64" spans="1:65" x14ac:dyDescent="0.35">
+    <row r="64" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
         <v>181</v>
       </c>
@@ -2665,7 +2665,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="65" spans="1:66" x14ac:dyDescent="0.35">
+    <row r="65" spans="1:66" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
         <v>181</v>
       </c>
@@ -2679,7 +2679,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="66" spans="1:66" x14ac:dyDescent="0.35">
+    <row r="66" spans="1:66" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
         <v>184</v>
       </c>
@@ -2693,7 +2693,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="67" spans="1:66" x14ac:dyDescent="0.35">
+    <row r="67" spans="1:66" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
         <v>186</v>
       </c>
@@ -2752,7 +2752,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="68" spans="1:66" x14ac:dyDescent="0.35">
+    <row r="68" spans="1:66" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
         <v>188</v>
       </c>
@@ -2781,7 +2781,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="69" spans="1:66" x14ac:dyDescent="0.35">
+    <row r="69" spans="1:66" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
         <v>188</v>
       </c>
@@ -2804,7 +2804,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="70" spans="1:66" x14ac:dyDescent="0.35">
+    <row r="70" spans="1:66" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
         <v>191</v>
       </c>
@@ -2818,7 +2818,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="71" spans="1:66" x14ac:dyDescent="0.35">
+    <row r="71" spans="1:66" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
         <v>193</v>
       </c>
@@ -2838,7 +2838,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="72" spans="1:66" x14ac:dyDescent="0.35">
+    <row r="72" spans="1:66" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
         <v>195</v>
       </c>
@@ -2852,7 +2852,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="73" spans="1:66" x14ac:dyDescent="0.35">
+    <row r="73" spans="1:66" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
         <v>197</v>
       </c>
@@ -2866,7 +2866,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="74" spans="1:66" x14ac:dyDescent="0.35">
+    <row r="74" spans="1:66" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
         <v>197</v>
       </c>
@@ -2886,7 +2886,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="75" spans="1:66" x14ac:dyDescent="0.35">
+    <row r="75" spans="1:66" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
         <v>200</v>
       </c>
@@ -2900,7 +2900,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="76" spans="1:66" x14ac:dyDescent="0.35">
+    <row r="76" spans="1:66" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
         <v>202</v>
       </c>
@@ -2920,7 +2920,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="77" spans="1:66" x14ac:dyDescent="0.35">
+    <row r="77" spans="1:66" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
         <v>204</v>
       </c>
@@ -2937,7 +2937,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="78" spans="1:66" x14ac:dyDescent="0.35">
+    <row r="78" spans="1:66" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
         <v>206</v>
       </c>
@@ -2951,7 +2951,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="79" spans="1:66" x14ac:dyDescent="0.35">
+    <row r="79" spans="1:66" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
         <v>208</v>
       </c>
@@ -2965,7 +2965,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="80" spans="1:66" x14ac:dyDescent="0.35">
+    <row r="80" spans="1:66" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
         <v>210</v>
       </c>
@@ -2979,7 +2979,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="81" spans="1:65" x14ac:dyDescent="0.35">
+    <row r="81" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
         <v>66</v>
       </c>
@@ -2999,7 +2999,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="82" spans="1:65" x14ac:dyDescent="0.35">
+    <row r="82" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
         <v>71</v>
       </c>
@@ -3034,7 +3034,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="83" spans="1:65" x14ac:dyDescent="0.35">
+    <row r="83" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
         <v>73</v>
       </c>
@@ -3060,7 +3060,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="84" spans="1:65" x14ac:dyDescent="0.35">
+    <row r="84" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
         <v>75</v>
       </c>
@@ -3074,7 +3074,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="85" spans="1:65" x14ac:dyDescent="0.35">
+    <row r="85" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
         <v>77</v>
       </c>
@@ -3094,7 +3094,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="86" spans="1:65" x14ac:dyDescent="0.35">
+    <row r="86" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
         <v>79</v>
       </c>
@@ -3111,7 +3111,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="87" spans="1:65" x14ac:dyDescent="0.35">
+    <row r="87" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
         <v>213</v>
       </c>
@@ -3128,7 +3128,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="88" spans="1:65" x14ac:dyDescent="0.35">
+    <row r="88" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
         <v>215</v>
       </c>
@@ -3145,7 +3145,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="89" spans="1:65" x14ac:dyDescent="0.35">
+    <row r="89" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
         <v>215</v>
       </c>
@@ -3168,7 +3168,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="90" spans="1:65" x14ac:dyDescent="0.35">
+    <row r="90" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
         <v>218</v>
       </c>
@@ -3245,7 +3245,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="91" spans="1:65" x14ac:dyDescent="0.35">
+    <row r="91" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
         <v>82</v>
       </c>
@@ -3325,7 +3325,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="92" spans="1:65" x14ac:dyDescent="0.35">
+    <row r="92" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
         <v>84</v>
       </c>
@@ -3402,7 +3402,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="93" spans="1:65" x14ac:dyDescent="0.35">
+    <row r="93" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
         <v>86</v>
       </c>
@@ -3416,7 +3416,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="94" spans="1:65" x14ac:dyDescent="0.35">
+    <row r="94" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
         <v>88</v>
       </c>
@@ -3430,7 +3430,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="95" spans="1:65" x14ac:dyDescent="0.35">
+    <row r="95" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
         <v>90</v>
       </c>
@@ -3447,7 +3447,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="96" spans="1:65" x14ac:dyDescent="0.35">
+    <row r="96" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
         <v>90</v>
       </c>
@@ -3464,7 +3464,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="97" spans="1:61" x14ac:dyDescent="0.35">
+    <row r="97" spans="1:61" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
         <v>92</v>
       </c>
@@ -3478,7 +3478,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="98" spans="1:61" x14ac:dyDescent="0.35">
+    <row r="98" spans="1:61" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
         <v>92</v>
       </c>
@@ -3504,7 +3504,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="99" spans="1:61" x14ac:dyDescent="0.35">
+    <row r="99" spans="1:61" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
         <v>221</v>
       </c>
@@ -3521,7 +3521,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="100" spans="1:61" x14ac:dyDescent="0.35">
+    <row r="100" spans="1:61" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
         <v>223</v>
       </c>
@@ -3541,7 +3541,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="101" spans="1:61" x14ac:dyDescent="0.35">
+    <row r="101" spans="1:61" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
         <v>95</v>
       </c>
@@ -3558,7 +3558,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="102" spans="1:61" x14ac:dyDescent="0.35">
+    <row r="102" spans="1:61" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
         <v>97</v>
       </c>
@@ -3575,7 +3575,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="103" spans="1:61" x14ac:dyDescent="0.35">
+    <row r="103" spans="1:61" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
         <v>99</v>
       </c>
@@ -3589,7 +3589,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="104" spans="1:61" x14ac:dyDescent="0.35">
+    <row r="104" spans="1:61" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
         <v>101</v>
       </c>
@@ -3636,7 +3636,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="105" spans="1:61" x14ac:dyDescent="0.35">
+    <row r="105" spans="1:61" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
         <v>103</v>
       </c>
@@ -3656,7 +3656,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="106" spans="1:61" x14ac:dyDescent="0.35">
+    <row r="106" spans="1:61" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
         <v>103</v>
       </c>
@@ -3676,7 +3676,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="107" spans="1:61" x14ac:dyDescent="0.35">
+    <row r="107" spans="1:61" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
         <v>226</v>
       </c>
@@ -3690,7 +3690,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="108" spans="1:61" x14ac:dyDescent="0.35">
+    <row r="108" spans="1:61" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
         <v>105</v>
       </c>
@@ -3710,7 +3710,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="109" spans="1:61" x14ac:dyDescent="0.35">
+    <row r="109" spans="1:61" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
         <v>105</v>
       </c>
@@ -3724,7 +3724,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="110" spans="1:61" x14ac:dyDescent="0.35">
+    <row r="110" spans="1:61" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
         <v>108</v>
       </c>
@@ -3744,7 +3744,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="111" spans="1:61" x14ac:dyDescent="0.35">
+    <row r="111" spans="1:61" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
         <v>110</v>
       </c>
@@ -3764,7 +3764,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="112" spans="1:61" x14ac:dyDescent="0.35">
+    <row r="112" spans="1:61" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
         <v>112</v>
       </c>
@@ -3781,7 +3781,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="113" spans="1:60" x14ac:dyDescent="0.35">
+    <row r="113" spans="1:60" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
         <v>114</v>
       </c>
@@ -3801,7 +3801,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="114" spans="1:60" x14ac:dyDescent="0.35">
+    <row r="114" spans="1:60" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
         <v>116</v>
       </c>
@@ -3815,7 +3815,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="115" spans="1:60" x14ac:dyDescent="0.35">
+    <row r="115" spans="1:60" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
         <v>116</v>
       </c>
@@ -3829,7 +3829,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="116" spans="1:60" x14ac:dyDescent="0.35">
+    <row r="116" spans="1:60" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
         <v>118</v>
       </c>
@@ -3849,7 +3849,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="117" spans="1:60" x14ac:dyDescent="0.35">
+    <row r="117" spans="1:60" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
         <v>118</v>
       </c>
@@ -3869,7 +3869,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="118" spans="1:60" x14ac:dyDescent="0.35">
+    <row r="118" spans="1:60" x14ac:dyDescent="0.25">
       <c r="A118" t="s">
         <v>121</v>
       </c>
@@ -3883,7 +3883,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="119" spans="1:60" x14ac:dyDescent="0.35">
+    <row r="119" spans="1:60" x14ac:dyDescent="0.25">
       <c r="A119" t="s">
         <v>121</v>
       </c>
@@ -3909,7 +3909,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="120" spans="1:60" x14ac:dyDescent="0.35">
+    <row r="120" spans="1:60" x14ac:dyDescent="0.25">
       <c r="A120" t="s">
         <v>125</v>
       </c>
@@ -3935,7 +3935,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="121" spans="1:60" x14ac:dyDescent="0.35">
+    <row r="121" spans="1:60" x14ac:dyDescent="0.25">
       <c r="A121" t="s">
         <v>128</v>
       </c>
@@ -3958,7 +3958,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="122" spans="1:60" x14ac:dyDescent="0.35">
+    <row r="122" spans="1:60" x14ac:dyDescent="0.25">
       <c r="A122" t="s">
         <v>128</v>
       </c>
@@ -3981,7 +3981,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="123" spans="1:60" x14ac:dyDescent="0.35">
+    <row r="123" spans="1:60" x14ac:dyDescent="0.25">
       <c r="A123" t="s">
         <v>131</v>
       </c>
@@ -4004,7 +4004,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="124" spans="1:60" x14ac:dyDescent="0.35">
+    <row r="124" spans="1:60" x14ac:dyDescent="0.25">
       <c r="A124" t="s">
         <v>133</v>
       </c>
@@ -4024,7 +4024,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="125" spans="1:60" x14ac:dyDescent="0.35">
+    <row r="125" spans="1:60" x14ac:dyDescent="0.25">
       <c r="A125" t="s">
         <v>133</v>
       </c>
@@ -4041,7 +4041,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="126" spans="1:60" x14ac:dyDescent="0.35">
+    <row r="126" spans="1:60" x14ac:dyDescent="0.25">
       <c r="A126" t="s">
         <v>133</v>
       </c>
@@ -4058,7 +4058,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="127" spans="1:60" x14ac:dyDescent="0.35">
+    <row r="127" spans="1:60" x14ac:dyDescent="0.25">
       <c r="A127" t="s">
         <v>137</v>
       </c>
@@ -4081,7 +4081,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="128" spans="1:60" x14ac:dyDescent="0.35">
+    <row r="128" spans="1:60" x14ac:dyDescent="0.25">
       <c r="A128" t="s">
         <v>139</v>
       </c>
@@ -4101,7 +4101,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="129" spans="1:60" x14ac:dyDescent="0.35">
+    <row r="129" spans="1:60" x14ac:dyDescent="0.25">
       <c r="A129" t="s">
         <v>139</v>
       </c>
@@ -4124,7 +4124,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="130" spans="1:60" x14ac:dyDescent="0.35">
+    <row r="130" spans="1:60" x14ac:dyDescent="0.25">
       <c r="A130" t="s">
         <v>142</v>
       </c>
@@ -4138,7 +4138,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="131" spans="1:60" x14ac:dyDescent="0.35">
+    <row r="131" spans="1:60" x14ac:dyDescent="0.25">
       <c r="A131" t="s">
         <v>145</v>
       </c>
@@ -4152,7 +4152,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="132" spans="1:60" x14ac:dyDescent="0.35">
+    <row r="132" spans="1:60" x14ac:dyDescent="0.25">
       <c r="A132" t="s">
         <v>145</v>
       </c>
@@ -4184,7 +4184,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="133" spans="1:60" x14ac:dyDescent="0.35">
+    <row r="133" spans="1:60" x14ac:dyDescent="0.25">
       <c r="A133" t="s">
         <v>229</v>
       </c>
@@ -4201,7 +4201,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="134" spans="1:60" x14ac:dyDescent="0.35">
+    <row r="134" spans="1:60" x14ac:dyDescent="0.25">
       <c r="A134" t="s">
         <v>231</v>
       </c>
@@ -4215,7 +4215,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="135" spans="1:60" x14ac:dyDescent="0.35">
+    <row r="135" spans="1:60" x14ac:dyDescent="0.25">
       <c r="A135" t="s">
         <v>233</v>
       </c>
@@ -4232,7 +4232,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="136" spans="1:60" x14ac:dyDescent="0.35">
+    <row r="136" spans="1:60" x14ac:dyDescent="0.25">
       <c r="A136" t="s">
         <v>235</v>
       </c>
@@ -4249,7 +4249,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="137" spans="1:60" x14ac:dyDescent="0.35">
+    <row r="137" spans="1:60" x14ac:dyDescent="0.25">
       <c r="A137" t="s">
         <v>235</v>
       </c>
@@ -4269,7 +4269,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="138" spans="1:60" x14ac:dyDescent="0.35">
+    <row r="138" spans="1:60" x14ac:dyDescent="0.25">
       <c r="A138" t="s">
         <v>238</v>
       </c>
@@ -4283,7 +4283,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="139" spans="1:60" x14ac:dyDescent="0.35">
+    <row r="139" spans="1:60" x14ac:dyDescent="0.25">
       <c r="A139" t="s">
         <v>155</v>
       </c>
@@ -4297,7 +4297,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="140" spans="1:60" x14ac:dyDescent="0.35">
+    <row r="140" spans="1:60" x14ac:dyDescent="0.25">
       <c r="A140" t="s">
         <v>241</v>
       </c>
@@ -4311,7 +4311,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="141" spans="1:60" x14ac:dyDescent="0.35">
+    <row r="141" spans="1:60" x14ac:dyDescent="0.25">
       <c r="A141" t="s">
         <v>243</v>
       </c>
@@ -4325,7 +4325,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="142" spans="1:60" x14ac:dyDescent="0.35">
+    <row r="142" spans="1:60" x14ac:dyDescent="0.25">
       <c r="A142" t="s">
         <v>157</v>
       </c>
@@ -4357,7 +4357,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="143" spans="1:60" x14ac:dyDescent="0.35">
+    <row r="143" spans="1:60" x14ac:dyDescent="0.25">
       <c r="A143" t="s">
         <v>157</v>
       </c>
@@ -4374,7 +4374,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="144" spans="1:60" x14ac:dyDescent="0.35">
+    <row r="144" spans="1:60" x14ac:dyDescent="0.25">
       <c r="A144" t="s">
         <v>160</v>
       </c>
@@ -4406,7 +4406,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="145" spans="1:57" x14ac:dyDescent="0.35">
+    <row r="145" spans="1:57" x14ac:dyDescent="0.25">
       <c r="A145" t="s">
         <v>245</v>
       </c>
@@ -4477,7 +4477,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="146" spans="1:57" x14ac:dyDescent="0.35">
+    <row r="146" spans="1:57" x14ac:dyDescent="0.25">
       <c r="A146" t="s">
         <v>164</v>
       </c>
@@ -4551,7 +4551,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="147" spans="1:57" x14ac:dyDescent="0.35">
+    <row r="147" spans="1:57" x14ac:dyDescent="0.25">
       <c r="A147" t="s">
         <v>166</v>
       </c>
@@ -4619,7 +4619,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="148" spans="1:57" x14ac:dyDescent="0.35">
+    <row r="148" spans="1:57" x14ac:dyDescent="0.25">
       <c r="A148" t="s">
         <v>168</v>
       </c>
@@ -4633,7 +4633,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="149" spans="1:57" x14ac:dyDescent="0.35">
+    <row r="149" spans="1:57" x14ac:dyDescent="0.25">
       <c r="A149" t="s">
         <v>168</v>
       </c>
@@ -4653,7 +4653,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="150" spans="1:57" x14ac:dyDescent="0.35">
+    <row r="150" spans="1:57" x14ac:dyDescent="0.25">
       <c r="A150" t="s">
         <v>170</v>
       </c>
@@ -4670,7 +4670,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="151" spans="1:57" x14ac:dyDescent="0.35">
+    <row r="151" spans="1:57" x14ac:dyDescent="0.25">
       <c r="A151" t="s">
         <v>170</v>
       </c>
@@ -4687,7 +4687,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="152" spans="1:57" x14ac:dyDescent="0.35">
+    <row r="152" spans="1:57" x14ac:dyDescent="0.25">
       <c r="A152" t="s">
         <v>173</v>
       </c>
@@ -4701,7 +4701,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="153" spans="1:57" x14ac:dyDescent="0.35">
+    <row r="153" spans="1:57" x14ac:dyDescent="0.25">
       <c r="A153" t="s">
         <v>248</v>
       </c>
@@ -4718,7 +4718,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="154" spans="1:57" x14ac:dyDescent="0.35">
+    <row r="154" spans="1:57" x14ac:dyDescent="0.25">
       <c r="A154" t="s">
         <v>177</v>
       </c>
@@ -4735,7 +4735,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="155" spans="1:57" x14ac:dyDescent="0.35">
+    <row r="155" spans="1:57" x14ac:dyDescent="0.25">
       <c r="A155" t="s">
         <v>177</v>
       </c>
@@ -4749,7 +4749,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="156" spans="1:57" x14ac:dyDescent="0.35">
+    <row r="156" spans="1:57" x14ac:dyDescent="0.25">
       <c r="A156" t="s">
         <v>179</v>
       </c>
@@ -4769,7 +4769,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="157" spans="1:57" x14ac:dyDescent="0.35">
+    <row r="157" spans="1:57" x14ac:dyDescent="0.25">
       <c r="A157" t="s">
         <v>181</v>
       </c>
@@ -4783,7 +4783,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="158" spans="1:57" x14ac:dyDescent="0.35">
+    <row r="158" spans="1:57" x14ac:dyDescent="0.25">
       <c r="A158" t="s">
         <v>181</v>
       </c>
@@ -4797,7 +4797,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="159" spans="1:57" x14ac:dyDescent="0.35">
+    <row r="159" spans="1:57" x14ac:dyDescent="0.25">
       <c r="A159" t="s">
         <v>184</v>
       </c>
@@ -4811,7 +4811,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="160" spans="1:57" x14ac:dyDescent="0.35">
+    <row r="160" spans="1:57" x14ac:dyDescent="0.25">
       <c r="A160" t="s">
         <v>186</v>
       </c>
@@ -4852,7 +4852,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="161" spans="1:60" x14ac:dyDescent="0.35">
+    <row r="161" spans="1:60" x14ac:dyDescent="0.25">
       <c r="A161" t="s">
         <v>188</v>
       </c>
@@ -4887,7 +4887,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="162" spans="1:60" x14ac:dyDescent="0.35">
+    <row r="162" spans="1:60" x14ac:dyDescent="0.25">
       <c r="A162" t="s">
         <v>188</v>
       </c>
@@ -4904,7 +4904,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="163" spans="1:60" x14ac:dyDescent="0.35">
+    <row r="163" spans="1:60" x14ac:dyDescent="0.25">
       <c r="A163" t="s">
         <v>193</v>
       </c>
@@ -4918,7 +4918,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="164" spans="1:60" x14ac:dyDescent="0.35">
+    <row r="164" spans="1:60" x14ac:dyDescent="0.25">
       <c r="A164" t="s">
         <v>193</v>
       </c>
@@ -4938,7 +4938,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="165" spans="1:60" x14ac:dyDescent="0.35">
+    <row r="165" spans="1:60" x14ac:dyDescent="0.25">
       <c r="A165" t="s">
         <v>197</v>
       </c>
@@ -4952,7 +4952,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="166" spans="1:60" x14ac:dyDescent="0.35">
+    <row r="166" spans="1:60" x14ac:dyDescent="0.25">
       <c r="A166" t="s">
         <v>197</v>
       </c>
@@ -4969,7 +4969,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="167" spans="1:60" x14ac:dyDescent="0.35">
+    <row r="167" spans="1:60" x14ac:dyDescent="0.25">
       <c r="A167" t="s">
         <v>202</v>
       </c>
@@ -4995,7 +4995,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="168" spans="1:60" x14ac:dyDescent="0.35">
+    <row r="168" spans="1:60" x14ac:dyDescent="0.25">
       <c r="A168" t="s">
         <v>204</v>
       </c>
@@ -5015,7 +5015,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="169" spans="1:60" x14ac:dyDescent="0.35">
+    <row r="169" spans="1:60" x14ac:dyDescent="0.25">
       <c r="A169" t="s">
         <v>208</v>
       </c>
@@ -5035,7 +5035,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="170" spans="1:60" x14ac:dyDescent="0.35">
+    <row r="170" spans="1:60" x14ac:dyDescent="0.25">
       <c r="A170" t="s">
         <v>208</v>
       </c>
@@ -5061,7 +5061,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="171" spans="1:60" x14ac:dyDescent="0.35">
+    <row r="171" spans="1:60" x14ac:dyDescent="0.25">
       <c r="A171" t="s">
         <v>253</v>
       </c>
@@ -5078,7 +5078,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="172" spans="1:60" x14ac:dyDescent="0.35">
+    <row r="172" spans="1:60" x14ac:dyDescent="0.25">
       <c r="A172" t="s">
         <v>210</v>
       </c>
@@ -5104,7 +5104,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="173" spans="1:60" x14ac:dyDescent="0.35">
+    <row r="173" spans="1:60" x14ac:dyDescent="0.25">
       <c r="A173" t="s">
         <v>255</v>
       </c>

--- a/html/Specialsystemer_excel.XLSX
+++ b/html/Specialsystemer_excel.XLSX
@@ -5,18 +5,18 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\GodkendteSystemer\html\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://medcomdk-my.sharepoint.com/personal/ras_medcom_dk/Documents/Dokumenter/GitHub/GodkendteSystemer/html/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{634F4C10-0E12-4520-8144-8BD6E1E150F4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="1" documentId="11_BEA61AB9E8E5F1D2D50A2A420E74ACE870D96F40" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B4E0AD37-CC92-47CA-81E9-9C634AD84C0D}"/>
   <bookViews>
-    <workbookView xWindow="4680" yWindow="4680" windowWidth="28800" windowHeight="15345" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="51840" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 07-10-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 08-10-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Specialsystemer">'Opdateret d. 07-10-2026'!$A$1:$BN$173</definedName>
+    <definedName name="Specialsystemer">'Opdateret d. 08-10-2026'!$A$1:$BN$173</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/Specialsystemer_excel.XLSX
+++ b/html/Specialsystemer_excel.XLSX
@@ -5,25 +5,25 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://medcomdk-my.sharepoint.com/personal/ras_medcom_dk/Documents/Dokumenter/GitHub/GodkendteSystemer/html/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hua\GitHub\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1" documentId="11_BEA61AB9E8E5F1D2D50A2A420E74ACE870D96F40" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B4E0AD37-CC92-47CA-81E9-9C634AD84C0D}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{67E5624E-7244-4081-92A9-70A23BE0F921}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="51840" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 08-10-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 09-10-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Specialsystemer">'Opdateret d. 08-10-2026'!$A$1:$BN$173</definedName>
+    <definedName name="Specialsystemer">'Opdateret d. 09-10-2026'!$A$1:$BN$173</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1211" uniqueCount="257">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1215" uniqueCount="257">
   <si>
     <t>Standard</t>
   </si>
@@ -58,9 +58,6 @@
     <t>Astma Dagbog (Asthmatech)</t>
   </si>
   <si>
-    <t>Blanketserver (SYNLAB)</t>
-  </si>
-  <si>
     <t>Bookplan (Capgemini)</t>
   </si>
   <si>
@@ -163,6 +160,9 @@
     <t>NetForvaltning Sundhed (EG)</t>
   </si>
   <si>
+    <t>NEXUS / E-SUNDHED Blanketserver (SYNLAB)</t>
+  </si>
+  <si>
     <t>OS2korrespondance (Digital Identity)</t>
   </si>
   <si>
@@ -232,10 +232,10 @@
     <t>Sende</t>
   </si>
   <si>
+    <t>Godkendt</t>
+  </si>
+  <si>
     <t>Tester</t>
-  </si>
-  <si>
-    <t>Godkendt</t>
   </si>
   <si>
     <t>Appointment Document</t>
@@ -1349,14 +1349,14 @@
       <c r="C2" t="s">
         <v>68</v>
       </c>
-      <c r="L2" t="s">
-        <v>69</v>
-      </c>
-      <c r="V2" t="s">
-        <v>70</v>
-      </c>
-      <c r="AF2" t="s">
-        <v>69</v>
+      <c r="U2" t="s">
+        <v>69</v>
+      </c>
+      <c r="AE2" t="s">
+        <v>70</v>
+      </c>
+      <c r="AT2" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="3" spans="1:66" x14ac:dyDescent="0.25">
@@ -1369,14 +1369,14 @@
       <c r="C3" t="s">
         <v>68</v>
       </c>
-      <c r="M3" t="s">
-        <v>70</v>
+      <c r="L3" t="s">
+        <v>69</v>
       </c>
       <c r="AX3" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="BI3" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="4" spans="1:66" x14ac:dyDescent="0.25">
@@ -1389,29 +1389,29 @@
       <c r="C4" t="s">
         <v>68</v>
       </c>
+      <c r="T4" t="s">
+        <v>69</v>
+      </c>
       <c r="U4" t="s">
-        <v>70</v>
-      </c>
-      <c r="V4" t="s">
-        <v>70</v>
-      </c>
-      <c r="AC4" t="s">
-        <v>70</v>
-      </c>
-      <c r="AK4" t="s">
-        <v>70</v>
-      </c>
-      <c r="AT4" t="s">
-        <v>70</v>
+        <v>69</v>
+      </c>
+      <c r="AB4" t="s">
+        <v>69</v>
+      </c>
+      <c r="AJ4" t="s">
+        <v>69</v>
+      </c>
+      <c r="AS4" t="s">
+        <v>69</v>
       </c>
       <c r="AU4" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="AZ4" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="BE4" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="5" spans="1:66" x14ac:dyDescent="0.25">
@@ -1424,11 +1424,11 @@
       <c r="C5" t="s">
         <v>68</v>
       </c>
-      <c r="V5" t="s">
-        <v>70</v>
-      </c>
-      <c r="AD5" t="s">
-        <v>69</v>
+      <c r="U5" t="s">
+        <v>69</v>
+      </c>
+      <c r="AC5" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="6" spans="1:66" x14ac:dyDescent="0.25">
@@ -1441,14 +1441,14 @@
       <c r="C6" t="s">
         <v>68</v>
       </c>
-      <c r="L6" t="s">
-        <v>69</v>
-      </c>
-      <c r="V6" t="s">
-        <v>70</v>
-      </c>
-      <c r="AF6" t="s">
-        <v>69</v>
+      <c r="U6" t="s">
+        <v>69</v>
+      </c>
+      <c r="AE6" t="s">
+        <v>70</v>
+      </c>
+      <c r="AT6" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="7" spans="1:66" x14ac:dyDescent="0.25">
@@ -1461,11 +1461,11 @@
       <c r="C7" t="s">
         <v>68</v>
       </c>
-      <c r="W7" t="s">
+      <c r="V7" t="s">
         <v>81</v>
       </c>
       <c r="AX7" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="8" spans="1:66" x14ac:dyDescent="0.25">
@@ -1479,64 +1479,64 @@
         <v>68</v>
       </c>
       <c r="G8" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="J8" t="s">
         <v>81</v>
       </c>
-      <c r="O8" t="s">
-        <v>70</v>
-      </c>
-      <c r="Q8" t="s">
-        <v>70</v>
+      <c r="N8" t="s">
+        <v>69</v>
+      </c>
+      <c r="P8" t="s">
+        <v>69</v>
+      </c>
+      <c r="T8" t="s">
+        <v>69</v>
       </c>
       <c r="U8" t="s">
-        <v>70</v>
-      </c>
-      <c r="V8" t="s">
-        <v>70</v>
-      </c>
-      <c r="Z8" t="s">
+        <v>69</v>
+      </c>
+      <c r="Y8" t="s">
+        <v>70</v>
+      </c>
+      <c r="AB8" t="s">
         <v>69</v>
       </c>
       <c r="AC8" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="AD8" t="s">
-        <v>70</v>
-      </c>
-      <c r="AE8" t="s">
-        <v>70</v>
-      </c>
-      <c r="AH8" t="s">
-        <v>70</v>
-      </c>
-      <c r="AK8" t="s">
-        <v>70</v>
-      </c>
-      <c r="AT8" t="s">
-        <v>70</v>
+        <v>69</v>
+      </c>
+      <c r="AG8" t="s">
+        <v>69</v>
+      </c>
+      <c r="AJ8" t="s">
+        <v>69</v>
+      </c>
+      <c r="AS8" t="s">
+        <v>69</v>
       </c>
       <c r="AU8" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="AW8" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="AZ8" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="BE8" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="BF8" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="BJ8" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="BL8" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
     </row>
     <row r="9" spans="1:66" x14ac:dyDescent="0.25">
@@ -1552,47 +1552,47 @@
       <c r="J9" t="s">
         <v>81</v>
       </c>
+      <c r="T9" t="s">
+        <v>69</v>
+      </c>
       <c r="U9" t="s">
-        <v>70</v>
-      </c>
-      <c r="V9" t="s">
-        <v>70</v>
-      </c>
-      <c r="Z9" t="s">
+        <v>69</v>
+      </c>
+      <c r="Y9" t="s">
+        <v>70</v>
+      </c>
+      <c r="AB9" t="s">
         <v>69</v>
       </c>
       <c r="AC9" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="AD9" t="s">
-        <v>70</v>
-      </c>
-      <c r="AE9" t="s">
-        <v>70</v>
-      </c>
-      <c r="AH9" t="s">
-        <v>70</v>
-      </c>
-      <c r="AT9" t="s">
-        <v>70</v>
+        <v>69</v>
+      </c>
+      <c r="AG9" t="s">
+        <v>69</v>
+      </c>
+      <c r="AS9" t="s">
+        <v>69</v>
       </c>
       <c r="AU9" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="AW9" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="AZ9" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="BB9" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="BE9" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="BF9" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="10" spans="1:66" x14ac:dyDescent="0.25">
@@ -1605,8 +1605,8 @@
       <c r="C10" t="s">
         <v>68</v>
       </c>
-      <c r="AT10" t="s">
-        <v>70</v>
+      <c r="AS10" t="s">
+        <v>69</v>
       </c>
     </row>
     <row r="11" spans="1:66" x14ac:dyDescent="0.25">
@@ -1619,8 +1619,8 @@
       <c r="C11" t="s">
         <v>68</v>
       </c>
-      <c r="AT11" t="s">
-        <v>70</v>
+      <c r="AS11" t="s">
+        <v>69</v>
       </c>
     </row>
     <row r="12" spans="1:66" x14ac:dyDescent="0.25">
@@ -1633,8 +1633,8 @@
       <c r="C12" t="s">
         <v>68</v>
       </c>
-      <c r="V12" t="s">
-        <v>70</v>
+      <c r="U12" t="s">
+        <v>69</v>
       </c>
     </row>
     <row r="13" spans="1:66" x14ac:dyDescent="0.25">
@@ -1648,7 +1648,7 @@
         <v>68</v>
       </c>
       <c r="BB13" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="14" spans="1:66" x14ac:dyDescent="0.25">
@@ -1661,8 +1661,8 @@
       <c r="C14" t="s">
         <v>68</v>
       </c>
-      <c r="V14" t="s">
-        <v>70</v>
+      <c r="U14" t="s">
+        <v>69</v>
       </c>
     </row>
     <row r="15" spans="1:66" x14ac:dyDescent="0.25">
@@ -1675,8 +1675,8 @@
       <c r="C15" t="s">
         <v>68</v>
       </c>
-      <c r="V15" t="s">
-        <v>70</v>
+      <c r="U15" t="s">
+        <v>69</v>
       </c>
     </row>
     <row r="16" spans="1:66" x14ac:dyDescent="0.25">
@@ -1689,8 +1689,8 @@
       <c r="C16" t="s">
         <v>68</v>
       </c>
-      <c r="V16" t="s">
-        <v>70</v>
+      <c r="U16" t="s">
+        <v>69</v>
       </c>
     </row>
     <row r="17" spans="1:66" x14ac:dyDescent="0.25">
@@ -1703,8 +1703,8 @@
       <c r="C17" t="s">
         <v>68</v>
       </c>
-      <c r="V17" t="s">
-        <v>70</v>
+      <c r="U17" t="s">
+        <v>69</v>
       </c>
     </row>
     <row r="18" spans="1:66" x14ac:dyDescent="0.25">
@@ -1717,52 +1717,58 @@
       <c r="C18" t="s">
         <v>68</v>
       </c>
+      <c r="T18" t="s">
+        <v>69</v>
+      </c>
       <c r="U18" t="s">
-        <v>70</v>
-      </c>
-      <c r="V18" t="s">
-        <v>70</v>
+        <v>69</v>
+      </c>
+      <c r="AA18" t="s">
+        <v>69</v>
       </c>
       <c r="AB18" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="AC18" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="AD18" t="s">
-        <v>70</v>
-      </c>
-      <c r="AE18" t="s">
-        <v>70</v>
-      </c>
-      <c r="AH18" t="s">
-        <v>70</v>
-      </c>
-      <c r="AK18" t="s">
-        <v>70</v>
+        <v>69</v>
+      </c>
+      <c r="AG18" t="s">
+        <v>69</v>
+      </c>
+      <c r="AJ18" t="s">
+        <v>69</v>
+      </c>
+      <c r="AS18" t="s">
+        <v>69</v>
       </c>
       <c r="AT18" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="AU18" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="AW18" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="AZ18" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="BB18" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="BE18" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="BG18" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="BH18" t="s">
+        <v>70</v>
+      </c>
+      <c r="BN18" t="s">
         <v>69</v>
       </c>
     </row>
@@ -1776,8 +1782,8 @@
       <c r="C19" t="s">
         <v>68</v>
       </c>
-      <c r="AA19" t="s">
-        <v>69</v>
+      <c r="Z19" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="20" spans="1:66" x14ac:dyDescent="0.25">
@@ -1793,14 +1799,14 @@
       <c r="D20" t="s">
         <v>81</v>
       </c>
+      <c r="AN20" t="s">
+        <v>81</v>
+      </c>
       <c r="AO20" t="s">
-        <v>81</v>
-      </c>
-      <c r="AP20" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="BN20" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="21" spans="1:66" x14ac:dyDescent="0.25">
@@ -1814,7 +1820,7 @@
         <v>68</v>
       </c>
       <c r="BK21" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="22" spans="1:66" x14ac:dyDescent="0.25">
@@ -1827,8 +1833,8 @@
       <c r="C22" t="s">
         <v>68</v>
       </c>
-      <c r="T22" t="s">
-        <v>69</v>
+      <c r="S22" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="23" spans="1:66" x14ac:dyDescent="0.25">
@@ -1841,8 +1847,8 @@
       <c r="C23" t="s">
         <v>68</v>
       </c>
-      <c r="T23" t="s">
-        <v>69</v>
+      <c r="S23" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="24" spans="1:66" x14ac:dyDescent="0.25">
@@ -1855,11 +1861,11 @@
       <c r="C24" t="s">
         <v>68</v>
       </c>
-      <c r="W24" t="s">
+      <c r="V24" t="s">
         <v>81</v>
       </c>
       <c r="AX24" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="25" spans="1:66" x14ac:dyDescent="0.25">
@@ -1872,8 +1878,8 @@
       <c r="C25" t="s">
         <v>68</v>
       </c>
-      <c r="T25" t="s">
-        <v>69</v>
+      <c r="S25" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="26" spans="1:66" x14ac:dyDescent="0.25">
@@ -1887,10 +1893,10 @@
         <v>68</v>
       </c>
       <c r="D26" t="s">
-        <v>69</v>
-      </c>
-      <c r="AJ26" t="s">
-        <v>69</v>
+        <v>70</v>
+      </c>
+      <c r="AI26" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="27" spans="1:66" x14ac:dyDescent="0.25">
@@ -1906,20 +1912,20 @@
       <c r="D27" t="s">
         <v>81</v>
       </c>
-      <c r="S27" t="s">
-        <v>70</v>
-      </c>
-      <c r="AG27" t="s">
+      <c r="R27" t="s">
+        <v>69</v>
+      </c>
+      <c r="AF27" t="s">
         <v>81</v>
       </c>
-      <c r="AO27" t="s">
+      <c r="AN27" t="s">
         <v>81</v>
       </c>
       <c r="BG27" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="BN27" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="28" spans="1:66" x14ac:dyDescent="0.25">
@@ -1933,19 +1939,19 @@
         <v>68</v>
       </c>
       <c r="D28" t="s">
-        <v>70</v>
-      </c>
-      <c r="S28" t="s">
-        <v>70</v>
-      </c>
-      <c r="AJ28" t="s">
-        <v>70</v>
+        <v>69</v>
+      </c>
+      <c r="R28" t="s">
+        <v>69</v>
+      </c>
+      <c r="AI28" t="s">
+        <v>69</v>
+      </c>
+      <c r="AN28" t="s">
+        <v>69</v>
       </c>
       <c r="AO28" t="s">
-        <v>70</v>
-      </c>
-      <c r="AP28" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="29" spans="1:66" x14ac:dyDescent="0.25">
@@ -1958,11 +1964,11 @@
       <c r="C29" t="s">
         <v>68</v>
       </c>
-      <c r="V29" t="s">
-        <v>70</v>
-      </c>
-      <c r="AE29" t="s">
-        <v>70</v>
+      <c r="U29" t="s">
+        <v>69</v>
+      </c>
+      <c r="AD29" t="s">
+        <v>69</v>
       </c>
     </row>
     <row r="30" spans="1:66" x14ac:dyDescent="0.25">
@@ -1975,19 +1981,19 @@
       <c r="C30" t="s">
         <v>68</v>
       </c>
+      <c r="T30" t="s">
+        <v>69</v>
+      </c>
       <c r="U30" t="s">
-        <v>70</v>
-      </c>
-      <c r="V30" t="s">
-        <v>70</v>
+        <v>69</v>
+      </c>
+      <c r="AB30" t="s">
+        <v>69</v>
       </c>
       <c r="AC30" t="s">
         <v>70</v>
       </c>
       <c r="AD30" t="s">
-        <v>69</v>
-      </c>
-      <c r="AE30" t="s">
         <v>124</v>
       </c>
     </row>
@@ -2001,8 +2007,8 @@
       <c r="C31" t="s">
         <v>68</v>
       </c>
-      <c r="V31" t="s">
-        <v>70</v>
+      <c r="U31" t="s">
+        <v>69</v>
       </c>
     </row>
     <row r="32" spans="1:66" x14ac:dyDescent="0.25">
@@ -2015,17 +2021,17 @@
       <c r="C32" t="s">
         <v>68</v>
       </c>
+      <c r="T32" t="s">
+        <v>69</v>
+      </c>
       <c r="U32" t="s">
-        <v>70</v>
-      </c>
-      <c r="V32" t="s">
-        <v>70</v>
-      </c>
-      <c r="AC32" t="s">
-        <v>70</v>
-      </c>
-      <c r="AE32" t="s">
-        <v>70</v>
+        <v>69</v>
+      </c>
+      <c r="AB32" t="s">
+        <v>69</v>
+      </c>
+      <c r="AD32" t="s">
+        <v>69</v>
       </c>
     </row>
     <row r="33" spans="1:66" x14ac:dyDescent="0.25">
@@ -2038,14 +2044,14 @@
       <c r="C33" t="s">
         <v>68</v>
       </c>
+      <c r="T33" t="s">
+        <v>69</v>
+      </c>
       <c r="U33" t="s">
-        <v>70</v>
-      </c>
-      <c r="V33" t="s">
-        <v>70</v>
-      </c>
-      <c r="AE33" t="s">
-        <v>70</v>
+        <v>69</v>
+      </c>
+      <c r="AD33" t="s">
+        <v>69</v>
       </c>
     </row>
     <row r="34" spans="1:66" x14ac:dyDescent="0.25">
@@ -2058,14 +2064,14 @@
       <c r="C34" t="s">
         <v>68</v>
       </c>
+      <c r="T34" t="s">
+        <v>69</v>
+      </c>
       <c r="U34" t="s">
-        <v>70</v>
-      </c>
-      <c r="V34" t="s">
-        <v>70</v>
-      </c>
-      <c r="AD34" t="s">
-        <v>69</v>
+        <v>69</v>
+      </c>
+      <c r="AC34" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="35" spans="1:66" x14ac:dyDescent="0.25">
@@ -2078,14 +2084,14 @@
       <c r="C35" t="s">
         <v>68</v>
       </c>
-      <c r="U35" t="s">
+      <c r="T35" t="s">
+        <v>69</v>
+      </c>
+      <c r="AC35" t="s">
         <v>70</v>
       </c>
       <c r="AD35" t="s">
         <v>69</v>
-      </c>
-      <c r="AE35" t="s">
-        <v>70</v>
       </c>
     </row>
     <row r="36" spans="1:66" x14ac:dyDescent="0.25">
@@ -2098,11 +2104,11 @@
       <c r="C36" t="s">
         <v>68</v>
       </c>
-      <c r="U36" t="s">
-        <v>70</v>
-      </c>
-      <c r="AE36" t="s">
-        <v>70</v>
+      <c r="T36" t="s">
+        <v>69</v>
+      </c>
+      <c r="AD36" t="s">
+        <v>69</v>
       </c>
     </row>
     <row r="37" spans="1:66" x14ac:dyDescent="0.25">
@@ -2115,8 +2121,8 @@
       <c r="C37" t="s">
         <v>68</v>
       </c>
-      <c r="U37" t="s">
-        <v>70</v>
+      <c r="T37" t="s">
+        <v>69</v>
       </c>
     </row>
     <row r="38" spans="1:66" x14ac:dyDescent="0.25">
@@ -2129,8 +2135,8 @@
       <c r="C38" t="s">
         <v>68</v>
       </c>
-      <c r="U38" t="s">
-        <v>70</v>
+      <c r="T38" t="s">
+        <v>69</v>
       </c>
     </row>
     <row r="39" spans="1:66" x14ac:dyDescent="0.25">
@@ -2143,14 +2149,14 @@
       <c r="C39" t="s">
         <v>68</v>
       </c>
-      <c r="U39" t="s">
+      <c r="T39" t="s">
+        <v>69</v>
+      </c>
+      <c r="AC39" t="s">
         <v>70</v>
       </c>
       <c r="AD39" t="s">
         <v>69</v>
-      </c>
-      <c r="AE39" t="s">
-        <v>70</v>
       </c>
     </row>
     <row r="40" spans="1:66" x14ac:dyDescent="0.25">
@@ -2163,11 +2169,11 @@
       <c r="C40" t="s">
         <v>68</v>
       </c>
-      <c r="U40" t="s">
-        <v>70</v>
-      </c>
-      <c r="AE40" t="s">
-        <v>70</v>
+      <c r="T40" t="s">
+        <v>69</v>
+      </c>
+      <c r="AD40" t="s">
+        <v>69</v>
       </c>
     </row>
     <row r="41" spans="1:66" x14ac:dyDescent="0.25">
@@ -2180,10 +2186,10 @@
       <c r="C41" t="s">
         <v>68</v>
       </c>
-      <c r="U41" t="s">
-        <v>70</v>
-      </c>
-      <c r="AE41" t="s">
+      <c r="T41" t="s">
+        <v>69</v>
+      </c>
+      <c r="AD41" t="s">
         <v>124</v>
       </c>
     </row>
@@ -2197,8 +2203,8 @@
       <c r="C42" t="s">
         <v>68</v>
       </c>
-      <c r="O42" t="s">
-        <v>70</v>
+      <c r="N42" t="s">
+        <v>69</v>
       </c>
     </row>
     <row r="43" spans="1:66" x14ac:dyDescent="0.25">
@@ -2211,8 +2217,8 @@
       <c r="C43" t="s">
         <v>68</v>
       </c>
-      <c r="AC43" t="s">
-        <v>70</v>
+      <c r="AB43" t="s">
+        <v>69</v>
       </c>
     </row>
     <row r="44" spans="1:66" x14ac:dyDescent="0.25">
@@ -2226,13 +2232,13 @@
         <v>68</v>
       </c>
       <c r="AV44" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="BA44" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="BL44" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
     </row>
     <row r="45" spans="1:66" x14ac:dyDescent="0.25">
@@ -2245,17 +2251,17 @@
       <c r="C45" t="s">
         <v>68</v>
       </c>
-      <c r="O45" t="s">
-        <v>70</v>
-      </c>
-      <c r="AB45" t="s">
+      <c r="N45" t="s">
+        <v>69</v>
+      </c>
+      <c r="AA45" t="s">
         <v>81</v>
       </c>
       <c r="BL45" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="BN45" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="46" spans="1:66" x14ac:dyDescent="0.25">
@@ -2269,10 +2275,10 @@
         <v>68</v>
       </c>
       <c r="G46" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="AY46" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="47" spans="1:66" x14ac:dyDescent="0.25">
@@ -2286,7 +2292,7 @@
         <v>68</v>
       </c>
       <c r="J47" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="48" spans="1:66" x14ac:dyDescent="0.25">
@@ -2300,7 +2306,7 @@
         <v>68</v>
       </c>
       <c r="J48" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="49" spans="1:65" x14ac:dyDescent="0.25">
@@ -2314,10 +2320,10 @@
         <v>68</v>
       </c>
       <c r="BJ49" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="BM49" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="50" spans="1:65" x14ac:dyDescent="0.25">
@@ -2330,17 +2336,17 @@
       <c r="C50" t="s">
         <v>68</v>
       </c>
-      <c r="X50" t="s">
-        <v>69</v>
+      <c r="W50" t="s">
+        <v>70</v>
+      </c>
+      <c r="AP50" t="s">
+        <v>70</v>
       </c>
       <c r="AQ50" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="AR50" t="s">
-        <v>69</v>
-      </c>
-      <c r="AS50" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
     </row>
     <row r="51" spans="1:65" x14ac:dyDescent="0.25">
@@ -2353,26 +2359,26 @@
       <c r="C51" t="s">
         <v>68</v>
       </c>
-      <c r="L51" t="s">
-        <v>69</v>
-      </c>
-      <c r="U51" t="s">
-        <v>70</v>
-      </c>
-      <c r="AF51" t="s">
+      <c r="T51" t="s">
+        <v>69</v>
+      </c>
+      <c r="AE51" t="s">
+        <v>69</v>
+      </c>
+      <c r="AT51" t="s">
         <v>70</v>
       </c>
       <c r="AU51" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="AW51" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="BE51" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="BL51" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
     </row>
     <row r="52" spans="1:65" x14ac:dyDescent="0.25">
@@ -2385,14 +2391,14 @@
       <c r="C52" t="s">
         <v>68</v>
       </c>
-      <c r="P52" t="s">
-        <v>70</v>
-      </c>
-      <c r="R52" t="s">
-        <v>70</v>
-      </c>
-      <c r="AD52" t="s">
-        <v>70</v>
+      <c r="O52" t="s">
+        <v>69</v>
+      </c>
+      <c r="Q52" t="s">
+        <v>69</v>
+      </c>
+      <c r="AC52" t="s">
+        <v>69</v>
       </c>
     </row>
     <row r="53" spans="1:65" x14ac:dyDescent="0.25">
@@ -2406,28 +2412,28 @@
         <v>68</v>
       </c>
       <c r="H53" t="s">
-        <v>70</v>
-      </c>
-      <c r="N53" t="s">
-        <v>70</v>
-      </c>
-      <c r="Y53" t="s">
-        <v>70</v>
-      </c>
-      <c r="AF53" t="s">
-        <v>70</v>
-      </c>
-      <c r="AI53" t="s">
-        <v>70</v>
+        <v>69</v>
+      </c>
+      <c r="M53" t="s">
+        <v>69</v>
+      </c>
+      <c r="X53" t="s">
+        <v>69</v>
+      </c>
+      <c r="AE53" t="s">
+        <v>69</v>
+      </c>
+      <c r="AH53" t="s">
+        <v>69</v>
       </c>
       <c r="AU53" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="AZ53" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="BE53" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="54" spans="1:65" x14ac:dyDescent="0.25">
@@ -2440,8 +2446,8 @@
       <c r="C54" t="s">
         <v>68</v>
       </c>
-      <c r="AD54" t="s">
-        <v>69</v>
+      <c r="AC54" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="55" spans="1:65" x14ac:dyDescent="0.25">
@@ -2455,43 +2461,43 @@
         <v>68</v>
       </c>
       <c r="H55" t="s">
-        <v>70</v>
-      </c>
-      <c r="N55" t="s">
-        <v>70</v>
-      </c>
-      <c r="P55" t="s">
-        <v>70</v>
+        <v>69</v>
+      </c>
+      <c r="M55" t="s">
+        <v>69</v>
+      </c>
+      <c r="O55" t="s">
+        <v>69</v>
+      </c>
+      <c r="T55" t="s">
+        <v>69</v>
       </c>
       <c r="U55" t="s">
-        <v>70</v>
-      </c>
-      <c r="V55" t="s">
-        <v>70</v>
-      </c>
-      <c r="Y55" t="s">
-        <v>70</v>
-      </c>
-      <c r="AD55" t="s">
-        <v>70</v>
-      </c>
-      <c r="AF55" t="s">
-        <v>70</v>
-      </c>
-      <c r="AI55" t="s">
-        <v>70</v>
+        <v>69</v>
+      </c>
+      <c r="X55" t="s">
+        <v>69</v>
+      </c>
+      <c r="AC55" t="s">
+        <v>69</v>
+      </c>
+      <c r="AE55" t="s">
+        <v>69</v>
+      </c>
+      <c r="AH55" t="s">
+        <v>69</v>
       </c>
       <c r="AU55" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="AW55" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="AZ55" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="BE55" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="56" spans="1:65" x14ac:dyDescent="0.25">
@@ -2505,43 +2511,43 @@
         <v>68</v>
       </c>
       <c r="H56" t="s">
-        <v>70</v>
-      </c>
-      <c r="N56" t="s">
-        <v>70</v>
-      </c>
-      <c r="P56" t="s">
-        <v>70</v>
+        <v>69</v>
+      </c>
+      <c r="M56" t="s">
+        <v>69</v>
+      </c>
+      <c r="O56" t="s">
+        <v>69</v>
+      </c>
+      <c r="T56" t="s">
+        <v>69</v>
       </c>
       <c r="U56" t="s">
-        <v>70</v>
-      </c>
-      <c r="V56" t="s">
-        <v>70</v>
-      </c>
-      <c r="Y56" t="s">
-        <v>70</v>
-      </c>
-      <c r="AD56" t="s">
-        <v>70</v>
-      </c>
-      <c r="AF56" t="s">
-        <v>70</v>
-      </c>
-      <c r="AI56" t="s">
-        <v>70</v>
+        <v>69</v>
+      </c>
+      <c r="X56" t="s">
+        <v>69</v>
+      </c>
+      <c r="AC56" t="s">
+        <v>69</v>
+      </c>
+      <c r="AE56" t="s">
+        <v>69</v>
+      </c>
+      <c r="AH56" t="s">
+        <v>69</v>
       </c>
       <c r="AU56" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="AW56" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="AZ56" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="BE56" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="57" spans="1:65" x14ac:dyDescent="0.25">
@@ -2554,8 +2560,8 @@
       <c r="C57" t="s">
         <v>68</v>
       </c>
-      <c r="Y57" t="s">
-        <v>70</v>
+      <c r="X57" t="s">
+        <v>69</v>
       </c>
     </row>
     <row r="58" spans="1:65" x14ac:dyDescent="0.25">
@@ -2568,8 +2574,8 @@
       <c r="C58" t="s">
         <v>68</v>
       </c>
-      <c r="N58" t="s">
-        <v>70</v>
+      <c r="M58" t="s">
+        <v>69</v>
       </c>
     </row>
     <row r="59" spans="1:65" x14ac:dyDescent="0.25">
@@ -2582,8 +2588,8 @@
       <c r="C59" t="s">
         <v>68</v>
       </c>
-      <c r="R59" t="s">
-        <v>70</v>
+      <c r="Q59" t="s">
+        <v>69</v>
       </c>
     </row>
     <row r="60" spans="1:65" x14ac:dyDescent="0.25">
@@ -2596,8 +2602,8 @@
       <c r="C60" t="s">
         <v>68</v>
       </c>
-      <c r="Y60" t="s">
-        <v>70</v>
+      <c r="X60" t="s">
+        <v>69</v>
       </c>
     </row>
     <row r="61" spans="1:65" x14ac:dyDescent="0.25">
@@ -2611,16 +2617,16 @@
         <v>68</v>
       </c>
       <c r="E61" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="F61" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="I61" t="s">
-        <v>70</v>
-      </c>
-      <c r="M61" t="s">
-        <v>70</v>
+        <v>69</v>
+      </c>
+      <c r="L61" t="s">
+        <v>69</v>
       </c>
     </row>
     <row r="62" spans="1:65" x14ac:dyDescent="0.25">
@@ -2633,8 +2639,8 @@
       <c r="C62" t="s">
         <v>68</v>
       </c>
-      <c r="N62" t="s">
-        <v>70</v>
+      <c r="M62" t="s">
+        <v>69</v>
       </c>
     </row>
     <row r="63" spans="1:65" x14ac:dyDescent="0.25">
@@ -2647,8 +2653,8 @@
       <c r="C63" t="s">
         <v>68</v>
       </c>
-      <c r="Y63" t="s">
-        <v>70</v>
+      <c r="X63" t="s">
+        <v>69</v>
       </c>
     </row>
     <row r="64" spans="1:65" x14ac:dyDescent="0.25">
@@ -2661,8 +2667,8 @@
       <c r="C64" t="s">
         <v>68</v>
       </c>
-      <c r="V64" t="s">
-        <v>70</v>
+      <c r="U64" t="s">
+        <v>69</v>
       </c>
     </row>
     <row r="65" spans="1:66" x14ac:dyDescent="0.25">
@@ -2675,8 +2681,8 @@
       <c r="C65" t="s">
         <v>68</v>
       </c>
-      <c r="AC65" t="s">
-        <v>70</v>
+      <c r="AB65" t="s">
+        <v>69</v>
       </c>
     </row>
     <row r="66" spans="1:66" x14ac:dyDescent="0.25">
@@ -2689,8 +2695,8 @@
       <c r="C66" t="s">
         <v>68</v>
       </c>
-      <c r="V66" t="s">
-        <v>70</v>
+      <c r="U66" t="s">
+        <v>69</v>
       </c>
     </row>
     <row r="67" spans="1:66" x14ac:dyDescent="0.25">
@@ -2704,52 +2710,52 @@
         <v>68</v>
       </c>
       <c r="H67" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="K67" t="s">
-        <v>70</v>
-      </c>
-      <c r="N67" t="s">
-        <v>70</v>
-      </c>
-      <c r="P67" t="s">
-        <v>70</v>
-      </c>
-      <c r="R67" t="s">
-        <v>70</v>
-      </c>
-      <c r="Y67" t="s">
-        <v>70</v>
-      </c>
-      <c r="AB67" t="s">
+        <v>69</v>
+      </c>
+      <c r="M67" t="s">
+        <v>69</v>
+      </c>
+      <c r="O67" t="s">
+        <v>69</v>
+      </c>
+      <c r="Q67" t="s">
+        <v>69</v>
+      </c>
+      <c r="X67" t="s">
+        <v>69</v>
+      </c>
+      <c r="AA67" t="s">
         <v>81</v>
       </c>
+      <c r="AC67" t="s">
+        <v>69</v>
+      </c>
       <c r="AD67" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="AE67" t="s">
-        <v>70</v>
-      </c>
-      <c r="AF67" t="s">
-        <v>70</v>
-      </c>
-      <c r="AI67" t="s">
-        <v>70</v>
-      </c>
-      <c r="AO67" t="s">
+        <v>69</v>
+      </c>
+      <c r="AH67" t="s">
+        <v>69</v>
+      </c>
+      <c r="AN67" t="s">
         <v>81</v>
       </c>
       <c r="AU67" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="AW67" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="AZ67" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="BE67" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="68" spans="1:66" x14ac:dyDescent="0.25">
@@ -2763,22 +2769,22 @@
         <v>68</v>
       </c>
       <c r="D68" t="s">
-        <v>70</v>
-      </c>
-      <c r="T68" t="s">
-        <v>69</v>
-      </c>
-      <c r="AA68" t="s">
-        <v>69</v>
-      </c>
-      <c r="AJ68" t="s">
-        <v>70</v>
+        <v>69</v>
+      </c>
+      <c r="S68" t="s">
+        <v>70</v>
+      </c>
+      <c r="Z68" t="s">
+        <v>70</v>
+      </c>
+      <c r="AI68" t="s">
+        <v>69</v>
       </c>
       <c r="BK68" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="BN68" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="69" spans="1:66" x14ac:dyDescent="0.25">
@@ -2791,17 +2797,17 @@
       <c r="C69" t="s">
         <v>68</v>
       </c>
-      <c r="X69" t="s">
-        <v>69</v>
+      <c r="W69" t="s">
+        <v>70</v>
+      </c>
+      <c r="AP69" t="s">
+        <v>70</v>
       </c>
       <c r="AQ69" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="AR69" t="s">
-        <v>69</v>
-      </c>
-      <c r="AS69" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
     </row>
     <row r="70" spans="1:66" x14ac:dyDescent="0.25">
@@ -2814,8 +2820,8 @@
       <c r="C70" t="s">
         <v>68</v>
       </c>
-      <c r="Y70" t="s">
-        <v>70</v>
+      <c r="X70" t="s">
+        <v>69</v>
       </c>
     </row>
     <row r="71" spans="1:66" x14ac:dyDescent="0.25">
@@ -2828,14 +2834,14 @@
       <c r="C71" t="s">
         <v>68</v>
       </c>
-      <c r="N71" t="s">
-        <v>70</v>
-      </c>
-      <c r="Y71" t="s">
-        <v>70</v>
-      </c>
-      <c r="AD71" t="s">
-        <v>69</v>
+      <c r="M71" t="s">
+        <v>69</v>
+      </c>
+      <c r="X71" t="s">
+        <v>69</v>
+      </c>
+      <c r="AC71" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="72" spans="1:66" x14ac:dyDescent="0.25">
@@ -2848,8 +2854,8 @@
       <c r="C72" t="s">
         <v>68</v>
       </c>
-      <c r="Y72" t="s">
-        <v>70</v>
+      <c r="X72" t="s">
+        <v>69</v>
       </c>
     </row>
     <row r="73" spans="1:66" x14ac:dyDescent="0.25">
@@ -2862,8 +2868,8 @@
       <c r="C73" t="s">
         <v>68</v>
       </c>
-      <c r="N73" t="s">
-        <v>70</v>
+      <c r="M73" t="s">
+        <v>69</v>
       </c>
     </row>
     <row r="74" spans="1:66" x14ac:dyDescent="0.25">
@@ -2876,14 +2882,14 @@
       <c r="C74" t="s">
         <v>68</v>
       </c>
-      <c r="N74" t="s">
-        <v>70</v>
-      </c>
-      <c r="Y74" t="s">
-        <v>70</v>
-      </c>
-      <c r="AD74" t="s">
-        <v>69</v>
+      <c r="M74" t="s">
+        <v>69</v>
+      </c>
+      <c r="X74" t="s">
+        <v>69</v>
+      </c>
+      <c r="AC74" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="75" spans="1:66" x14ac:dyDescent="0.25">
@@ -2896,8 +2902,8 @@
       <c r="C75" t="s">
         <v>68</v>
       </c>
-      <c r="AD75" t="s">
-        <v>69</v>
+      <c r="AC75" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="76" spans="1:66" x14ac:dyDescent="0.25">
@@ -2910,14 +2916,14 @@
       <c r="C76" t="s">
         <v>68</v>
       </c>
+      <c r="T76" t="s">
+        <v>69</v>
+      </c>
       <c r="U76" t="s">
-        <v>70</v>
-      </c>
-      <c r="V76" t="s">
-        <v>70</v>
-      </c>
-      <c r="AC76" t="s">
-        <v>70</v>
+        <v>69</v>
+      </c>
+      <c r="AB76" t="s">
+        <v>69</v>
       </c>
     </row>
     <row r="77" spans="1:66" x14ac:dyDescent="0.25">
@@ -2930,11 +2936,11 @@
       <c r="C77" t="s">
         <v>68</v>
       </c>
+      <c r="T77" t="s">
+        <v>69</v>
+      </c>
       <c r="U77" t="s">
-        <v>70</v>
-      </c>
-      <c r="V77" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="78" spans="1:66" x14ac:dyDescent="0.25">
@@ -2947,8 +2953,8 @@
       <c r="C78" t="s">
         <v>68</v>
       </c>
-      <c r="O78" t="s">
-        <v>69</v>
+      <c r="N78" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="79" spans="1:66" x14ac:dyDescent="0.25">
@@ -2961,7 +2967,7 @@
       <c r="C79" t="s">
         <v>68</v>
       </c>
-      <c r="AB79" t="s">
+      <c r="AA79" t="s">
         <v>81</v>
       </c>
     </row>
@@ -2975,8 +2981,8 @@
       <c r="C80" t="s">
         <v>68</v>
       </c>
-      <c r="O80" t="s">
-        <v>70</v>
+      <c r="N80" t="s">
+        <v>69</v>
       </c>
     </row>
     <row r="81" spans="1:65" x14ac:dyDescent="0.25">
@@ -2989,14 +2995,14 @@
       <c r="C81" t="s">
         <v>212</v>
       </c>
-      <c r="L81" t="s">
-        <v>69</v>
-      </c>
-      <c r="V81" t="s">
-        <v>70</v>
-      </c>
-      <c r="AF81" t="s">
-        <v>69</v>
+      <c r="U81" t="s">
+        <v>69</v>
+      </c>
+      <c r="AE81" t="s">
+        <v>70</v>
+      </c>
+      <c r="AT81" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="82" spans="1:65" x14ac:dyDescent="0.25">
@@ -3009,29 +3015,29 @@
       <c r="C82" t="s">
         <v>212</v>
       </c>
-      <c r="M82" t="s">
-        <v>70</v>
-      </c>
-      <c r="AA82" t="s">
+      <c r="L82" t="s">
+        <v>69</v>
+      </c>
+      <c r="Z82" t="s">
+        <v>70</v>
+      </c>
+      <c r="AL82" t="s">
         <v>69</v>
       </c>
       <c r="AM82" t="s">
         <v>70</v>
       </c>
-      <c r="AN82" t="s">
-        <v>69</v>
-      </c>
       <c r="AX82" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="BC82" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="BD82" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="BH82" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="83" spans="1:65" x14ac:dyDescent="0.25">
@@ -3044,20 +3050,20 @@
       <c r="C83" t="s">
         <v>212</v>
       </c>
+      <c r="T83" t="s">
+        <v>69</v>
+      </c>
       <c r="U83" t="s">
-        <v>70</v>
-      </c>
-      <c r="V83" t="s">
-        <v>70</v>
-      </c>
-      <c r="AT83" t="s">
-        <v>70</v>
+        <v>69</v>
+      </c>
+      <c r="AS83" t="s">
+        <v>69</v>
       </c>
       <c r="AU83" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="BE83" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="84" spans="1:65" x14ac:dyDescent="0.25">
@@ -3070,8 +3076,8 @@
       <c r="C84" t="s">
         <v>212</v>
       </c>
-      <c r="U84" t="s">
-        <v>70</v>
+      <c r="T84" t="s">
+        <v>69</v>
       </c>
     </row>
     <row r="85" spans="1:65" x14ac:dyDescent="0.25">
@@ -3084,14 +3090,14 @@
       <c r="C85" t="s">
         <v>212</v>
       </c>
-      <c r="L85" t="s">
-        <v>69</v>
-      </c>
-      <c r="V85" t="s">
-        <v>70</v>
-      </c>
-      <c r="AF85" t="s">
-        <v>69</v>
+      <c r="U85" t="s">
+        <v>69</v>
+      </c>
+      <c r="AE85" t="s">
+        <v>70</v>
+      </c>
+      <c r="AT85" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="86" spans="1:65" x14ac:dyDescent="0.25">
@@ -3104,11 +3110,11 @@
       <c r="C86" t="s">
         <v>212</v>
       </c>
-      <c r="W86" t="s">
+      <c r="V86" t="s">
         <v>81</v>
       </c>
       <c r="AX86" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="87" spans="1:65" x14ac:dyDescent="0.25">
@@ -3122,10 +3128,10 @@
         <v>212</v>
       </c>
       <c r="BC87" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="BH87" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="88" spans="1:65" x14ac:dyDescent="0.25">
@@ -3142,7 +3148,7 @@
         <v>81</v>
       </c>
       <c r="BH88" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="89" spans="1:65" x14ac:dyDescent="0.25">
@@ -3155,17 +3161,17 @@
       <c r="C89" t="s">
         <v>212</v>
       </c>
-      <c r="AM89" t="s">
-        <v>69</v>
+      <c r="AL89" t="s">
+        <v>70</v>
       </c>
       <c r="BC89" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="BD89" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="BH89" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="90" spans="1:65" x14ac:dyDescent="0.25">
@@ -3179,70 +3185,70 @@
         <v>212</v>
       </c>
       <c r="G90" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="J90" t="s">
         <v>81</v>
       </c>
-      <c r="O90" t="s">
-        <v>70</v>
+      <c r="N90" t="s">
+        <v>69</v>
+      </c>
+      <c r="T90" t="s">
+        <v>69</v>
       </c>
       <c r="U90" t="s">
-        <v>70</v>
-      </c>
-      <c r="V90" t="s">
-        <v>70</v>
-      </c>
-      <c r="Z90" t="s">
+        <v>69</v>
+      </c>
+      <c r="Y90" t="s">
+        <v>70</v>
+      </c>
+      <c r="AA90" t="s">
         <v>69</v>
       </c>
       <c r="AB90" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="AC90" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="AD90" t="s">
-        <v>70</v>
-      </c>
-      <c r="AE90" t="s">
-        <v>70</v>
-      </c>
-      <c r="AH90" t="s">
-        <v>70</v>
-      </c>
-      <c r="AK90" t="s">
-        <v>70</v>
-      </c>
-      <c r="AT90" t="s">
-        <v>70</v>
+        <v>69</v>
+      </c>
+      <c r="AG90" t="s">
+        <v>69</v>
+      </c>
+      <c r="AJ90" t="s">
+        <v>69</v>
+      </c>
+      <c r="AS90" t="s">
+        <v>69</v>
       </c>
       <c r="AU90" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="AW90" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="AY90" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="AZ90" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="BB90" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="BE90" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="BH90" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="BL90" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="BM90" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="91" spans="1:65" x14ac:dyDescent="0.25">
@@ -3256,73 +3262,73 @@
         <v>212</v>
       </c>
       <c r="G91" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="J91" t="s">
         <v>81</v>
       </c>
-      <c r="O91" t="s">
-        <v>70</v>
+      <c r="N91" t="s">
+        <v>69</v>
+      </c>
+      <c r="T91" t="s">
+        <v>69</v>
       </c>
       <c r="U91" t="s">
-        <v>70</v>
-      </c>
-      <c r="V91" t="s">
-        <v>70</v>
-      </c>
-      <c r="Z91" t="s">
+        <v>69</v>
+      </c>
+      <c r="Y91" t="s">
+        <v>70</v>
+      </c>
+      <c r="AA91" t="s">
         <v>69</v>
       </c>
       <c r="AB91" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="AC91" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="AD91" t="s">
-        <v>70</v>
-      </c>
-      <c r="AE91" t="s">
-        <v>70</v>
-      </c>
-      <c r="AH91" t="s">
-        <v>70</v>
-      </c>
-      <c r="AK91" t="s">
-        <v>70</v>
-      </c>
-      <c r="AT91" t="s">
-        <v>70</v>
+        <v>69</v>
+      </c>
+      <c r="AG91" t="s">
+        <v>69</v>
+      </c>
+      <c r="AJ91" t="s">
+        <v>69</v>
+      </c>
+      <c r="AS91" t="s">
+        <v>69</v>
       </c>
       <c r="AU91" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="AW91" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="AY91" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="AZ91" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="BB91" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="BE91" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="BG91" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="BH91" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="BL91" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="BM91" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="92" spans="1:65" x14ac:dyDescent="0.25">
@@ -3336,70 +3342,70 @@
         <v>212</v>
       </c>
       <c r="G92" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="J92" t="s">
         <v>81</v>
       </c>
-      <c r="O92" t="s">
-        <v>70</v>
+      <c r="N92" t="s">
+        <v>69</v>
+      </c>
+      <c r="T92" t="s">
+        <v>69</v>
       </c>
       <c r="U92" t="s">
-        <v>70</v>
-      </c>
-      <c r="V92" t="s">
-        <v>70</v>
-      </c>
-      <c r="Z92" t="s">
+        <v>69</v>
+      </c>
+      <c r="Y92" t="s">
+        <v>70</v>
+      </c>
+      <c r="AA92" t="s">
         <v>69</v>
       </c>
       <c r="AB92" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="AC92" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="AD92" t="s">
-        <v>70</v>
-      </c>
-      <c r="AE92" t="s">
-        <v>70</v>
-      </c>
-      <c r="AH92" t="s">
-        <v>70</v>
-      </c>
-      <c r="AK92" t="s">
-        <v>70</v>
-      </c>
-      <c r="AT92" t="s">
-        <v>70</v>
+        <v>69</v>
+      </c>
+      <c r="AG92" t="s">
+        <v>69</v>
+      </c>
+      <c r="AJ92" t="s">
+        <v>69</v>
+      </c>
+      <c r="AS92" t="s">
+        <v>69</v>
       </c>
       <c r="AU92" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="AW92" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="AY92" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="AZ92" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="BB92" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="BE92" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="BH92" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="BL92" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="BM92" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="93" spans="1:65" x14ac:dyDescent="0.25">
@@ -3412,8 +3418,8 @@
       <c r="C93" t="s">
         <v>212</v>
       </c>
-      <c r="AT93" t="s">
-        <v>70</v>
+      <c r="AS93" t="s">
+        <v>69</v>
       </c>
     </row>
     <row r="94" spans="1:65" x14ac:dyDescent="0.25">
@@ -3426,8 +3432,8 @@
       <c r="C94" t="s">
         <v>212</v>
       </c>
-      <c r="AT94" t="s">
-        <v>70</v>
+      <c r="AS94" t="s">
+        <v>69</v>
       </c>
     </row>
     <row r="95" spans="1:65" x14ac:dyDescent="0.25">
@@ -3440,11 +3446,11 @@
       <c r="C95" t="s">
         <v>212</v>
       </c>
-      <c r="V95" t="s">
-        <v>70</v>
-      </c>
-      <c r="AE95" t="s">
-        <v>70</v>
+      <c r="U95" t="s">
+        <v>69</v>
+      </c>
+      <c r="AD95" t="s">
+        <v>69</v>
       </c>
     </row>
     <row r="96" spans="1:65" x14ac:dyDescent="0.25">
@@ -3457,14 +3463,14 @@
       <c r="C96" t="s">
         <v>212</v>
       </c>
-      <c r="V96" t="s">
-        <v>70</v>
-      </c>
-      <c r="AD96" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="97" spans="1:61" x14ac:dyDescent="0.25">
+      <c r="U96" t="s">
+        <v>69</v>
+      </c>
+      <c r="AC96" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="97" spans="1:66" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
         <v>92</v>
       </c>
@@ -3474,11 +3480,11 @@
       <c r="C97" t="s">
         <v>212</v>
       </c>
-      <c r="AE97" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="98" spans="1:61" x14ac:dyDescent="0.25">
+      <c r="AD97" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="98" spans="1:66" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
         <v>92</v>
       </c>
@@ -3488,23 +3494,23 @@
       <c r="C98" t="s">
         <v>212</v>
       </c>
-      <c r="V98" t="s">
-        <v>70</v>
-      </c>
-      <c r="Y98" t="s">
-        <v>70</v>
+      <c r="U98" t="s">
+        <v>69</v>
+      </c>
+      <c r="X98" t="s">
+        <v>69</v>
+      </c>
+      <c r="AB98" t="s">
+        <v>69</v>
       </c>
       <c r="AC98" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="AD98" t="s">
-        <v>70</v>
-      </c>
-      <c r="AE98" t="s">
         <v>124</v>
       </c>
     </row>
-    <row r="99" spans="1:61" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:66" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
         <v>221</v>
       </c>
@@ -3514,14 +3520,14 @@
       <c r="C99" t="s">
         <v>212</v>
       </c>
-      <c r="V99" t="s">
-        <v>70</v>
-      </c>
-      <c r="AD99" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="100" spans="1:61" x14ac:dyDescent="0.25">
+      <c r="U99" t="s">
+        <v>69</v>
+      </c>
+      <c r="AC99" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="100" spans="1:66" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
         <v>223</v>
       </c>
@@ -3531,17 +3537,17 @@
       <c r="C100" t="s">
         <v>212</v>
       </c>
-      <c r="V100" t="s">
-        <v>70</v>
+      <c r="U100" t="s">
+        <v>69</v>
+      </c>
+      <c r="AB100" t="s">
+        <v>69</v>
       </c>
       <c r="AC100" t="s">
-        <v>70</v>
-      </c>
-      <c r="AD100" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="101" spans="1:61" x14ac:dyDescent="0.25">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="101" spans="1:66" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
         <v>95</v>
       </c>
@@ -3551,14 +3557,14 @@
       <c r="C101" t="s">
         <v>212</v>
       </c>
-      <c r="V101" t="s">
-        <v>70</v>
-      </c>
-      <c r="AD101" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="102" spans="1:61" x14ac:dyDescent="0.25">
+      <c r="U101" t="s">
+        <v>69</v>
+      </c>
+      <c r="AC101" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="102" spans="1:66" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
         <v>97</v>
       </c>
@@ -3568,14 +3574,14 @@
       <c r="C102" t="s">
         <v>212</v>
       </c>
-      <c r="V102" t="s">
-        <v>70</v>
-      </c>
-      <c r="AE102" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="103" spans="1:61" x14ac:dyDescent="0.25">
+      <c r="U102" t="s">
+        <v>69</v>
+      </c>
+      <c r="AD102" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="103" spans="1:66" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
         <v>99</v>
       </c>
@@ -3585,11 +3591,11 @@
       <c r="C103" t="s">
         <v>212</v>
       </c>
-      <c r="V103" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="104" spans="1:61" x14ac:dyDescent="0.25">
+      <c r="U103" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="104" spans="1:66" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
         <v>101</v>
       </c>
@@ -3600,43 +3606,49 @@
         <v>212</v>
       </c>
       <c r="H104" t="s">
-        <v>70</v>
-      </c>
-      <c r="V104" t="s">
-        <v>70</v>
-      </c>
-      <c r="Y104" t="s">
-        <v>70</v>
+        <v>69</v>
+      </c>
+      <c r="U104" t="s">
+        <v>69</v>
+      </c>
+      <c r="X104" t="s">
+        <v>69</v>
+      </c>
+      <c r="AB104" t="s">
+        <v>69</v>
       </c>
       <c r="AC104" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="AD104" t="s">
-        <v>70</v>
-      </c>
-      <c r="AE104" t="s">
-        <v>70</v>
-      </c>
-      <c r="AH104" t="s">
-        <v>70</v>
+        <v>69</v>
+      </c>
+      <c r="AG104" t="s">
+        <v>69</v>
+      </c>
+      <c r="AS104" t="s">
+        <v>69</v>
       </c>
       <c r="AT104" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="AU104" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="AW104" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="BB104" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="BE104" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="105" spans="1:61" x14ac:dyDescent="0.25">
+        <v>69</v>
+      </c>
+      <c r="BN104" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="105" spans="1:66" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
         <v>103</v>
       </c>
@@ -3646,17 +3658,17 @@
       <c r="C105" t="s">
         <v>212</v>
       </c>
-      <c r="AN105" t="s">
-        <v>69</v>
+      <c r="AM105" t="s">
+        <v>70</v>
       </c>
       <c r="BH105" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="BI105" t="s">
         <v>81</v>
       </c>
     </row>
-    <row r="106" spans="1:61" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:66" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
         <v>103</v>
       </c>
@@ -3667,16 +3679,16 @@
         <v>212</v>
       </c>
       <c r="E106" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="F106" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="BH106" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="107" spans="1:61" x14ac:dyDescent="0.25">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="107" spans="1:66" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
         <v>226</v>
       </c>
@@ -3687,10 +3699,10 @@
         <v>212</v>
       </c>
       <c r="BH107" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="108" spans="1:61" x14ac:dyDescent="0.25">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="108" spans="1:66" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
         <v>105</v>
       </c>
@@ -3700,17 +3712,17 @@
       <c r="C108" t="s">
         <v>212</v>
       </c>
+      <c r="AM108" t="s">
+        <v>70</v>
+      </c>
       <c r="AN108" t="s">
-        <v>69</v>
-      </c>
-      <c r="AO108" t="s">
         <v>81</v>
       </c>
       <c r="BH108" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="109" spans="1:61" x14ac:dyDescent="0.25">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="109" spans="1:66" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
         <v>105</v>
       </c>
@@ -3721,10 +3733,10 @@
         <v>212</v>
       </c>
       <c r="BH109" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="110" spans="1:61" x14ac:dyDescent="0.25">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="110" spans="1:66" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
         <v>108</v>
       </c>
@@ -3734,17 +3746,17 @@
       <c r="C110" t="s">
         <v>212</v>
       </c>
-      <c r="T110" t="s">
-        <v>69</v>
-      </c>
-      <c r="AL110" t="s">
-        <v>70</v>
+      <c r="S110" t="s">
+        <v>70</v>
+      </c>
+      <c r="AK110" t="s">
+        <v>69</v>
       </c>
       <c r="BH110" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="111" spans="1:61" x14ac:dyDescent="0.25">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="111" spans="1:66" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
         <v>110</v>
       </c>
@@ -3754,17 +3766,17 @@
       <c r="C111" t="s">
         <v>212</v>
       </c>
-      <c r="T111" t="s">
-        <v>69</v>
-      </c>
-      <c r="AL111" t="s">
-        <v>70</v>
+      <c r="S111" t="s">
+        <v>70</v>
+      </c>
+      <c r="AK111" t="s">
+        <v>69</v>
       </c>
       <c r="BH111" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="112" spans="1:61" x14ac:dyDescent="0.25">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="112" spans="1:66" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
         <v>112</v>
       </c>
@@ -3774,11 +3786,11 @@
       <c r="C112" t="s">
         <v>212</v>
       </c>
-      <c r="W112" t="s">
+      <c r="V112" t="s">
         <v>81</v>
       </c>
       <c r="AX112" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="113" spans="1:60" x14ac:dyDescent="0.25">
@@ -3791,14 +3803,14 @@
       <c r="C113" t="s">
         <v>212</v>
       </c>
-      <c r="T113" t="s">
-        <v>69</v>
-      </c>
-      <c r="AL113" t="s">
-        <v>70</v>
+      <c r="S113" t="s">
+        <v>70</v>
+      </c>
+      <c r="AK113" t="s">
+        <v>69</v>
       </c>
       <c r="BH113" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="114" spans="1:60" x14ac:dyDescent="0.25">
@@ -3812,7 +3824,7 @@
         <v>212</v>
       </c>
       <c r="BH114" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="115" spans="1:60" x14ac:dyDescent="0.25">
@@ -3826,7 +3838,7 @@
         <v>212</v>
       </c>
       <c r="BH115" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="116" spans="1:60" x14ac:dyDescent="0.25">
@@ -3839,14 +3851,14 @@
       <c r="C116" t="s">
         <v>212</v>
       </c>
+      <c r="AM116" t="s">
+        <v>70</v>
+      </c>
       <c r="AN116" t="s">
-        <v>69</v>
-      </c>
-      <c r="AO116" t="s">
         <v>81</v>
       </c>
       <c r="BH116" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="117" spans="1:60" x14ac:dyDescent="0.25">
@@ -3859,14 +3871,14 @@
       <c r="C117" t="s">
         <v>212</v>
       </c>
-      <c r="AJ117" t="s">
-        <v>70</v>
-      </c>
-      <c r="AO117" t="s">
-        <v>70</v>
+      <c r="AI117" t="s">
+        <v>69</v>
+      </c>
+      <c r="AN117" t="s">
+        <v>69</v>
       </c>
       <c r="BH117" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="118" spans="1:60" x14ac:dyDescent="0.25">
@@ -3880,7 +3892,7 @@
         <v>212</v>
       </c>
       <c r="BB118" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="119" spans="1:60" x14ac:dyDescent="0.25">
@@ -3893,20 +3905,20 @@
       <c r="C119" t="s">
         <v>212</v>
       </c>
+      <c r="T119" t="s">
+        <v>69</v>
+      </c>
       <c r="U119" t="s">
-        <v>70</v>
-      </c>
-      <c r="V119" t="s">
-        <v>70</v>
-      </c>
-      <c r="AN119" t="s">
-        <v>70</v>
+        <v>69</v>
+      </c>
+      <c r="AM119" t="s">
+        <v>69</v>
       </c>
       <c r="AZ119" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="BH119" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="120" spans="1:60" x14ac:dyDescent="0.25">
@@ -3919,20 +3931,20 @@
       <c r="C120" t="s">
         <v>212</v>
       </c>
+      <c r="T120" t="s">
+        <v>69</v>
+      </c>
       <c r="U120" t="s">
-        <v>70</v>
-      </c>
-      <c r="V120" t="s">
-        <v>70</v>
-      </c>
-      <c r="AE120" t="s">
-        <v>70</v>
+        <v>69</v>
+      </c>
+      <c r="AD120" t="s">
+        <v>69</v>
       </c>
       <c r="BD120" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="BH120" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="121" spans="1:60" x14ac:dyDescent="0.25">
@@ -3945,17 +3957,17 @@
       <c r="C121" t="s">
         <v>212</v>
       </c>
+      <c r="T121" t="s">
+        <v>69</v>
+      </c>
       <c r="U121" t="s">
-        <v>70</v>
-      </c>
-      <c r="V121" t="s">
-        <v>70</v>
-      </c>
-      <c r="AE121" t="s">
-        <v>70</v>
+        <v>69</v>
+      </c>
+      <c r="AD121" t="s">
+        <v>69</v>
       </c>
       <c r="BH121" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="122" spans="1:60" x14ac:dyDescent="0.25">
@@ -3968,17 +3980,17 @@
       <c r="C122" t="s">
         <v>212</v>
       </c>
+      <c r="T122" t="s">
+        <v>69</v>
+      </c>
       <c r="U122" t="s">
-        <v>70</v>
-      </c>
-      <c r="V122" t="s">
-        <v>70</v>
-      </c>
-      <c r="AC122" t="s">
-        <v>70</v>
-      </c>
-      <c r="AN122" t="s">
-        <v>70</v>
+        <v>69</v>
+      </c>
+      <c r="AB122" t="s">
+        <v>69</v>
+      </c>
+      <c r="AM122" t="s">
+        <v>69</v>
       </c>
     </row>
     <row r="123" spans="1:60" x14ac:dyDescent="0.25">
@@ -3991,17 +4003,17 @@
       <c r="C123" t="s">
         <v>212</v>
       </c>
-      <c r="U123" t="s">
-        <v>70</v>
-      </c>
-      <c r="AE123" t="s">
-        <v>70</v>
-      </c>
-      <c r="AN123" t="s">
-        <v>70</v>
+      <c r="T123" t="s">
+        <v>69</v>
+      </c>
+      <c r="AD123" t="s">
+        <v>69</v>
+      </c>
+      <c r="AM123" t="s">
+        <v>69</v>
       </c>
       <c r="BH123" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="124" spans="1:60" x14ac:dyDescent="0.25">
@@ -4014,14 +4026,14 @@
       <c r="C124" t="s">
         <v>212</v>
       </c>
-      <c r="U124" t="s">
-        <v>70</v>
-      </c>
-      <c r="AE124" t="s">
-        <v>70</v>
+      <c r="T124" t="s">
+        <v>69</v>
+      </c>
+      <c r="AD124" t="s">
+        <v>69</v>
       </c>
       <c r="BH124" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="125" spans="1:60" x14ac:dyDescent="0.25">
@@ -4034,11 +4046,11 @@
       <c r="C125" t="s">
         <v>212</v>
       </c>
-      <c r="U125" t="s">
-        <v>70</v>
+      <c r="T125" t="s">
+        <v>69</v>
       </c>
       <c r="BH125" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
     </row>
     <row r="126" spans="1:60" x14ac:dyDescent="0.25">
@@ -4051,11 +4063,11 @@
       <c r="C126" t="s">
         <v>212</v>
       </c>
-      <c r="U126" t="s">
-        <v>70</v>
-      </c>
-      <c r="AN126" t="s">
-        <v>70</v>
+      <c r="T126" t="s">
+        <v>69</v>
+      </c>
+      <c r="AM126" t="s">
+        <v>69</v>
       </c>
     </row>
     <row r="127" spans="1:60" x14ac:dyDescent="0.25">
@@ -4068,17 +4080,17 @@
       <c r="C127" t="s">
         <v>212</v>
       </c>
-      <c r="U127" t="s">
-        <v>70</v>
-      </c>
-      <c r="AE127" t="s">
-        <v>70</v>
-      </c>
-      <c r="AN127" t="s">
-        <v>70</v>
+      <c r="T127" t="s">
+        <v>69</v>
+      </c>
+      <c r="AD127" t="s">
+        <v>69</v>
+      </c>
+      <c r="AM127" t="s">
+        <v>69</v>
       </c>
       <c r="BH127" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="128" spans="1:60" x14ac:dyDescent="0.25">
@@ -4091,14 +4103,14 @@
       <c r="C128" t="s">
         <v>212</v>
       </c>
-      <c r="U128" t="s">
-        <v>70</v>
-      </c>
-      <c r="AE128" t="s">
-        <v>70</v>
+      <c r="T128" t="s">
+        <v>69</v>
+      </c>
+      <c r="AD128" t="s">
+        <v>69</v>
       </c>
       <c r="BH128" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="129" spans="1:60" x14ac:dyDescent="0.25">
@@ -4111,14 +4123,14 @@
       <c r="C129" t="s">
         <v>212</v>
       </c>
-      <c r="U129" t="s">
-        <v>70</v>
-      </c>
-      <c r="AE129" t="s">
+      <c r="T129" t="s">
+        <v>69</v>
+      </c>
+      <c r="AD129" t="s">
         <v>124</v>
       </c>
-      <c r="AN129" t="s">
-        <v>70</v>
+      <c r="AM129" t="s">
+        <v>69</v>
       </c>
       <c r="BH129" t="s">
         <v>124</v>
@@ -4135,7 +4147,7 @@
         <v>212</v>
       </c>
       <c r="BA130" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="131" spans="1:60" x14ac:dyDescent="0.25">
@@ -4148,8 +4160,8 @@
       <c r="C131" t="s">
         <v>212</v>
       </c>
-      <c r="AE131" t="s">
-        <v>70</v>
+      <c r="AD131" t="s">
+        <v>69</v>
       </c>
     </row>
     <row r="132" spans="1:60" x14ac:dyDescent="0.25">
@@ -4162,26 +4174,26 @@
       <c r="C132" t="s">
         <v>212</v>
       </c>
-      <c r="O132" t="s">
-        <v>70</v>
-      </c>
-      <c r="Q132" t="s">
-        <v>70</v>
-      </c>
-      <c r="V132" t="s">
-        <v>70</v>
-      </c>
-      <c r="Z132" t="s">
-        <v>69</v>
-      </c>
-      <c r="AC132" t="s">
-        <v>70</v>
-      </c>
-      <c r="AM132" t="s">
+      <c r="N132" t="s">
+        <v>69</v>
+      </c>
+      <c r="P132" t="s">
+        <v>69</v>
+      </c>
+      <c r="U132" t="s">
+        <v>69</v>
+      </c>
+      <c r="Y132" t="s">
+        <v>70</v>
+      </c>
+      <c r="AB132" t="s">
+        <v>69</v>
+      </c>
+      <c r="AL132" t="s">
         <v>81</v>
       </c>
       <c r="BD132" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
     </row>
     <row r="133" spans="1:60" x14ac:dyDescent="0.25">
@@ -4195,10 +4207,10 @@
         <v>212</v>
       </c>
       <c r="BC133" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="BD133" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="134" spans="1:60" x14ac:dyDescent="0.25">
@@ -4211,8 +4223,8 @@
       <c r="C134" t="s">
         <v>212</v>
       </c>
-      <c r="V134" t="s">
-        <v>70</v>
+      <c r="U134" t="s">
+        <v>69</v>
       </c>
     </row>
     <row r="135" spans="1:60" x14ac:dyDescent="0.25">
@@ -4225,11 +4237,11 @@
       <c r="C135" t="s">
         <v>212</v>
       </c>
-      <c r="AM135" t="s">
+      <c r="AL135" t="s">
         <v>81</v>
       </c>
       <c r="BD135" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
     </row>
     <row r="136" spans="1:60" x14ac:dyDescent="0.25">
@@ -4242,11 +4254,11 @@
       <c r="C136" t="s">
         <v>212</v>
       </c>
-      <c r="V136" t="s">
-        <v>70</v>
-      </c>
-      <c r="AC136" t="s">
-        <v>70</v>
+      <c r="U136" t="s">
+        <v>69</v>
+      </c>
+      <c r="AB136" t="s">
+        <v>69</v>
       </c>
     </row>
     <row r="137" spans="1:60" x14ac:dyDescent="0.25">
@@ -4259,13 +4271,13 @@
       <c r="C137" t="s">
         <v>212</v>
       </c>
-      <c r="V137" t="s">
-        <v>70</v>
-      </c>
-      <c r="AC137" t="s">
-        <v>70</v>
-      </c>
-      <c r="AM137" t="s">
+      <c r="U137" t="s">
+        <v>69</v>
+      </c>
+      <c r="AB137" t="s">
+        <v>69</v>
+      </c>
+      <c r="AL137" t="s">
         <v>81</v>
       </c>
     </row>
@@ -4279,7 +4291,7 @@
       <c r="C138" t="s">
         <v>212</v>
       </c>
-      <c r="AM138" t="s">
+      <c r="AL138" t="s">
         <v>81</v>
       </c>
     </row>
@@ -4294,7 +4306,7 @@
         <v>212</v>
       </c>
       <c r="BH139" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
     </row>
     <row r="140" spans="1:60" x14ac:dyDescent="0.25">
@@ -4308,7 +4320,7 @@
         <v>212</v>
       </c>
       <c r="BH140" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
     </row>
     <row r="141" spans="1:60" x14ac:dyDescent="0.25">
@@ -4322,7 +4334,7 @@
         <v>212</v>
       </c>
       <c r="BC141" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="142" spans="1:60" x14ac:dyDescent="0.25">
@@ -4335,26 +4347,26 @@
       <c r="C142" t="s">
         <v>212</v>
       </c>
-      <c r="L142" t="s">
-        <v>69</v>
-      </c>
-      <c r="U142" t="s">
-        <v>70</v>
-      </c>
-      <c r="AF142" t="s">
-        <v>70</v>
-      </c>
-      <c r="AO142" t="s">
+      <c r="T142" t="s">
+        <v>69</v>
+      </c>
+      <c r="AE142" t="s">
+        <v>69</v>
+      </c>
+      <c r="AN142" t="s">
         <v>81</v>
       </c>
+      <c r="AT142" t="s">
+        <v>70</v>
+      </c>
       <c r="AU142" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="AW142" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="BE142" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="143" spans="1:60" x14ac:dyDescent="0.25">
@@ -4367,11 +4379,11 @@
       <c r="C143" t="s">
         <v>212</v>
       </c>
-      <c r="P143" t="s">
-        <v>70</v>
-      </c>
-      <c r="AD143" t="s">
-        <v>70</v>
+      <c r="O143" t="s">
+        <v>69</v>
+      </c>
+      <c r="AC143" t="s">
+        <v>69</v>
       </c>
     </row>
     <row r="144" spans="1:60" x14ac:dyDescent="0.25">
@@ -4385,25 +4397,25 @@
         <v>212</v>
       </c>
       <c r="H144" t="s">
-        <v>70</v>
-      </c>
-      <c r="N144" t="s">
-        <v>70</v>
-      </c>
-      <c r="Y144" t="s">
-        <v>70</v>
-      </c>
-      <c r="AF144" t="s">
-        <v>70</v>
-      </c>
-      <c r="AI144" t="s">
-        <v>70</v>
+        <v>69</v>
+      </c>
+      <c r="M144" t="s">
+        <v>69</v>
+      </c>
+      <c r="X144" t="s">
+        <v>69</v>
+      </c>
+      <c r="AE144" t="s">
+        <v>69</v>
+      </c>
+      <c r="AH144" t="s">
+        <v>69</v>
       </c>
       <c r="AU144" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="BE144" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="145" spans="1:57" x14ac:dyDescent="0.25">
@@ -4417,64 +4429,64 @@
         <v>212</v>
       </c>
       <c r="E145" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="F145" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="H145" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="I145" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="K145" t="s">
-        <v>70</v>
+        <v>69</v>
+      </c>
+      <c r="L145" t="s">
+        <v>69</v>
       </c>
       <c r="M145" t="s">
-        <v>70</v>
-      </c>
-      <c r="N145" t="s">
-        <v>70</v>
-      </c>
-      <c r="P145" t="s">
-        <v>70</v>
-      </c>
-      <c r="R145" t="s">
-        <v>70</v>
+        <v>69</v>
+      </c>
+      <c r="O145" t="s">
+        <v>69</v>
+      </c>
+      <c r="Q145" t="s">
+        <v>69</v>
+      </c>
+      <c r="T145" t="s">
+        <v>69</v>
       </c>
       <c r="U145" t="s">
-        <v>70</v>
-      </c>
-      <c r="V145" t="s">
-        <v>70</v>
-      </c>
-      <c r="Y145" t="s">
-        <v>70</v>
-      </c>
-      <c r="AD145" t="s">
-        <v>70</v>
-      </c>
-      <c r="AF145" t="s">
-        <v>70</v>
-      </c>
-      <c r="AI145" t="s">
-        <v>70</v>
-      </c>
-      <c r="AO145" t="s">
+        <v>69</v>
+      </c>
+      <c r="X145" t="s">
+        <v>69</v>
+      </c>
+      <c r="AC145" t="s">
+        <v>69</v>
+      </c>
+      <c r="AE145" t="s">
+        <v>69</v>
+      </c>
+      <c r="AH145" t="s">
+        <v>69</v>
+      </c>
+      <c r="AN145" t="s">
         <v>81</v>
       </c>
       <c r="AU145" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="AW145" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="AZ145" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="BE145" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="146" spans="1:57" x14ac:dyDescent="0.25">
@@ -4488,67 +4500,67 @@
         <v>212</v>
       </c>
       <c r="E146" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="F146" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="H146" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="I146" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="K146" t="s">
-        <v>70</v>
+        <v>69</v>
+      </c>
+      <c r="L146" t="s">
+        <v>69</v>
       </c>
       <c r="M146" t="s">
-        <v>70</v>
-      </c>
-      <c r="N146" t="s">
-        <v>70</v>
-      </c>
-      <c r="P146" t="s">
-        <v>70</v>
-      </c>
-      <c r="R146" t="s">
-        <v>70</v>
+        <v>69</v>
+      </c>
+      <c r="O146" t="s">
+        <v>69</v>
+      </c>
+      <c r="Q146" t="s">
+        <v>69</v>
+      </c>
+      <c r="T146" t="s">
+        <v>69</v>
       </c>
       <c r="U146" t="s">
-        <v>70</v>
-      </c>
-      <c r="V146" t="s">
-        <v>70</v>
-      </c>
-      <c r="Y146" t="s">
-        <v>70</v>
-      </c>
-      <c r="AB146" t="s">
-        <v>70</v>
-      </c>
-      <c r="AD146" t="s">
-        <v>70</v>
-      </c>
-      <c r="AF146" t="s">
-        <v>70</v>
-      </c>
-      <c r="AI146" t="s">
-        <v>70</v>
-      </c>
-      <c r="AO146" t="s">
+        <v>69</v>
+      </c>
+      <c r="X146" t="s">
+        <v>69</v>
+      </c>
+      <c r="AA146" t="s">
+        <v>69</v>
+      </c>
+      <c r="AC146" t="s">
+        <v>69</v>
+      </c>
+      <c r="AE146" t="s">
+        <v>69</v>
+      </c>
+      <c r="AH146" t="s">
+        <v>69</v>
+      </c>
+      <c r="AN146" t="s">
         <v>81</v>
       </c>
       <c r="AU146" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="AW146" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="AZ146" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="BE146" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="147" spans="1:57" x14ac:dyDescent="0.25">
@@ -4562,61 +4574,61 @@
         <v>212</v>
       </c>
       <c r="E147" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="F147" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="H147" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="I147" t="s">
-        <v>70</v>
+        <v>69</v>
+      </c>
+      <c r="L147" t="s">
+        <v>69</v>
       </c>
       <c r="M147" t="s">
-        <v>70</v>
-      </c>
-      <c r="N147" t="s">
-        <v>70</v>
-      </c>
-      <c r="P147" t="s">
-        <v>70</v>
-      </c>
-      <c r="R147" t="s">
-        <v>70</v>
+        <v>69</v>
+      </c>
+      <c r="O147" t="s">
+        <v>69</v>
+      </c>
+      <c r="Q147" t="s">
+        <v>69</v>
+      </c>
+      <c r="T147" t="s">
+        <v>69</v>
       </c>
       <c r="U147" t="s">
-        <v>70</v>
-      </c>
-      <c r="V147" t="s">
-        <v>70</v>
-      </c>
-      <c r="Y147" t="s">
-        <v>70</v>
-      </c>
-      <c r="AD147" t="s">
-        <v>70</v>
-      </c>
-      <c r="AF147" t="s">
-        <v>70</v>
-      </c>
-      <c r="AI147" t="s">
-        <v>70</v>
-      </c>
-      <c r="AO147" t="s">
+        <v>69</v>
+      </c>
+      <c r="X147" t="s">
+        <v>69</v>
+      </c>
+      <c r="AC147" t="s">
+        <v>69</v>
+      </c>
+      <c r="AE147" t="s">
+        <v>69</v>
+      </c>
+      <c r="AH147" t="s">
+        <v>69</v>
+      </c>
+      <c r="AN147" t="s">
         <v>81</v>
       </c>
       <c r="AU147" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="AW147" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="AZ147" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="BE147" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="148" spans="1:57" x14ac:dyDescent="0.25">
@@ -4629,8 +4641,8 @@
       <c r="C148" t="s">
         <v>212</v>
       </c>
-      <c r="AE148" t="s">
-        <v>70</v>
+      <c r="AD148" t="s">
+        <v>69</v>
       </c>
     </row>
     <row r="149" spans="1:57" x14ac:dyDescent="0.25">
@@ -4643,13 +4655,13 @@
       <c r="C149" t="s">
         <v>212</v>
       </c>
-      <c r="Y149" t="s">
-        <v>70</v>
+      <c r="X149" t="s">
+        <v>69</v>
+      </c>
+      <c r="AC149" t="s">
+        <v>69</v>
       </c>
       <c r="AD149" t="s">
-        <v>70</v>
-      </c>
-      <c r="AE149" t="s">
         <v>124</v>
       </c>
     </row>
@@ -4663,11 +4675,11 @@
       <c r="C150" t="s">
         <v>212</v>
       </c>
-      <c r="N150" t="s">
-        <v>70</v>
-      </c>
-      <c r="AE150" t="s">
-        <v>70</v>
+      <c r="M150" t="s">
+        <v>69</v>
+      </c>
+      <c r="AD150" t="s">
+        <v>69</v>
       </c>
     </row>
     <row r="151" spans="1:57" x14ac:dyDescent="0.25">
@@ -4680,10 +4692,10 @@
       <c r="C151" t="s">
         <v>212</v>
       </c>
+      <c r="AC151" t="s">
+        <v>69</v>
+      </c>
       <c r="AD151" t="s">
-        <v>70</v>
-      </c>
-      <c r="AE151" t="s">
         <v>124</v>
       </c>
     </row>
@@ -4697,8 +4709,8 @@
       <c r="C152" t="s">
         <v>212</v>
       </c>
-      <c r="AD152" t="s">
-        <v>70</v>
+      <c r="AC152" t="s">
+        <v>69</v>
       </c>
     </row>
     <row r="153" spans="1:57" x14ac:dyDescent="0.25">
@@ -4711,11 +4723,11 @@
       <c r="C153" t="s">
         <v>212</v>
       </c>
-      <c r="Y153" t="s">
-        <v>70</v>
-      </c>
-      <c r="AD153" t="s">
-        <v>70</v>
+      <c r="X153" t="s">
+        <v>69</v>
+      </c>
+      <c r="AC153" t="s">
+        <v>69</v>
       </c>
     </row>
     <row r="154" spans="1:57" x14ac:dyDescent="0.25">
@@ -4728,11 +4740,11 @@
       <c r="C154" t="s">
         <v>212</v>
       </c>
-      <c r="N154" t="s">
-        <v>70</v>
-      </c>
-      <c r="Y154" t="s">
-        <v>70</v>
+      <c r="M154" t="s">
+        <v>69</v>
+      </c>
+      <c r="X154" t="s">
+        <v>69</v>
       </c>
     </row>
     <row r="155" spans="1:57" x14ac:dyDescent="0.25">
@@ -4745,8 +4757,8 @@
       <c r="C155" t="s">
         <v>212</v>
       </c>
-      <c r="AD155" t="s">
-        <v>70</v>
+      <c r="AC155" t="s">
+        <v>69</v>
       </c>
     </row>
     <row r="156" spans="1:57" x14ac:dyDescent="0.25">
@@ -4759,14 +4771,14 @@
       <c r="C156" t="s">
         <v>212</v>
       </c>
-      <c r="N156" t="s">
-        <v>70</v>
-      </c>
-      <c r="Y156" t="s">
-        <v>70</v>
-      </c>
-      <c r="AE156" t="s">
-        <v>70</v>
+      <c r="M156" t="s">
+        <v>69</v>
+      </c>
+      <c r="X156" t="s">
+        <v>69</v>
+      </c>
+      <c r="AD156" t="s">
+        <v>69</v>
       </c>
     </row>
     <row r="157" spans="1:57" x14ac:dyDescent="0.25">
@@ -4779,8 +4791,8 @@
       <c r="C157" t="s">
         <v>212</v>
       </c>
-      <c r="V157" t="s">
-        <v>70</v>
+      <c r="U157" t="s">
+        <v>69</v>
       </c>
     </row>
     <row r="158" spans="1:57" x14ac:dyDescent="0.25">
@@ -4793,8 +4805,8 @@
       <c r="C158" t="s">
         <v>212</v>
       </c>
-      <c r="AC158" t="s">
-        <v>70</v>
+      <c r="AB158" t="s">
+        <v>69</v>
       </c>
     </row>
     <row r="159" spans="1:57" x14ac:dyDescent="0.25">
@@ -4807,8 +4819,8 @@
       <c r="C159" t="s">
         <v>212</v>
       </c>
-      <c r="V159" t="s">
-        <v>70</v>
+      <c r="U159" t="s">
+        <v>69</v>
       </c>
     </row>
     <row r="160" spans="1:57" x14ac:dyDescent="0.25">
@@ -4822,34 +4834,34 @@
         <v>212</v>
       </c>
       <c r="H160" t="s">
-        <v>70</v>
-      </c>
-      <c r="P160" t="s">
-        <v>70</v>
-      </c>
-      <c r="Y160" t="s">
-        <v>70</v>
+        <v>69</v>
+      </c>
+      <c r="O160" t="s">
+        <v>69</v>
+      </c>
+      <c r="X160" t="s">
+        <v>69</v>
+      </c>
+      <c r="AC160" t="s">
+        <v>69</v>
       </c>
       <c r="AD160" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="AE160" t="s">
-        <v>70</v>
-      </c>
-      <c r="AF160" t="s">
-        <v>70</v>
-      </c>
-      <c r="AI160" t="s">
-        <v>70</v>
+        <v>69</v>
+      </c>
+      <c r="AH160" t="s">
+        <v>69</v>
       </c>
       <c r="AU160" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="AW160" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="BE160" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="161" spans="1:60" x14ac:dyDescent="0.25">
@@ -4863,28 +4875,28 @@
         <v>212</v>
       </c>
       <c r="E161" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="F161" t="s">
-        <v>70</v>
-      </c>
-      <c r="T161" t="s">
-        <v>69</v>
-      </c>
-      <c r="AJ161" t="s">
-        <v>70</v>
-      </c>
-      <c r="AL161" t="s">
-        <v>70</v>
+        <v>69</v>
+      </c>
+      <c r="S161" t="s">
+        <v>70</v>
+      </c>
+      <c r="AI161" t="s">
+        <v>69</v>
+      </c>
+      <c r="AK161" t="s">
+        <v>69</v>
       </c>
       <c r="BC161" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="BD161" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="BH161" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="162" spans="1:60" x14ac:dyDescent="0.25">
@@ -4898,10 +4910,10 @@
         <v>212</v>
       </c>
       <c r="BC162" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="BH162" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
     </row>
     <row r="163" spans="1:60" x14ac:dyDescent="0.25">
@@ -4915,7 +4927,7 @@
         <v>212</v>
       </c>
       <c r="AZ163" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="164" spans="1:60" x14ac:dyDescent="0.25">
@@ -4928,11 +4940,11 @@
       <c r="C164" t="s">
         <v>212</v>
       </c>
-      <c r="N164" t="s">
-        <v>70</v>
-      </c>
-      <c r="Y164" t="s">
-        <v>70</v>
+      <c r="M164" t="s">
+        <v>69</v>
+      </c>
+      <c r="X164" t="s">
+        <v>69</v>
       </c>
       <c r="AZ164" t="s">
         <v>81</v>
@@ -4948,8 +4960,8 @@
       <c r="C165" t="s">
         <v>212</v>
       </c>
-      <c r="N165" t="s">
-        <v>69</v>
+      <c r="M165" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="166" spans="1:60" x14ac:dyDescent="0.25">
@@ -4962,11 +4974,11 @@
       <c r="C166" t="s">
         <v>212</v>
       </c>
-      <c r="N166" t="s">
-        <v>70</v>
+      <c r="M166" t="s">
+        <v>69</v>
       </c>
       <c r="AZ166" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="167" spans="1:60" x14ac:dyDescent="0.25">
@@ -4979,20 +4991,20 @@
       <c r="C167" t="s">
         <v>212</v>
       </c>
+      <c r="T167" t="s">
+        <v>69</v>
+      </c>
       <c r="U167" t="s">
-        <v>70</v>
-      </c>
-      <c r="V167" t="s">
-        <v>70</v>
-      </c>
-      <c r="AC167" t="s">
-        <v>70</v>
-      </c>
-      <c r="AN167" t="s">
-        <v>70</v>
+        <v>69</v>
+      </c>
+      <c r="AB167" t="s">
+        <v>69</v>
+      </c>
+      <c r="AM167" t="s">
+        <v>69</v>
       </c>
       <c r="BH167" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="168" spans="1:60" x14ac:dyDescent="0.25">
@@ -5005,14 +5017,14 @@
       <c r="C168" t="s">
         <v>212</v>
       </c>
+      <c r="T168" t="s">
+        <v>69</v>
+      </c>
       <c r="U168" t="s">
-        <v>70</v>
-      </c>
-      <c r="V168" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="BH168" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
     </row>
     <row r="169" spans="1:60" x14ac:dyDescent="0.25">
@@ -5025,14 +5037,14 @@
       <c r="C169" t="s">
         <v>212</v>
       </c>
-      <c r="N169" t="s">
-        <v>69</v>
-      </c>
-      <c r="AE169" t="s">
-        <v>70</v>
+      <c r="M169" t="s">
+        <v>70</v>
+      </c>
+      <c r="AD169" t="s">
+        <v>69</v>
       </c>
       <c r="BH169" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="170" spans="1:60" x14ac:dyDescent="0.25">
@@ -5045,20 +5057,20 @@
       <c r="C170" t="s">
         <v>212</v>
       </c>
+      <c r="AL170" t="s">
+        <v>70</v>
+      </c>
       <c r="AM170" t="s">
         <v>69</v>
       </c>
-      <c r="AN170" t="s">
-        <v>70</v>
-      </c>
       <c r="BC170" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="BD170" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="BH170" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="171" spans="1:60" x14ac:dyDescent="0.25">
@@ -5071,11 +5083,11 @@
       <c r="C171" t="s">
         <v>212</v>
       </c>
-      <c r="AN171" t="s">
-        <v>70</v>
+      <c r="AM171" t="s">
+        <v>69</v>
       </c>
       <c r="BC171" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="172" spans="1:60" x14ac:dyDescent="0.25">
@@ -5088,20 +5100,20 @@
       <c r="C172" t="s">
         <v>212</v>
       </c>
-      <c r="V172" t="s">
-        <v>70</v>
-      </c>
-      <c r="AC172" t="s">
+      <c r="U172" t="s">
+        <v>69</v>
+      </c>
+      <c r="AB172" t="s">
+        <v>69</v>
+      </c>
+      <c r="AL172" t="s">
         <v>70</v>
       </c>
       <c r="AM172" t="s">
         <v>69</v>
       </c>
-      <c r="AN172" t="s">
-        <v>70</v>
-      </c>
       <c r="BC172" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="173" spans="1:60" x14ac:dyDescent="0.25">
@@ -5115,7 +5127,7 @@
         <v>212</v>
       </c>
       <c r="BH173" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
     </row>
   </sheetData>

--- a/html/Specialsystemer_excel.XLSX
+++ b/html/Specialsystemer_excel.XLSX
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hua\GitHub\GodkendteSystemer\html\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Documents\GitHub\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{67E5624E-7244-4081-92A9-70A23BE0F921}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{42B413A9-32F7-4F0B-A29C-1D02C3709FA2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-15" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Opdateret d. 09-10-2026" sheetId="1" r:id="rId1"/>

--- a/html/Specialsystemer_excel.XLSX
+++ b/html/Specialsystemer_excel.XLSX
@@ -5,18 +5,18 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Documents\GitHub\GodkendteSystemer\html\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://medcomdk-my.sharepoint.com/personal/ras_medcom_dk/Documents/Dokumenter/GitHub/GodkendteSystemer/html/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{42B413A9-32F7-4F0B-A29C-1D02C3709FA2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="1" documentId="11_BEA61AB98A45F5CBDB0A2A165E7380DE70D9687B" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{94EFBB04-B6A9-4D18-9A0E-8FD08F07B4A0}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-15" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1710" yWindow="1560" windowWidth="14400" windowHeight="8205" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 09-10-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 23-10-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Specialsystemer">'Opdateret d. 09-10-2026'!$A$1:$BN$173</definedName>
+    <definedName name="Specialsystemer">'Opdateret d. 23-10-2026'!$A$1:$BN$173</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>
